--- a/LangMod/EN/Things.xlsx
+++ b/LangMod/EN/Things.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -11,7 +11,7 @@
     <sheet name="Thing" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Thing!$A$3:$AZ$426</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Thing!$A$3:$AZ$425</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -852,8 +852,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="6.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="8.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="10.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="11.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="6.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="1" width="4.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="9.46"/>
@@ -2405,10 +2404,10 @@
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
+      <c r="T17" s="2"/>
       <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
       <c r="X17" s="3"/>
       <c r="Y17" s="2"/>
       <c r="Z17" s="3"/>
@@ -2479,12 +2478,12 @@
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
-      <c r="T18" s="2"/>
+      <c r="T18" s="3"/>
       <c r="U18" s="3"/>
-      <c r="V18" s="2"/>
-      <c r="W18" s="2"/>
+      <c r="V18" s="3"/>
+      <c r="W18" s="3"/>
       <c r="X18" s="3"/>
-      <c r="Y18" s="2"/>
+      <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
       <c r="AA18" s="4"/>
       <c r="AB18" s="5"/>
@@ -2493,7 +2492,7 @@
       <c r="AE18" s="3"/>
       <c r="AF18" s="4"/>
       <c r="AG18" s="3"/>
-      <c r="AH18" s="2"/>
+      <c r="AH18" s="3"/>
       <c r="AI18" s="3"/>
       <c r="AJ18" s="3"/>
       <c r="AK18" s="3"/>
@@ -2509,7 +2508,7 @@
       <c r="AU18" s="3"/>
       <c r="AV18" s="3"/>
       <c r="AW18" s="3"/>
-      <c r="AX18" s="2"/>
+      <c r="AX18" s="3"/>
       <c r="AY18" s="3"/>
       <c r="AZ18" s="3"/>
       <c r="BA18" s="3"/>
@@ -2556,9 +2555,9 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
+      <c r="W19" s="2"/>
       <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
+      <c r="Y19" s="2"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="4"/>
       <c r="AB19" s="5"/>
@@ -2567,7 +2566,7 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="4"/>
       <c r="AG19" s="3"/>
-      <c r="AH19" s="3"/>
+      <c r="AH19" s="2"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
@@ -2629,8 +2628,8 @@
       <c r="S20" s="3"/>
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
-      <c r="V20" s="3"/>
-      <c r="W20" s="2"/>
+      <c r="V20" s="2"/>
+      <c r="W20" s="3"/>
       <c r="X20" s="3"/>
       <c r="Y20" s="2"/>
       <c r="Z20" s="3"/>
@@ -2704,7 +2703,7 @@
       <c r="T21" s="3"/>
       <c r="U21" s="3"/>
       <c r="V21" s="2"/>
-      <c r="W21" s="3"/>
+      <c r="W21" s="2"/>
       <c r="X21" s="3"/>
       <c r="Y21" s="2"/>
       <c r="Z21" s="3"/>
@@ -2789,7 +2788,7 @@
       <c r="AE22" s="3"/>
       <c r="AF22" s="4"/>
       <c r="AG22" s="3"/>
-      <c r="AH22" s="2"/>
+      <c r="AH22" s="3"/>
       <c r="AI22" s="3"/>
       <c r="AJ22" s="3"/>
       <c r="AK22" s="3"/>
@@ -2803,7 +2802,7 @@
       <c r="AS22" s="3"/>
       <c r="AT22" s="3"/>
       <c r="AU22" s="3"/>
-      <c r="AV22" s="3"/>
+      <c r="AV22" s="2"/>
       <c r="AW22" s="3"/>
       <c r="AX22" s="3"/>
       <c r="AY22" s="3"/>
@@ -2852,7 +2851,7 @@
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
       <c r="V23" s="2"/>
-      <c r="W23" s="2"/>
+      <c r="W23" s="3"/>
       <c r="X23" s="3"/>
       <c r="Y23" s="2"/>
       <c r="Z23" s="3"/>
@@ -2863,7 +2862,7 @@
       <c r="AE23" s="3"/>
       <c r="AF23" s="4"/>
       <c r="AG23" s="3"/>
-      <c r="AH23" s="3"/>
+      <c r="AH23" s="2"/>
       <c r="AI23" s="3"/>
       <c r="AJ23" s="3"/>
       <c r="AK23" s="3"/>
@@ -2877,7 +2876,7 @@
       <c r="AS23" s="3"/>
       <c r="AT23" s="3"/>
       <c r="AU23" s="3"/>
-      <c r="AV23" s="2"/>
+      <c r="AV23" s="3"/>
       <c r="AW23" s="3"/>
       <c r="AX23" s="3"/>
       <c r="AY23" s="3"/>
@@ -2951,7 +2950,7 @@
       <c r="AS24" s="3"/>
       <c r="AT24" s="3"/>
       <c r="AU24" s="3"/>
-      <c r="AV24" s="3"/>
+      <c r="AV24" s="2"/>
       <c r="AW24" s="3"/>
       <c r="AX24" s="3"/>
       <c r="AY24" s="3"/>
@@ -2983,7 +2982,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
-      <c r="F25" s="2"/>
+      <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="2"/>
@@ -2999,8 +2998,8 @@
       <c r="S25" s="3"/>
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
-      <c r="V25" s="2"/>
-      <c r="W25" s="3"/>
+      <c r="V25" s="3"/>
+      <c r="W25" s="2"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="2"/>
       <c r="Z25" s="3"/>
@@ -3011,7 +3010,7 @@
       <c r="AE25" s="3"/>
       <c r="AF25" s="4"/>
       <c r="AG25" s="3"/>
-      <c r="AH25" s="2"/>
+      <c r="AH25" s="3"/>
       <c r="AI25" s="3"/>
       <c r="AJ25" s="3"/>
       <c r="AK25" s="3"/>
@@ -3025,7 +3024,7 @@
       <c r="AS25" s="3"/>
       <c r="AT25" s="3"/>
       <c r="AU25" s="3"/>
-      <c r="AV25" s="2"/>
+      <c r="AV25" s="3"/>
       <c r="AW25" s="3"/>
       <c r="AX25" s="3"/>
       <c r="AY25" s="3"/>
@@ -3131,7 +3130,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
+      <c r="F27" s="2"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="2"/>
@@ -3205,7 +3204,7 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
-      <c r="F28" s="2"/>
+      <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="2"/>
@@ -3279,7 +3278,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
+      <c r="F29" s="2"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="2"/>
@@ -3359,7 +3358,7 @@
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
+      <c r="L30" s="2"/>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
       <c r="O30" s="3"/>
@@ -3433,7 +3432,7 @@
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="3"/>
-      <c r="L31" s="2"/>
+      <c r="L31" s="3"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
       <c r="O31" s="3"/>
@@ -3739,10 +3738,10 @@
       <c r="S35" s="3"/>
       <c r="T35" s="3"/>
       <c r="U35" s="3"/>
-      <c r="V35" s="3"/>
-      <c r="W35" s="2"/>
+      <c r="V35" s="2"/>
+      <c r="W35" s="3"/>
       <c r="X35" s="3"/>
-      <c r="Y35" s="2"/>
+      <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
       <c r="AA35" s="4"/>
       <c r="AB35" s="5"/>
@@ -3816,7 +3815,7 @@
       <c r="V36" s="2"/>
       <c r="W36" s="3"/>
       <c r="X36" s="3"/>
-      <c r="Y36" s="3"/>
+      <c r="Y36" s="2"/>
       <c r="Z36" s="3"/>
       <c r="AA36" s="4"/>
       <c r="AB36" s="5"/>
@@ -3877,7 +3876,7 @@
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="3"/>
-      <c r="L37" s="3"/>
+      <c r="L37" s="2"/>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
       <c r="O37" s="3"/>
@@ -3887,8 +3886,8 @@
       <c r="S37" s="3"/>
       <c r="T37" s="3"/>
       <c r="U37" s="3"/>
-      <c r="V37" s="2"/>
-      <c r="W37" s="3"/>
+      <c r="V37" s="3"/>
+      <c r="W37" s="2"/>
       <c r="X37" s="3"/>
       <c r="Y37" s="2"/>
       <c r="Z37" s="3"/>
@@ -3951,7 +3950,7 @@
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="3"/>
-      <c r="L38" s="2"/>
+      <c r="L38" s="3"/>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
       <c r="O38" s="3"/>
@@ -3962,7 +3961,7 @@
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
-      <c r="W38" s="2"/>
+      <c r="W38" s="3"/>
       <c r="X38" s="3"/>
       <c r="Y38" s="2"/>
       <c r="Z38" s="3"/>
@@ -4025,7 +4024,7 @@
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
+      <c r="L39" s="2"/>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
       <c r="O39" s="3"/>
@@ -4036,7 +4035,7 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-      <c r="W39" s="3"/>
+      <c r="W39" s="2"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="2"/>
       <c r="Z39" s="3"/>
@@ -4055,7 +4054,7 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
-      <c r="AP39" s="3"/>
+      <c r="AP39" s="2"/>
       <c r="AQ39" s="3"/>
       <c r="AR39" s="3"/>
       <c r="AS39" s="3"/>
@@ -4106,13 +4105,13 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-      <c r="S40" s="3"/>
+      <c r="S40" s="2"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-      <c r="W40" s="2"/>
+      <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-      <c r="Y40" s="2"/>
+      <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="4"/>
       <c r="AB40" s="5"/>
@@ -4129,7 +4128,7 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
-      <c r="AP40" s="2"/>
+      <c r="AP40" s="3"/>
       <c r="AQ40" s="3"/>
       <c r="AR40" s="3"/>
       <c r="AS40" s="3"/>
@@ -4173,20 +4172,20 @@
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="3"/>
-      <c r="L41" s="2"/>
+      <c r="L41" s="3"/>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
       <c r="O41" s="3"/>
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
-      <c r="S41" s="2"/>
+      <c r="S41" s="3"/>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
       <c r="V41" s="3"/>
-      <c r="W41" s="3"/>
+      <c r="W41" s="2"/>
       <c r="X41" s="3"/>
-      <c r="Y41" s="3"/>
+      <c r="Y41" s="2"/>
       <c r="Z41" s="3"/>
       <c r="AA41" s="4"/>
       <c r="AB41" s="5"/>
@@ -4195,7 +4194,7 @@
       <c r="AE41" s="3"/>
       <c r="AF41" s="4"/>
       <c r="AG41" s="3"/>
-      <c r="AH41" s="3"/>
+      <c r="AH41" s="2"/>
       <c r="AI41" s="3"/>
       <c r="AJ41" s="3"/>
       <c r="AK41" s="3"/>
@@ -4246,7 +4245,7 @@
       <c r="H42" s="3"/>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
-      <c r="K42" s="3"/>
+      <c r="K42" s="2"/>
       <c r="L42" s="3"/>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
@@ -4258,9 +4257,9 @@
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
-      <c r="W42" s="2"/>
+      <c r="W42" s="3"/>
       <c r="X42" s="3"/>
-      <c r="Y42" s="2"/>
+      <c r="Y42" s="3"/>
       <c r="Z42" s="3"/>
       <c r="AA42" s="4"/>
       <c r="AB42" s="5"/>
@@ -4281,7 +4280,7 @@
       <c r="AQ42" s="3"/>
       <c r="AR42" s="3"/>
       <c r="AS42" s="3"/>
-      <c r="AT42" s="3"/>
+      <c r="AT42" s="2"/>
       <c r="AU42" s="3"/>
       <c r="AV42" s="3"/>
       <c r="AW42" s="3"/>
@@ -4320,7 +4319,7 @@
       <c r="H43" s="3"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
+      <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
@@ -4343,7 +4342,7 @@
       <c r="AE43" s="3"/>
       <c r="AF43" s="4"/>
       <c r="AG43" s="3"/>
-      <c r="AH43" s="2"/>
+      <c r="AH43" s="3"/>
       <c r="AI43" s="3"/>
       <c r="AJ43" s="3"/>
       <c r="AK43" s="3"/>
@@ -4355,7 +4354,7 @@
       <c r="AQ43" s="3"/>
       <c r="AR43" s="3"/>
       <c r="AS43" s="3"/>
-      <c r="AT43" s="2"/>
+      <c r="AT43" s="3"/>
       <c r="AU43" s="3"/>
       <c r="AV43" s="3"/>
       <c r="AW43" s="3"/>
@@ -4406,9 +4405,9 @@
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
-      <c r="W44" s="3"/>
+      <c r="W44" s="2"/>
       <c r="X44" s="3"/>
-      <c r="Y44" s="3"/>
+      <c r="Y44" s="2"/>
       <c r="Z44" s="3"/>
       <c r="AA44" s="4"/>
       <c r="AB44" s="5"/>
@@ -4725,11 +4724,11 @@
       <c r="AQ48" s="3"/>
       <c r="AR48" s="3"/>
       <c r="AS48" s="3"/>
-      <c r="AT48" s="3"/>
+      <c r="AT48" s="2"/>
       <c r="AU48" s="3"/>
       <c r="AV48" s="3"/>
       <c r="AW48" s="3"/>
-      <c r="AX48" s="3"/>
+      <c r="AX48" s="2"/>
       <c r="AY48" s="3"/>
       <c r="AZ48" s="3"/>
       <c r="BA48" s="3"/>
@@ -4776,7 +4775,7 @@
       <c r="T49" s="3"/>
       <c r="U49" s="3"/>
       <c r="V49" s="3"/>
-      <c r="W49" s="2"/>
+      <c r="W49" s="3"/>
       <c r="X49" s="3"/>
       <c r="Y49" s="2"/>
       <c r="Z49" s="3"/>
@@ -4799,11 +4798,11 @@
       <c r="AQ49" s="3"/>
       <c r="AR49" s="3"/>
       <c r="AS49" s="3"/>
-      <c r="AT49" s="2"/>
+      <c r="AT49" s="3"/>
       <c r="AU49" s="3"/>
       <c r="AV49" s="3"/>
       <c r="AW49" s="3"/>
-      <c r="AX49" s="2"/>
+      <c r="AX49" s="3"/>
       <c r="AY49" s="3"/>
       <c r="AZ49" s="3"/>
       <c r="BA49" s="3"/>
@@ -4850,7 +4849,7 @@
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3"/>
-      <c r="W50" s="3"/>
+      <c r="W50" s="2"/>
       <c r="X50" s="3"/>
       <c r="Y50" s="2"/>
       <c r="Z50" s="3"/>
@@ -4982,7 +4981,7 @@
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
       <c r="F52" s="2"/>
-      <c r="G52" s="3"/>
+      <c r="G52" s="2"/>
       <c r="H52" s="3"/>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
@@ -5130,7 +5129,7 @@
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
       <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
+      <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
@@ -5146,7 +5145,7 @@
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
-      <c r="W54" s="2"/>
+      <c r="W54" s="3"/>
       <c r="X54" s="3"/>
       <c r="Y54" s="2"/>
       <c r="Z54" s="3"/>
@@ -5157,7 +5156,7 @@
       <c r="AE54" s="3"/>
       <c r="AF54" s="4"/>
       <c r="AG54" s="3"/>
-      <c r="AH54" s="3"/>
+      <c r="AH54" s="2"/>
       <c r="AI54" s="3"/>
       <c r="AJ54" s="3"/>
       <c r="AK54" s="3"/>
@@ -5231,7 +5230,7 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="4"/>
       <c r="AG55" s="3"/>
-      <c r="AH55" s="2"/>
+      <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
@@ -5243,11 +5242,11 @@
       <c r="AQ55" s="3"/>
       <c r="AR55" s="3"/>
       <c r="AS55" s="3"/>
-      <c r="AT55" s="3"/>
+      <c r="AT55" s="2"/>
       <c r="AU55" s="3"/>
       <c r="AV55" s="3"/>
       <c r="AW55" s="3"/>
-      <c r="AX55" s="3"/>
+      <c r="AX55" s="2"/>
       <c r="AY55" s="3"/>
       <c r="AZ55" s="3"/>
       <c r="BA55" s="3"/>
@@ -5282,8 +5281,8 @@
       <c r="H56" s="3"/>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
-      <c r="K56" s="3"/>
-      <c r="L56" s="3"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
       <c r="O56" s="3"/>
@@ -5293,10 +5292,10 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-      <c r="V56" s="3"/>
+      <c r="V56" s="2"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-      <c r="Y56" s="2"/>
+      <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="4"/>
       <c r="AB56" s="5"/>
@@ -5305,7 +5304,7 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="4"/>
       <c r="AG56" s="3"/>
-      <c r="AH56" s="3"/>
+      <c r="AH56" s="2"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
@@ -5317,13 +5316,13 @@
       <c r="AQ56" s="3"/>
       <c r="AR56" s="3"/>
       <c r="AS56" s="3"/>
-      <c r="AT56" s="2"/>
+      <c r="AT56" s="3"/>
       <c r="AU56" s="3"/>
       <c r="AV56" s="3"/>
       <c r="AW56" s="3"/>
-      <c r="AX56" s="2"/>
+      <c r="AX56" s="3"/>
       <c r="AY56" s="3"/>
-      <c r="AZ56" s="3"/>
+      <c r="AZ56" s="2"/>
       <c r="BA56" s="3"/>
       <c r="BB56" s="3"/>
       <c r="BC56" s="3"/>
@@ -5397,7 +5396,7 @@
       <c r="AW57" s="3"/>
       <c r="AX57" s="3"/>
       <c r="AY57" s="3"/>
-      <c r="AZ57" s="2"/>
+      <c r="AZ57" s="3"/>
       <c r="BA57" s="3"/>
       <c r="BB57" s="3"/>
       <c r="BC57" s="3"/>
@@ -5441,7 +5440,7 @@
       <c r="S58" s="3"/>
       <c r="T58" s="3"/>
       <c r="U58" s="3"/>
-      <c r="V58" s="2"/>
+      <c r="V58" s="12"/>
       <c r="W58" s="3"/>
       <c r="X58" s="3"/>
       <c r="Y58" s="3"/>
@@ -5471,7 +5470,7 @@
       <c r="AW58" s="3"/>
       <c r="AX58" s="3"/>
       <c r="AY58" s="3"/>
-      <c r="AZ58" s="3"/>
+      <c r="AZ58" s="2"/>
       <c r="BA58" s="3"/>
       <c r="BB58" s="3"/>
       <c r="BC58" s="3"/>
@@ -5515,7 +5514,7 @@
       <c r="S59" s="3"/>
       <c r="T59" s="3"/>
       <c r="U59" s="3"/>
-      <c r="V59" s="12"/>
+      <c r="V59" s="2"/>
       <c r="W59" s="3"/>
       <c r="X59" s="3"/>
       <c r="Y59" s="3"/>
@@ -5590,9 +5589,9 @@
       <c r="T60" s="3"/>
       <c r="U60" s="3"/>
       <c r="V60" s="2"/>
-      <c r="W60" s="3"/>
+      <c r="W60" s="2"/>
       <c r="X60" s="3"/>
-      <c r="Y60" s="3"/>
+      <c r="Y60" s="2"/>
       <c r="Z60" s="3"/>
       <c r="AA60" s="4"/>
       <c r="AB60" s="5"/>
@@ -5738,9 +5737,9 @@
       <c r="T62" s="3"/>
       <c r="U62" s="3"/>
       <c r="V62" s="2"/>
-      <c r="W62" s="2"/>
+      <c r="W62" s="3"/>
       <c r="X62" s="3"/>
-      <c r="Y62" s="2"/>
+      <c r="Y62" s="3"/>
       <c r="Z62" s="3"/>
       <c r="AA62" s="4"/>
       <c r="AB62" s="5"/>
@@ -5812,9 +5811,9 @@
       <c r="T63" s="3"/>
       <c r="U63" s="3"/>
       <c r="V63" s="2"/>
-      <c r="W63" s="3"/>
+      <c r="W63" s="2"/>
       <c r="X63" s="3"/>
-      <c r="Y63" s="3"/>
+      <c r="Y63" s="2"/>
       <c r="Z63" s="3"/>
       <c r="AA63" s="4"/>
       <c r="AB63" s="5"/>
@@ -5989,7 +5988,7 @@
       <c r="AW65" s="3"/>
       <c r="AX65" s="3"/>
       <c r="AY65" s="3"/>
-      <c r="AZ65" s="2"/>
+      <c r="AZ65" s="3"/>
       <c r="BA65" s="3"/>
       <c r="BB65" s="3"/>
       <c r="BC65" s="3"/>
@@ -6022,7 +6021,7 @@
       <c r="H66" s="3"/>
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
-      <c r="K66" s="2"/>
+      <c r="K66" s="3"/>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
@@ -6033,20 +6032,20 @@
       <c r="S66" s="3"/>
       <c r="T66" s="3"/>
       <c r="U66" s="3"/>
-      <c r="V66" s="2"/>
-      <c r="W66" s="2"/>
+      <c r="V66" s="3"/>
+      <c r="W66" s="3"/>
       <c r="X66" s="3"/>
       <c r="Y66" s="2"/>
       <c r="Z66" s="3"/>
       <c r="AA66" s="4"/>
       <c r="AB66" s="5"/>
-      <c r="AC66" s="3"/>
+      <c r="AC66" s="2"/>
       <c r="AD66" s="3"/>
       <c r="AE66" s="3"/>
       <c r="AF66" s="4"/>
       <c r="AG66" s="3"/>
       <c r="AH66" s="2"/>
-      <c r="AI66" s="3"/>
+      <c r="AI66" s="6"/>
       <c r="AJ66" s="3"/>
       <c r="AK66" s="3"/>
       <c r="AL66" s="3"/>
@@ -6184,7 +6183,7 @@
       <c r="V68" s="3"/>
       <c r="W68" s="3"/>
       <c r="X68" s="3"/>
-      <c r="Y68" s="2"/>
+      <c r="Y68" s="3"/>
       <c r="Z68" s="3"/>
       <c r="AA68" s="4"/>
       <c r="AB68" s="5"/>
@@ -6256,19 +6255,19 @@
       <c r="T69" s="3"/>
       <c r="U69" s="3"/>
       <c r="V69" s="3"/>
-      <c r="W69" s="3"/>
+      <c r="W69" s="2"/>
       <c r="X69" s="3"/>
       <c r="Y69" s="3"/>
       <c r="Z69" s="3"/>
       <c r="AA69" s="4"/>
       <c r="AB69" s="5"/>
-      <c r="AC69" s="2"/>
+      <c r="AC69" s="3"/>
       <c r="AD69" s="3"/>
-      <c r="AE69" s="3"/>
+      <c r="AE69" s="2"/>
       <c r="AF69" s="4"/>
       <c r="AG69" s="3"/>
-      <c r="AH69" s="2"/>
-      <c r="AI69" s="6"/>
+      <c r="AH69" s="3"/>
+      <c r="AI69" s="3"/>
       <c r="AJ69" s="3"/>
       <c r="AK69" s="3"/>
       <c r="AL69" s="3"/>
@@ -6283,7 +6282,7 @@
       <c r="AU69" s="3"/>
       <c r="AV69" s="3"/>
       <c r="AW69" s="3"/>
-      <c r="AX69" s="3"/>
+      <c r="AX69" s="2"/>
       <c r="AY69" s="3"/>
       <c r="AZ69" s="3"/>
       <c r="BA69" s="3"/>
@@ -6332,13 +6331,13 @@
       <c r="V70" s="3"/>
       <c r="W70" s="2"/>
       <c r="X70" s="3"/>
-      <c r="Y70" s="3"/>
+      <c r="Y70" s="2"/>
       <c r="Z70" s="3"/>
       <c r="AA70" s="4"/>
       <c r="AB70" s="5"/>
       <c r="AC70" s="3"/>
       <c r="AD70" s="3"/>
-      <c r="AE70" s="2"/>
+      <c r="AE70" s="3"/>
       <c r="AF70" s="4"/>
       <c r="AG70" s="3"/>
       <c r="AH70" s="3"/>
@@ -6357,7 +6356,7 @@
       <c r="AU70" s="3"/>
       <c r="AV70" s="3"/>
       <c r="AW70" s="3"/>
-      <c r="AX70" s="2"/>
+      <c r="AX70" s="3"/>
       <c r="AY70" s="3"/>
       <c r="AZ70" s="3"/>
       <c r="BA70" s="3"/>
@@ -6467,7 +6466,7 @@
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
       <c r="K72" s="3"/>
-      <c r="L72" s="2"/>
+      <c r="L72" s="3"/>
       <c r="M72" s="2"/>
       <c r="N72" s="2"/>
       <c r="O72" s="3"/>
@@ -6478,9 +6477,9 @@
       <c r="T72" s="3"/>
       <c r="U72" s="3"/>
       <c r="V72" s="3"/>
-      <c r="W72" s="2"/>
+      <c r="W72" s="3"/>
       <c r="X72" s="3"/>
-      <c r="Y72" s="2"/>
+      <c r="Y72" s="3"/>
       <c r="Z72" s="3"/>
       <c r="AA72" s="4"/>
       <c r="AB72" s="5"/>
@@ -6554,7 +6553,7 @@
       <c r="V73" s="3"/>
       <c r="W73" s="3"/>
       <c r="X73" s="3"/>
-      <c r="Y73" s="3"/>
+      <c r="Y73" s="2"/>
       <c r="Z73" s="3"/>
       <c r="AA73" s="4"/>
       <c r="AB73" s="5"/>
@@ -6577,7 +6576,7 @@
       <c r="AS73" s="3"/>
       <c r="AT73" s="3"/>
       <c r="AU73" s="3"/>
-      <c r="AV73" s="3"/>
+      <c r="AV73" s="2"/>
       <c r="AW73" s="3"/>
       <c r="AX73" s="3"/>
       <c r="AY73" s="3"/>
@@ -6626,9 +6625,9 @@
       <c r="T74" s="3"/>
       <c r="U74" s="3"/>
       <c r="V74" s="3"/>
-      <c r="W74" s="3"/>
+      <c r="W74" s="2"/>
       <c r="X74" s="3"/>
-      <c r="Y74" s="2"/>
+      <c r="Y74" s="3"/>
       <c r="Z74" s="3"/>
       <c r="AA74" s="4"/>
       <c r="AB74" s="5"/>
@@ -6651,7 +6650,7 @@
       <c r="AS74" s="3"/>
       <c r="AT74" s="3"/>
       <c r="AU74" s="3"/>
-      <c r="AV74" s="2"/>
+      <c r="AV74" s="3"/>
       <c r="AW74" s="3"/>
       <c r="AX74" s="3"/>
       <c r="AY74" s="3"/>
@@ -6689,7 +6688,7 @@
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
       <c r="K75" s="3"/>
-      <c r="L75" s="3"/>
+      <c r="L75" s="2"/>
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
       <c r="O75" s="3"/>
@@ -6776,7 +6775,7 @@
       <c r="V76" s="3"/>
       <c r="W76" s="2"/>
       <c r="X76" s="3"/>
-      <c r="Y76" s="3"/>
+      <c r="Y76" s="2"/>
       <c r="Z76" s="3"/>
       <c r="AA76" s="4"/>
       <c r="AB76" s="5"/>
@@ -6831,7 +6830,7 @@
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
-      <c r="F77" s="2"/>
+      <c r="F77" s="3"/>
       <c r="G77" s="3"/>
       <c r="H77" s="3"/>
       <c r="I77" s="2"/>
@@ -6839,7 +6838,7 @@
       <c r="K77" s="3"/>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
-      <c r="N77" s="2"/>
+      <c r="N77" s="13"/>
       <c r="O77" s="3"/>
       <c r="P77" s="3"/>
       <c r="Q77" s="3"/>
@@ -6905,15 +6904,15 @@
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
-      <c r="F78" s="3"/>
+      <c r="F78" s="2"/>
       <c r="G78" s="3"/>
       <c r="H78" s="3"/>
       <c r="I78" s="2"/>
       <c r="J78" s="2"/>
       <c r="K78" s="3"/>
-      <c r="L78" s="2"/>
+      <c r="L78" s="3"/>
       <c r="M78" s="2"/>
-      <c r="N78" s="13"/>
+      <c r="N78" s="2"/>
       <c r="O78" s="3"/>
       <c r="P78" s="3"/>
       <c r="Q78" s="3"/>
@@ -6922,9 +6921,9 @@
       <c r="T78" s="3"/>
       <c r="U78" s="3"/>
       <c r="V78" s="3"/>
-      <c r="W78" s="2"/>
+      <c r="W78" s="3"/>
       <c r="X78" s="3"/>
-      <c r="Y78" s="2"/>
+      <c r="Y78" s="13"/>
       <c r="Z78" s="3"/>
       <c r="AA78" s="4"/>
       <c r="AB78" s="5"/>
@@ -7059,10 +7058,10 @@
       <c r="I80" s="2"/>
       <c r="J80" s="2"/>
       <c r="K80" s="3"/>
-      <c r="L80" s="3"/>
+      <c r="L80" s="2"/>
       <c r="M80" s="2"/>
       <c r="N80" s="2"/>
-      <c r="O80" s="3"/>
+      <c r="O80" s="2"/>
       <c r="P80" s="3"/>
       <c r="Q80" s="3"/>
       <c r="R80" s="3"/>
@@ -7070,9 +7069,9 @@
       <c r="T80" s="3"/>
       <c r="U80" s="3"/>
       <c r="V80" s="3"/>
-      <c r="W80" s="3"/>
+      <c r="W80" s="2"/>
       <c r="X80" s="3"/>
-      <c r="Y80" s="13"/>
+      <c r="Y80" s="2"/>
       <c r="Z80" s="3"/>
       <c r="AA80" s="4"/>
       <c r="AB80" s="5"/>
@@ -7080,7 +7079,7 @@
       <c r="AD80" s="3"/>
       <c r="AE80" s="3"/>
       <c r="AF80" s="4"/>
-      <c r="AG80" s="3"/>
+      <c r="AG80" s="2"/>
       <c r="AH80" s="3"/>
       <c r="AI80" s="3"/>
       <c r="AJ80" s="3"/>
@@ -7088,7 +7087,7 @@
       <c r="AL80" s="3"/>
       <c r="AM80" s="3"/>
       <c r="AN80" s="3"/>
-      <c r="AO80" s="3"/>
+      <c r="AO80" s="2"/>
       <c r="AP80" s="3"/>
       <c r="AQ80" s="3"/>
       <c r="AR80" s="3"/>
@@ -7155,8 +7154,8 @@
       <c r="AE81" s="3"/>
       <c r="AF81" s="4"/>
       <c r="AG81" s="2"/>
-      <c r="AH81" s="3"/>
-      <c r="AI81" s="3"/>
+      <c r="AH81" s="2"/>
+      <c r="AI81" s="2"/>
       <c r="AJ81" s="3"/>
       <c r="AK81" s="3"/>
       <c r="AL81" s="3"/>
@@ -7207,7 +7206,7 @@
       <c r="I82" s="2"/>
       <c r="J82" s="2"/>
       <c r="K82" s="3"/>
-      <c r="L82" s="2"/>
+      <c r="L82" s="3"/>
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -7217,7 +7216,7 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-      <c r="V82" s="3"/>
+      <c r="V82" s="2"/>
       <c r="W82" s="2"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="2"/>
@@ -7230,7 +7229,7 @@
       <c r="AF82" s="4"/>
       <c r="AG82" s="2"/>
       <c r="AH82" s="2"/>
-      <c r="AI82" s="2"/>
+      <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
@@ -7281,17 +7280,17 @@
       <c r="I83" s="2"/>
       <c r="J83" s="2"/>
       <c r="K83" s="3"/>
-      <c r="L83" s="3"/>
+      <c r="L83" s="2"/>
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
-      <c r="P83" s="3"/>
+      <c r="P83" s="2"/>
       <c r="Q83" s="3"/>
       <c r="R83" s="3"/>
       <c r="S83" s="3"/>
       <c r="T83" s="3"/>
       <c r="U83" s="3"/>
-      <c r="V83" s="2"/>
+      <c r="V83" s="3"/>
       <c r="W83" s="2"/>
       <c r="X83" s="3"/>
       <c r="Y83" s="2"/>
@@ -7303,7 +7302,7 @@
       <c r="AE83" s="3"/>
       <c r="AF83" s="4"/>
       <c r="AG83" s="2"/>
-      <c r="AH83" s="2"/>
+      <c r="AH83" s="3"/>
       <c r="AI83" s="3"/>
       <c r="AJ83" s="3"/>
       <c r="AK83" s="3"/>
@@ -7359,13 +7358,13 @@
       <c r="M84" s="2"/>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
-      <c r="P84" s="2"/>
+      <c r="P84" s="3"/>
       <c r="Q84" s="3"/>
       <c r="R84" s="3"/>
       <c r="S84" s="3"/>
       <c r="T84" s="3"/>
       <c r="U84" s="3"/>
-      <c r="V84" s="3"/>
+      <c r="V84" s="2"/>
       <c r="W84" s="2"/>
       <c r="X84" s="3"/>
       <c r="Y84" s="2"/>
@@ -7377,7 +7376,7 @@
       <c r="AE84" s="3"/>
       <c r="AF84" s="4"/>
       <c r="AG84" s="2"/>
-      <c r="AH84" s="3"/>
+      <c r="AH84" s="2"/>
       <c r="AI84" s="3"/>
       <c r="AJ84" s="3"/>
       <c r="AK84" s="3"/>
@@ -7429,7 +7428,7 @@
       <c r="I85" s="2"/>
       <c r="J85" s="2"/>
       <c r="K85" s="3"/>
-      <c r="L85" s="2"/>
+      <c r="L85" s="3"/>
       <c r="M85" s="2"/>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -7451,7 +7450,7 @@
       <c r="AE85" s="3"/>
       <c r="AF85" s="4"/>
       <c r="AG85" s="2"/>
-      <c r="AH85" s="2"/>
+      <c r="AH85" s="3"/>
       <c r="AI85" s="3"/>
       <c r="AJ85" s="3"/>
       <c r="AK85" s="3"/>
@@ -7660,7 +7659,7 @@
       <c r="R88" s="3"/>
       <c r="S88" s="3"/>
       <c r="T88" s="3"/>
-      <c r="U88" s="3"/>
+      <c r="U88" s="2"/>
       <c r="V88" s="2"/>
       <c r="W88" s="2"/>
       <c r="X88" s="3"/>
@@ -7673,7 +7672,7 @@
       <c r="AE88" s="3"/>
       <c r="AF88" s="4"/>
       <c r="AG88" s="2"/>
-      <c r="AH88" s="3"/>
+      <c r="AH88" s="2"/>
       <c r="AI88" s="3"/>
       <c r="AJ88" s="3"/>
       <c r="AK88" s="3"/>
@@ -7728,25 +7727,25 @@
       <c r="L89" s="3"/>
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+      <c r="O89" s="3"/>
       <c r="P89" s="3"/>
       <c r="Q89" s="3"/>
       <c r="R89" s="3"/>
       <c r="S89" s="3"/>
       <c r="T89" s="3"/>
-      <c r="U89" s="2"/>
-      <c r="V89" s="2"/>
+      <c r="U89" s="3"/>
+      <c r="V89" s="3"/>
       <c r="W89" s="2"/>
       <c r="X89" s="3"/>
       <c r="Y89" s="2"/>
       <c r="Z89" s="3"/>
       <c r="AA89" s="4"/>
       <c r="AB89" s="5"/>
-      <c r="AC89" s="3"/>
+      <c r="AC89" s="2"/>
       <c r="AD89" s="3"/>
       <c r="AE89" s="3"/>
       <c r="AF89" s="4"/>
-      <c r="AG89" s="2"/>
+      <c r="AG89" s="3"/>
       <c r="AH89" s="2"/>
       <c r="AI89" s="3"/>
       <c r="AJ89" s="3"/>
@@ -7754,7 +7753,7 @@
       <c r="AL89" s="3"/>
       <c r="AM89" s="3"/>
       <c r="AN89" s="3"/>
-      <c r="AO89" s="2"/>
+      <c r="AO89" s="3"/>
       <c r="AP89" s="3"/>
       <c r="AQ89" s="3"/>
       <c r="AR89" s="3"/>
@@ -7821,7 +7820,7 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="4"/>
       <c r="AG90" s="3"/>
-      <c r="AH90" s="2"/>
+      <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
@@ -7895,7 +7894,7 @@
       <c r="AE91" s="3"/>
       <c r="AF91" s="4"/>
       <c r="AG91" s="3"/>
-      <c r="AH91" s="3"/>
+      <c r="AH91" s="2"/>
       <c r="AI91" s="3"/>
       <c r="AJ91" s="3"/>
       <c r="AK91" s="3"/>
@@ -7911,7 +7910,7 @@
       <c r="AU91" s="3"/>
       <c r="AV91" s="3"/>
       <c r="AW91" s="3"/>
-      <c r="AX91" s="3"/>
+      <c r="AX91" s="2"/>
       <c r="AY91" s="3"/>
       <c r="AZ91" s="3"/>
       <c r="BA91" s="3"/>
@@ -7965,7 +7964,7 @@
       <c r="AA92" s="4"/>
       <c r="AB92" s="5"/>
       <c r="AC92" s="2"/>
-      <c r="AD92" s="3"/>
+      <c r="AD92" s="2"/>
       <c r="AE92" s="3"/>
       <c r="AF92" s="4"/>
       <c r="AG92" s="3"/>
@@ -8024,7 +8023,7 @@
       <c r="L93" s="3"/>
       <c r="M93" s="2"/>
       <c r="N93" s="2"/>
-      <c r="O93" s="3"/>
+      <c r="O93" s="2"/>
       <c r="P93" s="3"/>
       <c r="Q93" s="3"/>
       <c r="R93" s="3"/>
@@ -8038,11 +8037,11 @@
       <c r="Z93" s="3"/>
       <c r="AA93" s="4"/>
       <c r="AB93" s="5"/>
-      <c r="AC93" s="2"/>
-      <c r="AD93" s="2"/>
+      <c r="AC93" s="3"/>
+      <c r="AD93" s="3"/>
       <c r="AE93" s="3"/>
       <c r="AF93" s="4"/>
-      <c r="AG93" s="3"/>
+      <c r="AG93" s="2"/>
       <c r="AH93" s="2"/>
       <c r="AI93" s="3"/>
       <c r="AJ93" s="3"/>
@@ -8050,7 +8049,7 @@
       <c r="AL93" s="3"/>
       <c r="AM93" s="3"/>
       <c r="AN93" s="3"/>
-      <c r="AO93" s="3"/>
+      <c r="AO93" s="2"/>
       <c r="AP93" s="3"/>
       <c r="AQ93" s="3"/>
       <c r="AR93" s="3"/>
@@ -8095,7 +8094,7 @@
       <c r="I94" s="2"/>
       <c r="J94" s="2"/>
       <c r="K94" s="3"/>
-      <c r="L94" s="3"/>
+      <c r="L94" s="2"/>
       <c r="M94" s="2"/>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -8133,7 +8132,7 @@
       <c r="AU94" s="3"/>
       <c r="AV94" s="3"/>
       <c r="AW94" s="3"/>
-      <c r="AX94" s="2"/>
+      <c r="AX94" s="3"/>
       <c r="AY94" s="3"/>
       <c r="AZ94" s="3"/>
       <c r="BA94" s="3"/>
@@ -8243,7 +8242,7 @@
       <c r="I96" s="2"/>
       <c r="J96" s="2"/>
       <c r="K96" s="3"/>
-      <c r="L96" s="2"/>
+      <c r="L96" s="3"/>
       <c r="M96" s="2"/>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -8264,7 +8263,7 @@
       <c r="AD96" s="3"/>
       <c r="AE96" s="3"/>
       <c r="AF96" s="4"/>
-      <c r="AG96" s="2"/>
+      <c r="AG96" s="3"/>
       <c r="AH96" s="2"/>
       <c r="AI96" s="3"/>
       <c r="AJ96" s="3"/>
@@ -8272,7 +8271,7 @@
       <c r="AL96" s="3"/>
       <c r="AM96" s="3"/>
       <c r="AN96" s="3"/>
-      <c r="AO96" s="2"/>
+      <c r="AO96" s="3"/>
       <c r="AP96" s="3"/>
       <c r="AQ96" s="3"/>
       <c r="AR96" s="3"/>
@@ -8317,7 +8316,7 @@
       <c r="I97" s="2"/>
       <c r="J97" s="2"/>
       <c r="K97" s="3"/>
-      <c r="L97" s="3"/>
+      <c r="L97" s="2"/>
       <c r="M97" s="2"/>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -8327,7 +8326,7 @@
       <c r="S97" s="3"/>
       <c r="T97" s="3"/>
       <c r="U97" s="3"/>
-      <c r="V97" s="3"/>
+      <c r="V97" s="2"/>
       <c r="W97" s="2"/>
       <c r="X97" s="3"/>
       <c r="Y97" s="2"/>
@@ -8338,15 +8337,15 @@
       <c r="AD97" s="3"/>
       <c r="AE97" s="3"/>
       <c r="AF97" s="4"/>
-      <c r="AG97" s="3"/>
-      <c r="AH97" s="2"/>
+      <c r="AG97" s="2"/>
+      <c r="AH97" s="3"/>
       <c r="AI97" s="3"/>
       <c r="AJ97" s="3"/>
       <c r="AK97" s="3"/>
       <c r="AL97" s="3"/>
       <c r="AM97" s="3"/>
       <c r="AN97" s="3"/>
-      <c r="AO97" s="3"/>
+      <c r="AO97" s="2"/>
       <c r="AP97" s="3"/>
       <c r="AQ97" s="3"/>
       <c r="AR97" s="3"/>
@@ -8391,17 +8390,17 @@
       <c r="I98" s="2"/>
       <c r="J98" s="2"/>
       <c r="K98" s="3"/>
-      <c r="L98" s="2"/>
+      <c r="L98" s="3"/>
       <c r="M98" s="2"/>
       <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
+      <c r="O98" s="3"/>
       <c r="P98" s="3"/>
       <c r="Q98" s="3"/>
       <c r="R98" s="3"/>
       <c r="S98" s="3"/>
       <c r="T98" s="3"/>
       <c r="U98" s="3"/>
-      <c r="V98" s="2"/>
+      <c r="V98" s="3"/>
       <c r="W98" s="2"/>
       <c r="X98" s="3"/>
       <c r="Y98" s="2"/>
@@ -8412,15 +8411,15 @@
       <c r="AD98" s="3"/>
       <c r="AE98" s="3"/>
       <c r="AF98" s="4"/>
-      <c r="AG98" s="2"/>
-      <c r="AH98" s="3"/>
+      <c r="AG98" s="3"/>
+      <c r="AH98" s="2"/>
       <c r="AI98" s="3"/>
       <c r="AJ98" s="3"/>
       <c r="AK98" s="3"/>
       <c r="AL98" s="3"/>
       <c r="AM98" s="3"/>
       <c r="AN98" s="3"/>
-      <c r="AO98" s="2"/>
+      <c r="AO98" s="3"/>
       <c r="AP98" s="3"/>
       <c r="AQ98" s="3"/>
       <c r="AR98" s="3"/>
@@ -8429,7 +8428,7 @@
       <c r="AU98" s="3"/>
       <c r="AV98" s="3"/>
       <c r="AW98" s="3"/>
-      <c r="AX98" s="3"/>
+      <c r="AX98" s="2"/>
       <c r="AY98" s="3"/>
       <c r="AZ98" s="3"/>
       <c r="BA98" s="3"/>
@@ -8465,10 +8464,10 @@
       <c r="I99" s="2"/>
       <c r="J99" s="2"/>
       <c r="K99" s="3"/>
-      <c r="L99" s="3"/>
+      <c r="L99" s="2"/>
       <c r="M99" s="2"/>
       <c r="N99" s="2"/>
-      <c r="O99" s="3"/>
+      <c r="O99" s="2"/>
       <c r="P99" s="3"/>
       <c r="Q99" s="3"/>
       <c r="R99" s="3"/>
@@ -8486,7 +8485,7 @@
       <c r="AD99" s="3"/>
       <c r="AE99" s="3"/>
       <c r="AF99" s="4"/>
-      <c r="AG99" s="3"/>
+      <c r="AG99" s="2"/>
       <c r="AH99" s="2"/>
       <c r="AI99" s="3"/>
       <c r="AJ99" s="3"/>
@@ -8494,7 +8493,7 @@
       <c r="AL99" s="3"/>
       <c r="AM99" s="3"/>
       <c r="AN99" s="3"/>
-      <c r="AO99" s="3"/>
+      <c r="AO99" s="2"/>
       <c r="AP99" s="3"/>
       <c r="AQ99" s="3"/>
       <c r="AR99" s="3"/>
@@ -8503,7 +8502,7 @@
       <c r="AU99" s="3"/>
       <c r="AV99" s="3"/>
       <c r="AW99" s="3"/>
-      <c r="AX99" s="2"/>
+      <c r="AX99" s="3"/>
       <c r="AY99" s="3"/>
       <c r="AZ99" s="3"/>
       <c r="BA99" s="3"/>
@@ -8550,7 +8549,7 @@
       <c r="T100" s="3"/>
       <c r="U100" s="3"/>
       <c r="V100" s="3"/>
-      <c r="W100" s="2"/>
+      <c r="W100" s="3"/>
       <c r="X100" s="3"/>
       <c r="Y100" s="2"/>
       <c r="Z100" s="3"/>
@@ -8772,7 +8771,7 @@
       <c r="T103" s="3"/>
       <c r="U103" s="3"/>
       <c r="V103" s="3"/>
-      <c r="W103" s="3"/>
+      <c r="W103" s="2"/>
       <c r="X103" s="3"/>
       <c r="Y103" s="2"/>
       <c r="Z103" s="3"/>
@@ -8834,11 +8833,11 @@
       <c r="H104" s="3"/>
       <c r="I104" s="2"/>
       <c r="J104" s="2"/>
-      <c r="K104" s="3"/>
+      <c r="K104" s="2"/>
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
       <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
+      <c r="O104" s="3"/>
       <c r="P104" s="3"/>
       <c r="Q104" s="3"/>
       <c r="R104" s="3"/>
@@ -8856,15 +8855,15 @@
       <c r="AD104" s="3"/>
       <c r="AE104" s="3"/>
       <c r="AF104" s="4"/>
-      <c r="AG104" s="2"/>
-      <c r="AH104" s="2"/>
+      <c r="AG104" s="3"/>
+      <c r="AH104" s="3"/>
       <c r="AI104" s="3"/>
       <c r="AJ104" s="3"/>
       <c r="AK104" s="3"/>
       <c r="AL104" s="3"/>
       <c r="AM104" s="3"/>
       <c r="AN104" s="3"/>
-      <c r="AO104" s="2"/>
+      <c r="AO104" s="3"/>
       <c r="AP104" s="3"/>
       <c r="AQ104" s="3"/>
       <c r="AR104" s="3"/>
@@ -8908,10 +8907,10 @@
       <c r="H105" s="3"/>
       <c r="I105" s="2"/>
       <c r="J105" s="2"/>
-      <c r="K105" s="2"/>
+      <c r="K105" s="3"/>
       <c r="L105" s="2"/>
-      <c r="M105" s="2"/>
-      <c r="N105" s="2"/>
+      <c r="M105" s="3"/>
+      <c r="N105" s="3"/>
       <c r="O105" s="3"/>
       <c r="P105" s="3"/>
       <c r="Q105" s="3"/>
@@ -8920,7 +8919,7 @@
       <c r="T105" s="3"/>
       <c r="U105" s="3"/>
       <c r="V105" s="3"/>
-      <c r="W105" s="2"/>
+      <c r="W105" s="3"/>
       <c r="X105" s="3"/>
       <c r="Y105" s="2"/>
       <c r="Z105" s="3"/>
@@ -8931,7 +8930,7 @@
       <c r="AE105" s="3"/>
       <c r="AF105" s="4"/>
       <c r="AG105" s="3"/>
-      <c r="AH105" s="3"/>
+      <c r="AH105" s="2"/>
       <c r="AI105" s="3"/>
       <c r="AJ105" s="3"/>
       <c r="AK105" s="3"/>
@@ -9131,7 +9130,7 @@
       <c r="I108" s="2"/>
       <c r="J108" s="2"/>
       <c r="K108" s="3"/>
-      <c r="L108" s="2"/>
+      <c r="L108" s="3"/>
       <c r="M108" s="3"/>
       <c r="N108" s="3"/>
       <c r="O108" s="3"/>
@@ -9205,7 +9204,7 @@
       <c r="I109" s="2"/>
       <c r="J109" s="2"/>
       <c r="K109" s="3"/>
-      <c r="L109" s="3"/>
+      <c r="L109" s="2"/>
       <c r="M109" s="3"/>
       <c r="N109" s="3"/>
       <c r="O109" s="3"/>
@@ -9274,7 +9273,7 @@
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
       <c r="F110" s="2"/>
-      <c r="G110" s="3"/>
+      <c r="G110" s="2"/>
       <c r="H110" s="3"/>
       <c r="I110" s="2"/>
       <c r="J110" s="2"/>
@@ -9292,7 +9291,7 @@
       <c r="V110" s="3"/>
       <c r="W110" s="3"/>
       <c r="X110" s="3"/>
-      <c r="Y110" s="2"/>
+      <c r="Y110" s="3"/>
       <c r="Z110" s="3"/>
       <c r="AA110" s="4"/>
       <c r="AB110" s="5"/>
@@ -9489,21 +9488,21 @@
       <c r="BS112" s="3"/>
       <c r="BT112" s="3"/>
     </row>
-    <row r="113" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="2"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
       <c r="F113" s="2"/>
-      <c r="G113" s="2"/>
+      <c r="G113" s="3"/>
       <c r="H113" s="3"/>
       <c r="I113" s="2"/>
       <c r="J113" s="2"/>
       <c r="K113" s="3"/>
       <c r="L113" s="2"/>
-      <c r="M113" s="3"/>
-      <c r="N113" s="3"/>
+      <c r="M113" s="2"/>
+      <c r="N113" s="2"/>
       <c r="O113" s="3"/>
       <c r="P113" s="3"/>
       <c r="Q113" s="3"/>
@@ -9523,7 +9522,7 @@
       <c r="AE113" s="3"/>
       <c r="AF113" s="4"/>
       <c r="AG113" s="3"/>
-      <c r="AH113" s="2"/>
+      <c r="AH113" s="3"/>
       <c r="AI113" s="3"/>
       <c r="AJ113" s="3"/>
       <c r="AK113" s="3"/>
@@ -9579,16 +9578,16 @@
       <c r="M114" s="2"/>
       <c r="N114" s="2"/>
       <c r="O114" s="3"/>
-      <c r="P114" s="3"/>
+      <c r="P114" s="2"/>
       <c r="Q114" s="3"/>
       <c r="R114" s="3"/>
       <c r="S114" s="3"/>
       <c r="T114" s="3"/>
       <c r="U114" s="3"/>
       <c r="V114" s="3"/>
-      <c r="W114" s="3"/>
+      <c r="W114" s="2"/>
       <c r="X114" s="3"/>
-      <c r="Y114" s="3"/>
+      <c r="Y114" s="2"/>
       <c r="Z114" s="3"/>
       <c r="AA114" s="4"/>
       <c r="AB114" s="5"/>
@@ -9648,21 +9647,21 @@
       <c r="H115" s="3"/>
       <c r="I115" s="2"/>
       <c r="J115" s="2"/>
-      <c r="K115" s="3"/>
+      <c r="K115" s="2"/>
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
       <c r="N115" s="2"/>
       <c r="O115" s="3"/>
-      <c r="P115" s="2"/>
+      <c r="P115" s="3"/>
       <c r="Q115" s="3"/>
       <c r="R115" s="3"/>
       <c r="S115" s="3"/>
       <c r="T115" s="3"/>
       <c r="U115" s="3"/>
       <c r="V115" s="3"/>
-      <c r="W115" s="2"/>
+      <c r="W115" s="3"/>
       <c r="X115" s="3"/>
-      <c r="Y115" s="2"/>
+      <c r="Y115" s="3"/>
       <c r="Z115" s="3"/>
       <c r="AA115" s="4"/>
       <c r="AB115" s="5"/>
@@ -9683,7 +9682,7 @@
       <c r="AQ115" s="3"/>
       <c r="AR115" s="3"/>
       <c r="AS115" s="3"/>
-      <c r="AT115" s="3"/>
+      <c r="AT115" s="2"/>
       <c r="AU115" s="3"/>
       <c r="AV115" s="3"/>
       <c r="AW115" s="3"/>
@@ -9712,7 +9711,7 @@
       <c r="BT115" s="3"/>
     </row>
     <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="2"/>
+      <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
@@ -9722,7 +9721,7 @@
       <c r="H116" s="3"/>
       <c r="I116" s="2"/>
       <c r="J116" s="2"/>
-      <c r="K116" s="2"/>
+      <c r="K116" s="3"/>
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
       <c r="N116" s="2"/>
@@ -9736,7 +9735,7 @@
       <c r="V116" s="3"/>
       <c r="W116" s="3"/>
       <c r="X116" s="3"/>
-      <c r="Y116" s="3"/>
+      <c r="Y116" s="14"/>
       <c r="Z116" s="3"/>
       <c r="AA116" s="4"/>
       <c r="AB116" s="5"/>
@@ -9757,7 +9756,7 @@
       <c r="AQ116" s="3"/>
       <c r="AR116" s="3"/>
       <c r="AS116" s="3"/>
-      <c r="AT116" s="2"/>
+      <c r="AT116" s="3"/>
       <c r="AU116" s="3"/>
       <c r="AV116" s="3"/>
       <c r="AW116" s="3"/>
@@ -9786,7 +9785,7 @@
       <c r="BT116" s="3"/>
     </row>
     <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="3"/>
+      <c r="A117" s="2"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
@@ -9810,7 +9809,7 @@
       <c r="V117" s="3"/>
       <c r="W117" s="3"/>
       <c r="X117" s="3"/>
-      <c r="Y117" s="14"/>
+      <c r="Y117" s="3"/>
       <c r="Z117" s="3"/>
       <c r="AA117" s="4"/>
       <c r="AB117" s="5"/>
@@ -9884,7 +9883,7 @@
       <c r="V118" s="3"/>
       <c r="W118" s="3"/>
       <c r="X118" s="3"/>
-      <c r="Y118" s="3"/>
+      <c r="Y118" s="2"/>
       <c r="Z118" s="3"/>
       <c r="AA118" s="4"/>
       <c r="AB118" s="5"/>
@@ -9956,7 +9955,7 @@
       <c r="T119" s="3"/>
       <c r="U119" s="3"/>
       <c r="V119" s="3"/>
-      <c r="W119" s="3"/>
+      <c r="W119" s="2"/>
       <c r="X119" s="3"/>
       <c r="Y119" s="2"/>
       <c r="Z119" s="3"/>
@@ -10014,7 +10013,7 @@
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
       <c r="F120" s="2"/>
-      <c r="G120" s="3"/>
+      <c r="G120" s="2"/>
       <c r="H120" s="3"/>
       <c r="I120" s="2"/>
       <c r="J120" s="2"/>
@@ -10030,7 +10029,7 @@
       <c r="T120" s="3"/>
       <c r="U120" s="3"/>
       <c r="V120" s="3"/>
-      <c r="W120" s="2"/>
+      <c r="W120" s="3"/>
       <c r="X120" s="3"/>
       <c r="Y120" s="2"/>
       <c r="Z120" s="3"/>
@@ -10088,7 +10087,7 @@
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
       <c r="F121" s="2"/>
-      <c r="G121" s="2"/>
+      <c r="G121" s="3"/>
       <c r="H121" s="3"/>
       <c r="I121" s="2"/>
       <c r="J121" s="2"/>
@@ -10104,7 +10103,7 @@
       <c r="T121" s="3"/>
       <c r="U121" s="3"/>
       <c r="V121" s="3"/>
-      <c r="W121" s="3"/>
+      <c r="W121" s="2"/>
       <c r="X121" s="3"/>
       <c r="Y121" s="2"/>
       <c r="Z121" s="3"/>
@@ -10271,7 +10270,7 @@
       <c r="AM123" s="3"/>
       <c r="AN123" s="3"/>
       <c r="AO123" s="3"/>
-      <c r="AP123" s="3"/>
+      <c r="AP123" s="2"/>
       <c r="AQ123" s="3"/>
       <c r="AR123" s="3"/>
       <c r="AS123" s="3"/>
@@ -10309,8 +10308,8 @@
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
-      <c r="F124" s="2"/>
-      <c r="G124" s="3"/>
+      <c r="F124" s="3"/>
+      <c r="G124" s="2"/>
       <c r="H124" s="3"/>
       <c r="I124" s="2"/>
       <c r="J124" s="2"/>
@@ -10325,10 +10324,10 @@
       <c r="S124" s="3"/>
       <c r="T124" s="3"/>
       <c r="U124" s="3"/>
-      <c r="V124" s="3"/>
-      <c r="W124" s="2"/>
+      <c r="V124" s="2"/>
+      <c r="W124" s="3"/>
       <c r="X124" s="3"/>
-      <c r="Y124" s="2"/>
+      <c r="Y124" s="3"/>
       <c r="Z124" s="3"/>
       <c r="AA124" s="4"/>
       <c r="AB124" s="5"/>
@@ -10345,10 +10344,10 @@
       <c r="AM124" s="3"/>
       <c r="AN124" s="3"/>
       <c r="AO124" s="3"/>
-      <c r="AP124" s="2"/>
+      <c r="AP124" s="3"/>
       <c r="AQ124" s="3"/>
-      <c r="AR124" s="3"/>
-      <c r="AS124" s="3"/>
+      <c r="AR124" s="2"/>
+      <c r="AS124" s="2"/>
       <c r="AT124" s="3"/>
       <c r="AU124" s="3"/>
       <c r="AV124" s="3"/>
@@ -10383,8 +10382,8 @@
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
-      <c r="F125" s="3"/>
-      <c r="G125" s="2"/>
+      <c r="F125" s="2"/>
+      <c r="G125" s="3"/>
       <c r="H125" s="3"/>
       <c r="I125" s="2"/>
       <c r="J125" s="2"/>
@@ -10399,7 +10398,7 @@
       <c r="S125" s="3"/>
       <c r="T125" s="3"/>
       <c r="U125" s="3"/>
-      <c r="V125" s="2"/>
+      <c r="V125" s="3"/>
       <c r="W125" s="3"/>
       <c r="X125" s="3"/>
       <c r="Y125" s="3"/>
@@ -10421,8 +10420,8 @@
       <c r="AO125" s="3"/>
       <c r="AP125" s="3"/>
       <c r="AQ125" s="3"/>
-      <c r="AR125" s="2"/>
-      <c r="AS125" s="2"/>
+      <c r="AR125" s="3"/>
+      <c r="AS125" s="3"/>
       <c r="AT125" s="3"/>
       <c r="AU125" s="3"/>
       <c r="AV125" s="3"/>
@@ -10532,7 +10531,7 @@
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
       <c r="F127" s="2"/>
-      <c r="G127" s="3"/>
+      <c r="G127" s="2"/>
       <c r="H127" s="3"/>
       <c r="I127" s="2"/>
       <c r="J127" s="2"/>
@@ -10606,7 +10605,7 @@
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
       <c r="F128" s="2"/>
-      <c r="G128" s="2"/>
+      <c r="G128" s="3"/>
       <c r="H128" s="3"/>
       <c r="I128" s="2"/>
       <c r="J128" s="2"/>
@@ -10622,9 +10621,9 @@
       <c r="T128" s="3"/>
       <c r="U128" s="3"/>
       <c r="V128" s="3"/>
-      <c r="W128" s="3"/>
+      <c r="W128" s="2"/>
       <c r="X128" s="3"/>
-      <c r="Y128" s="3"/>
+      <c r="Y128" s="2"/>
       <c r="Z128" s="3"/>
       <c r="AA128" s="4"/>
       <c r="AB128" s="5"/>
@@ -10644,7 +10643,7 @@
       <c r="AP128" s="3"/>
       <c r="AQ128" s="3"/>
       <c r="AR128" s="3"/>
-      <c r="AS128" s="3"/>
+      <c r="AS128" s="2"/>
       <c r="AT128" s="3"/>
       <c r="AU128" s="3"/>
       <c r="AV128" s="3"/>
@@ -10695,7 +10694,7 @@
       <c r="S129" s="3"/>
       <c r="T129" s="3"/>
       <c r="U129" s="3"/>
-      <c r="V129" s="3"/>
+      <c r="V129" s="2"/>
       <c r="W129" s="2"/>
       <c r="X129" s="3"/>
       <c r="Y129" s="2"/>
@@ -10758,7 +10757,7 @@
       <c r="H130" s="3"/>
       <c r="I130" s="2"/>
       <c r="J130" s="2"/>
-      <c r="K130" s="3"/>
+      <c r="K130" s="2"/>
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
       <c r="N130" s="2"/>
@@ -10769,7 +10768,7 @@
       <c r="S130" s="3"/>
       <c r="T130" s="3"/>
       <c r="U130" s="3"/>
-      <c r="V130" s="2"/>
+      <c r="V130" s="3"/>
       <c r="W130" s="2"/>
       <c r="X130" s="3"/>
       <c r="Y130" s="2"/>
@@ -10781,7 +10780,7 @@
       <c r="AE130" s="3"/>
       <c r="AF130" s="4"/>
       <c r="AG130" s="3"/>
-      <c r="AH130" s="3"/>
+      <c r="AH130" s="2"/>
       <c r="AI130" s="3"/>
       <c r="AJ130" s="3"/>
       <c r="AK130" s="3"/>
@@ -10792,8 +10791,8 @@
       <c r="AP130" s="3"/>
       <c r="AQ130" s="3"/>
       <c r="AR130" s="3"/>
-      <c r="AS130" s="2"/>
-      <c r="AT130" s="3"/>
+      <c r="AS130" s="3"/>
+      <c r="AT130" s="2"/>
       <c r="AU130" s="3"/>
       <c r="AV130" s="3"/>
       <c r="AW130" s="3"/>
@@ -10844,7 +10843,7 @@
       <c r="T131" s="3"/>
       <c r="U131" s="3"/>
       <c r="V131" s="3"/>
-      <c r="W131" s="2"/>
+      <c r="W131" s="3"/>
       <c r="X131" s="3"/>
       <c r="Y131" s="2"/>
       <c r="Z131" s="3"/>
@@ -10906,11 +10905,11 @@
       <c r="H132" s="3"/>
       <c r="I132" s="2"/>
       <c r="J132" s="2"/>
-      <c r="K132" s="2"/>
-      <c r="L132" s="2"/>
+      <c r="K132" s="3"/>
+      <c r="L132" s="3"/>
       <c r="M132" s="2"/>
       <c r="N132" s="2"/>
-      <c r="O132" s="3"/>
+      <c r="O132" s="2"/>
       <c r="P132" s="3"/>
       <c r="Q132" s="3"/>
       <c r="R132" s="3"/>
@@ -10918,7 +10917,7 @@
       <c r="T132" s="3"/>
       <c r="U132" s="3"/>
       <c r="V132" s="3"/>
-      <c r="W132" s="3"/>
+      <c r="W132" s="2"/>
       <c r="X132" s="3"/>
       <c r="Y132" s="2"/>
       <c r="Z132" s="3"/>
@@ -10929,7 +10928,7 @@
       <c r="AE132" s="3"/>
       <c r="AF132" s="4"/>
       <c r="AG132" s="3"/>
-      <c r="AH132" s="2"/>
+      <c r="AH132" s="3"/>
       <c r="AI132" s="3"/>
       <c r="AJ132" s="3"/>
       <c r="AK132" s="3"/>
@@ -10941,7 +10940,7 @@
       <c r="AQ132" s="3"/>
       <c r="AR132" s="3"/>
       <c r="AS132" s="3"/>
-      <c r="AT132" s="2"/>
+      <c r="AT132" s="3"/>
       <c r="AU132" s="3"/>
       <c r="AV132" s="3"/>
       <c r="AW132" s="3"/>
@@ -10969,7 +10968,7 @@
       <c r="BS132" s="3"/>
       <c r="BT132" s="3"/>
     </row>
-    <row r="133" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="2"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -10984,7 +10983,7 @@
       <c r="L133" s="3"/>
       <c r="M133" s="2"/>
       <c r="N133" s="2"/>
-      <c r="O133" s="2"/>
+      <c r="O133" s="3"/>
       <c r="P133" s="3"/>
       <c r="Q133" s="3"/>
       <c r="R133" s="3"/>
@@ -10998,20 +10997,20 @@
       <c r="Z133" s="3"/>
       <c r="AA133" s="4"/>
       <c r="AB133" s="5"/>
-      <c r="AC133" s="3"/>
-      <c r="AD133" s="3"/>
+      <c r="AC133" s="2"/>
+      <c r="AD133" s="2"/>
       <c r="AE133" s="3"/>
       <c r="AF133" s="4"/>
       <c r="AG133" s="3"/>
-      <c r="AH133" s="3"/>
+      <c r="AH133" s="2"/>
       <c r="AI133" s="3"/>
       <c r="AJ133" s="3"/>
       <c r="AK133" s="3"/>
       <c r="AL133" s="3"/>
       <c r="AM133" s="3"/>
       <c r="AN133" s="3"/>
-      <c r="AO133" s="3"/>
-      <c r="AP133" s="3"/>
+      <c r="AO133" s="2"/>
+      <c r="AP133" s="2"/>
       <c r="AQ133" s="3"/>
       <c r="AR133" s="3"/>
       <c r="AS133" s="3"/>
@@ -11019,7 +11018,7 @@
       <c r="AU133" s="3"/>
       <c r="AV133" s="3"/>
       <c r="AW133" s="3"/>
-      <c r="AX133" s="3"/>
+      <c r="AX133" s="2"/>
       <c r="AY133" s="3"/>
       <c r="AZ133" s="3"/>
       <c r="BA133" s="3"/>
@@ -11055,7 +11054,7 @@
       <c r="I134" s="2"/>
       <c r="J134" s="2"/>
       <c r="K134" s="3"/>
-      <c r="L134" s="3"/>
+      <c r="L134" s="2"/>
       <c r="M134" s="2"/>
       <c r="N134" s="2"/>
       <c r="O134" s="3"/>
@@ -11066,14 +11065,14 @@
       <c r="T134" s="3"/>
       <c r="U134" s="3"/>
       <c r="V134" s="3"/>
-      <c r="W134" s="2"/>
+      <c r="W134" s="3"/>
       <c r="X134" s="3"/>
-      <c r="Y134" s="2"/>
+      <c r="Y134" s="3"/>
       <c r="Z134" s="3"/>
       <c r="AA134" s="4"/>
       <c r="AB134" s="5"/>
       <c r="AC134" s="2"/>
-      <c r="AD134" s="2"/>
+      <c r="AD134" s="3"/>
       <c r="AE134" s="3"/>
       <c r="AF134" s="4"/>
       <c r="AG134" s="3"/>
@@ -11084,8 +11083,8 @@
       <c r="AL134" s="3"/>
       <c r="AM134" s="3"/>
       <c r="AN134" s="3"/>
-      <c r="AO134" s="2"/>
-      <c r="AP134" s="2"/>
+      <c r="AO134" s="3"/>
+      <c r="AP134" s="3"/>
       <c r="AQ134" s="3"/>
       <c r="AR134" s="3"/>
       <c r="AS134" s="3"/>
@@ -11093,7 +11092,7 @@
       <c r="AU134" s="3"/>
       <c r="AV134" s="3"/>
       <c r="AW134" s="3"/>
-      <c r="AX134" s="2"/>
+      <c r="AX134" s="3"/>
       <c r="AY134" s="3"/>
       <c r="AZ134" s="3"/>
       <c r="BA134" s="3"/>
@@ -11204,12 +11203,12 @@
       <c r="J136" s="2"/>
       <c r="K136" s="3"/>
       <c r="L136" s="2"/>
-      <c r="M136" s="2"/>
-      <c r="N136" s="2"/>
+      <c r="M136" s="3"/>
+      <c r="N136" s="3"/>
       <c r="O136" s="3"/>
       <c r="P136" s="3"/>
       <c r="Q136" s="3"/>
-      <c r="R136" s="3"/>
+      <c r="R136" s="2"/>
       <c r="S136" s="3"/>
       <c r="T136" s="3"/>
       <c r="U136" s="3"/>
@@ -11573,29 +11572,29 @@
       <c r="I141" s="2"/>
       <c r="J141" s="2"/>
       <c r="K141" s="3"/>
-      <c r="L141" s="2"/>
-      <c r="M141" s="3"/>
-      <c r="N141" s="3"/>
+      <c r="L141" s="3"/>
+      <c r="M141" s="2"/>
+      <c r="N141" s="2"/>
       <c r="O141" s="3"/>
       <c r="P141" s="3"/>
       <c r="Q141" s="3"/>
-      <c r="R141" s="2"/>
+      <c r="R141" s="3"/>
       <c r="S141" s="3"/>
       <c r="T141" s="3"/>
       <c r="U141" s="3"/>
       <c r="V141" s="3"/>
-      <c r="W141" s="3"/>
+      <c r="W141" s="2"/>
       <c r="X141" s="3"/>
       <c r="Y141" s="3"/>
       <c r="Z141" s="3"/>
       <c r="AA141" s="4"/>
       <c r="AB141" s="5"/>
-      <c r="AC141" s="2"/>
+      <c r="AC141" s="3"/>
       <c r="AD141" s="3"/>
       <c r="AE141" s="3"/>
       <c r="AF141" s="4"/>
       <c r="AG141" s="3"/>
-      <c r="AH141" s="2"/>
+      <c r="AH141" s="3"/>
       <c r="AI141" s="3"/>
       <c r="AJ141" s="3"/>
       <c r="AK141" s="3"/>
@@ -11647,29 +11646,29 @@
       <c r="I142" s="2"/>
       <c r="J142" s="2"/>
       <c r="K142" s="3"/>
-      <c r="L142" s="3"/>
-      <c r="M142" s="2"/>
-      <c r="N142" s="2"/>
+      <c r="L142" s="2"/>
+      <c r="M142" s="3"/>
+      <c r="N142" s="3"/>
       <c r="O142" s="3"/>
       <c r="P142" s="3"/>
       <c r="Q142" s="3"/>
-      <c r="R142" s="3"/>
+      <c r="R142" s="2"/>
       <c r="S142" s="3"/>
       <c r="T142" s="3"/>
       <c r="U142" s="3"/>
       <c r="V142" s="3"/>
-      <c r="W142" s="2"/>
+      <c r="W142" s="3"/>
       <c r="X142" s="3"/>
       <c r="Y142" s="3"/>
       <c r="Z142" s="3"/>
       <c r="AA142" s="4"/>
       <c r="AB142" s="5"/>
-      <c r="AC142" s="3"/>
+      <c r="AC142" s="2"/>
       <c r="AD142" s="3"/>
       <c r="AE142" s="3"/>
       <c r="AF142" s="4"/>
       <c r="AG142" s="3"/>
-      <c r="AH142" s="3"/>
+      <c r="AH142" s="2"/>
       <c r="AI142" s="3"/>
       <c r="AJ142" s="3"/>
       <c r="AK142" s="3"/>
@@ -11679,7 +11678,7 @@
       <c r="AO142" s="3"/>
       <c r="AP142" s="3"/>
       <c r="AQ142" s="3"/>
-      <c r="AR142" s="3"/>
+      <c r="AR142" s="2"/>
       <c r="AS142" s="3"/>
       <c r="AT142" s="3"/>
       <c r="AU142" s="3"/>
@@ -11880,9 +11879,9 @@
       <c r="T145" s="3"/>
       <c r="U145" s="3"/>
       <c r="V145" s="3"/>
-      <c r="W145" s="3"/>
+      <c r="W145" s="2"/>
       <c r="X145" s="3"/>
-      <c r="Y145" s="3"/>
+      <c r="Y145" s="2"/>
       <c r="Z145" s="3"/>
       <c r="AA145" s="4"/>
       <c r="AB145" s="5"/>
@@ -11901,7 +11900,7 @@
       <c r="AO145" s="3"/>
       <c r="AP145" s="3"/>
       <c r="AQ145" s="3"/>
-      <c r="AR145" s="2"/>
+      <c r="AR145" s="3"/>
       <c r="AS145" s="3"/>
       <c r="AT145" s="3"/>
       <c r="AU145" s="3"/>
@@ -12017,7 +12016,7 @@
       <c r="I147" s="2"/>
       <c r="J147" s="2"/>
       <c r="K147" s="3"/>
-      <c r="L147" s="2"/>
+      <c r="L147" s="3"/>
       <c r="M147" s="3"/>
       <c r="N147" s="3"/>
       <c r="O147" s="3"/>
@@ -12165,29 +12164,29 @@
       <c r="I149" s="2"/>
       <c r="J149" s="2"/>
       <c r="K149" s="3"/>
-      <c r="L149" s="3"/>
-      <c r="M149" s="3"/>
-      <c r="N149" s="3"/>
+      <c r="L149" s="2"/>
+      <c r="M149" s="2"/>
+      <c r="N149" s="2"/>
       <c r="O149" s="3"/>
       <c r="P149" s="3"/>
       <c r="Q149" s="3"/>
-      <c r="R149" s="2"/>
+      <c r="R149" s="3"/>
       <c r="S149" s="3"/>
       <c r="T149" s="3"/>
       <c r="U149" s="3"/>
       <c r="V149" s="3"/>
-      <c r="W149" s="2"/>
+      <c r="W149" s="3"/>
       <c r="X149" s="3"/>
       <c r="Y149" s="2"/>
       <c r="Z149" s="3"/>
       <c r="AA149" s="4"/>
       <c r="AB149" s="5"/>
-      <c r="AC149" s="2"/>
+      <c r="AC149" s="3"/>
       <c r="AD149" s="3"/>
       <c r="AE149" s="3"/>
       <c r="AF149" s="4"/>
       <c r="AG149" s="3"/>
-      <c r="AH149" s="2"/>
+      <c r="AH149" s="3"/>
       <c r="AI149" s="3"/>
       <c r="AJ149" s="3"/>
       <c r="AK149" s="3"/>
@@ -12234,7 +12233,7 @@
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
       <c r="F150" s="2"/>
-      <c r="G150" s="3"/>
+      <c r="G150" s="2"/>
       <c r="H150" s="3"/>
       <c r="I150" s="2"/>
       <c r="J150" s="2"/>
@@ -12256,7 +12255,7 @@
       <c r="Z150" s="3"/>
       <c r="AA150" s="4"/>
       <c r="AB150" s="5"/>
-      <c r="AC150" s="3"/>
+      <c r="AC150" s="2"/>
       <c r="AD150" s="3"/>
       <c r="AE150" s="3"/>
       <c r="AF150" s="4"/>
@@ -12324,7 +12323,7 @@
       <c r="T151" s="3"/>
       <c r="U151" s="3"/>
       <c r="V151" s="3"/>
-      <c r="W151" s="3"/>
+      <c r="W151" s="2"/>
       <c r="X151" s="3"/>
       <c r="Y151" s="2"/>
       <c r="Z151" s="3"/>
@@ -12826,7 +12825,7 @@
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
       <c r="F158" s="2"/>
-      <c r="G158" s="2"/>
+      <c r="G158" s="3"/>
       <c r="H158" s="3"/>
       <c r="I158" s="2"/>
       <c r="J158" s="2"/>
@@ -12848,7 +12847,7 @@
       <c r="Z158" s="3"/>
       <c r="AA158" s="4"/>
       <c r="AB158" s="5"/>
-      <c r="AC158" s="2"/>
+      <c r="AC158" s="3"/>
       <c r="AD158" s="3"/>
       <c r="AE158" s="3"/>
       <c r="AF158" s="4"/>
@@ -12918,7 +12917,7 @@
       <c r="V159" s="3"/>
       <c r="W159" s="2"/>
       <c r="X159" s="3"/>
-      <c r="Y159" s="2"/>
+      <c r="Y159" s="3"/>
       <c r="Z159" s="3"/>
       <c r="AA159" s="4"/>
       <c r="AB159" s="5"/>
@@ -13053,7 +13052,7 @@
       <c r="I161" s="2"/>
       <c r="J161" s="2"/>
       <c r="K161" s="3"/>
-      <c r="L161" s="2"/>
+      <c r="L161" s="3"/>
       <c r="M161" s="2"/>
       <c r="N161" s="2"/>
       <c r="O161" s="3"/>
@@ -13064,7 +13063,7 @@
       <c r="T161" s="3"/>
       <c r="U161" s="3"/>
       <c r="V161" s="3"/>
-      <c r="W161" s="2"/>
+      <c r="W161" s="3"/>
       <c r="X161" s="3"/>
       <c r="Y161" s="3"/>
       <c r="Z161" s="3"/>
@@ -13075,7 +13074,7 @@
       <c r="AE161" s="3"/>
       <c r="AF161" s="4"/>
       <c r="AG161" s="3"/>
-      <c r="AH161" s="3"/>
+      <c r="AH161" s="2"/>
       <c r="AI161" s="3"/>
       <c r="AJ161" s="3"/>
       <c r="AK161" s="3"/>
@@ -13122,14 +13121,14 @@
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
       <c r="F162" s="2"/>
-      <c r="G162" s="3"/>
+      <c r="G162" s="2"/>
       <c r="H162" s="3"/>
       <c r="I162" s="2"/>
       <c r="J162" s="2"/>
       <c r="K162" s="3"/>
-      <c r="L162" s="3"/>
-      <c r="M162" s="2"/>
-      <c r="N162" s="2"/>
+      <c r="L162" s="2"/>
+      <c r="M162" s="3"/>
+      <c r="N162" s="3"/>
       <c r="O162" s="3"/>
       <c r="P162" s="3"/>
       <c r="Q162" s="3"/>
@@ -13140,11 +13139,11 @@
       <c r="V162" s="3"/>
       <c r="W162" s="3"/>
       <c r="X162" s="3"/>
-      <c r="Y162" s="3"/>
+      <c r="Y162" s="2"/>
       <c r="Z162" s="3"/>
       <c r="AA162" s="4"/>
       <c r="AB162" s="5"/>
-      <c r="AC162" s="3"/>
+      <c r="AC162" s="2"/>
       <c r="AD162" s="3"/>
       <c r="AE162" s="3"/>
       <c r="AF162" s="4"/>
@@ -13214,7 +13213,7 @@
       <c r="V163" s="3"/>
       <c r="W163" s="3"/>
       <c r="X163" s="3"/>
-      <c r="Y163" s="2"/>
+      <c r="Y163" s="15"/>
       <c r="Z163" s="3"/>
       <c r="AA163" s="4"/>
       <c r="AB163" s="5"/>
@@ -13223,7 +13222,7 @@
       <c r="AE163" s="3"/>
       <c r="AF163" s="4"/>
       <c r="AG163" s="3"/>
-      <c r="AH163" s="2"/>
+      <c r="AH163" s="3"/>
       <c r="AI163" s="3"/>
       <c r="AJ163" s="3"/>
       <c r="AK163" s="3"/>
@@ -13270,7 +13269,7 @@
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
       <c r="F164" s="2"/>
-      <c r="G164" s="2"/>
+      <c r="G164" s="3"/>
       <c r="H164" s="3"/>
       <c r="I164" s="2"/>
       <c r="J164" s="2"/>
@@ -13288,7 +13287,7 @@
       <c r="V164" s="3"/>
       <c r="W164" s="3"/>
       <c r="X164" s="3"/>
-      <c r="Y164" s="15"/>
+      <c r="Y164" s="2"/>
       <c r="Z164" s="3"/>
       <c r="AA164" s="4"/>
       <c r="AB164" s="5"/>
@@ -13349,7 +13348,7 @@
       <c r="I165" s="2"/>
       <c r="J165" s="2"/>
       <c r="K165" s="3"/>
-      <c r="L165" s="2"/>
+      <c r="L165" s="3"/>
       <c r="M165" s="3"/>
       <c r="N165" s="3"/>
       <c r="O165" s="3"/>
@@ -13423,7 +13422,7 @@
       <c r="I166" s="2"/>
       <c r="J166" s="2"/>
       <c r="K166" s="3"/>
-      <c r="L166" s="3"/>
+      <c r="L166" s="2"/>
       <c r="M166" s="3"/>
       <c r="N166" s="3"/>
       <c r="O166" s="3"/>
@@ -13492,7 +13491,7 @@
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
       <c r="F167" s="2"/>
-      <c r="G167" s="3"/>
+      <c r="G167" s="2"/>
       <c r="H167" s="3"/>
       <c r="I167" s="2"/>
       <c r="J167" s="2"/>
@@ -13503,12 +13502,12 @@
       <c r="O167" s="3"/>
       <c r="P167" s="3"/>
       <c r="Q167" s="3"/>
-      <c r="R167" s="3"/>
+      <c r="R167" s="2"/>
       <c r="S167" s="3"/>
       <c r="T167" s="3"/>
       <c r="U167" s="3"/>
       <c r="V167" s="3"/>
-      <c r="W167" s="3"/>
+      <c r="W167" s="2"/>
       <c r="X167" s="3"/>
       <c r="Y167" s="2"/>
       <c r="Z167" s="3"/>
@@ -13566,18 +13565,18 @@
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
       <c r="F168" s="2"/>
-      <c r="G168" s="2"/>
+      <c r="G168" s="3"/>
       <c r="H168" s="3"/>
       <c r="I168" s="2"/>
       <c r="J168" s="2"/>
       <c r="K168" s="3"/>
-      <c r="L168" s="2"/>
-      <c r="M168" s="3"/>
-      <c r="N168" s="3"/>
+      <c r="L168" s="3"/>
+      <c r="M168" s="2"/>
+      <c r="N168" s="2"/>
       <c r="O168" s="3"/>
       <c r="P168" s="3"/>
       <c r="Q168" s="3"/>
-      <c r="R168" s="2"/>
+      <c r="R168" s="3"/>
       <c r="S168" s="3"/>
       <c r="T168" s="3"/>
       <c r="U168" s="3"/>
@@ -13600,12 +13599,12 @@
       <c r="AL168" s="3"/>
       <c r="AM168" s="3"/>
       <c r="AN168" s="3"/>
-      <c r="AO168" s="3"/>
+      <c r="AO168" s="2"/>
       <c r="AP168" s="3"/>
       <c r="AQ168" s="3"/>
       <c r="AR168" s="3"/>
       <c r="AS168" s="3"/>
-      <c r="AT168" s="3"/>
+      <c r="AT168" s="2"/>
       <c r="AU168" s="3"/>
       <c r="AV168" s="3"/>
       <c r="AW168" s="3"/>
@@ -13640,18 +13639,18 @@
       <c r="D169" s="3"/>
       <c r="E169" s="3"/>
       <c r="F169" s="2"/>
-      <c r="G169" s="3"/>
+      <c r="G169" s="2"/>
       <c r="H169" s="3"/>
       <c r="I169" s="2"/>
       <c r="J169" s="2"/>
       <c r="K169" s="3"/>
-      <c r="L169" s="3"/>
-      <c r="M169" s="2"/>
-      <c r="N169" s="2"/>
+      <c r="L169" s="2"/>
+      <c r="M169" s="3"/>
+      <c r="N169" s="3"/>
       <c r="O169" s="3"/>
       <c r="P169" s="3"/>
       <c r="Q169" s="3"/>
-      <c r="R169" s="3"/>
+      <c r="R169" s="2"/>
       <c r="S169" s="3"/>
       <c r="T169" s="3"/>
       <c r="U169" s="3"/>
@@ -13674,12 +13673,12 @@
       <c r="AL169" s="3"/>
       <c r="AM169" s="3"/>
       <c r="AN169" s="3"/>
-      <c r="AO169" s="2"/>
+      <c r="AO169" s="3"/>
       <c r="AP169" s="3"/>
       <c r="AQ169" s="3"/>
       <c r="AR169" s="3"/>
       <c r="AS169" s="3"/>
-      <c r="AT169" s="2"/>
+      <c r="AT169" s="3"/>
       <c r="AU169" s="3"/>
       <c r="AV169" s="3"/>
       <c r="AW169" s="3"/>
@@ -13794,7 +13793,7 @@
       <c r="J171" s="2"/>
       <c r="K171" s="3"/>
       <c r="L171" s="2"/>
-      <c r="M171" s="3"/>
+      <c r="M171" s="2"/>
       <c r="N171" s="3"/>
       <c r="O171" s="3"/>
       <c r="P171" s="3"/>
@@ -13862,29 +13861,29 @@
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
       <c r="F172" s="2"/>
-      <c r="G172" s="2"/>
+      <c r="G172" s="3"/>
       <c r="H172" s="3"/>
       <c r="I172" s="2"/>
       <c r="J172" s="2"/>
       <c r="K172" s="3"/>
       <c r="L172" s="2"/>
       <c r="M172" s="2"/>
-      <c r="N172" s="3"/>
+      <c r="N172" s="2"/>
       <c r="O172" s="3"/>
       <c r="P172" s="3"/>
       <c r="Q172" s="3"/>
-      <c r="R172" s="2"/>
+      <c r="R172" s="3"/>
       <c r="S172" s="3"/>
       <c r="T172" s="3"/>
       <c r="U172" s="3"/>
       <c r="V172" s="3"/>
-      <c r="W172" s="2"/>
+      <c r="W172" s="3"/>
       <c r="X172" s="3"/>
-      <c r="Y172" s="2"/>
+      <c r="Y172" s="3"/>
       <c r="Z172" s="3"/>
       <c r="AA172" s="4"/>
       <c r="AB172" s="5"/>
-      <c r="AC172" s="2"/>
+      <c r="AC172" s="3"/>
       <c r="AD172" s="3"/>
       <c r="AE172" s="3"/>
       <c r="AF172" s="4"/>
@@ -14015,7 +14014,7 @@
       <c r="I174" s="2"/>
       <c r="J174" s="2"/>
       <c r="K174" s="3"/>
-      <c r="L174" s="2"/>
+      <c r="L174" s="3"/>
       <c r="M174" s="2"/>
       <c r="N174" s="2"/>
       <c r="O174" s="3"/>
@@ -14026,9 +14025,9 @@
       <c r="T174" s="3"/>
       <c r="U174" s="3"/>
       <c r="V174" s="3"/>
-      <c r="W174" s="3"/>
+      <c r="W174" s="2"/>
       <c r="X174" s="3"/>
-      <c r="Y174" s="3"/>
+      <c r="Y174" s="2"/>
       <c r="Z174" s="3"/>
       <c r="AA174" s="4"/>
       <c r="AB174" s="5"/>
@@ -14053,7 +14052,7 @@
       <c r="AU174" s="3"/>
       <c r="AV174" s="3"/>
       <c r="AW174" s="3"/>
-      <c r="AX174" s="3"/>
+      <c r="AX174" s="2"/>
       <c r="AY174" s="3"/>
       <c r="AZ174" s="3"/>
       <c r="BA174" s="3"/>
@@ -14089,7 +14088,7 @@
       <c r="I175" s="2"/>
       <c r="J175" s="2"/>
       <c r="K175" s="3"/>
-      <c r="L175" s="3"/>
+      <c r="L175" s="2"/>
       <c r="M175" s="2"/>
       <c r="N175" s="2"/>
       <c r="O175" s="3"/>
@@ -14111,7 +14110,7 @@
       <c r="AE175" s="3"/>
       <c r="AF175" s="4"/>
       <c r="AG175" s="3"/>
-      <c r="AH175" s="3"/>
+      <c r="AH175" s="2"/>
       <c r="AI175" s="3"/>
       <c r="AJ175" s="3"/>
       <c r="AK175" s="3"/>
@@ -14123,11 +14122,11 @@
       <c r="AQ175" s="3"/>
       <c r="AR175" s="3"/>
       <c r="AS175" s="3"/>
-      <c r="AT175" s="3"/>
+      <c r="AT175" s="2"/>
       <c r="AU175" s="3"/>
       <c r="AV175" s="3"/>
       <c r="AW175" s="3"/>
-      <c r="AX175" s="2"/>
+      <c r="AX175" s="3"/>
       <c r="AY175" s="3"/>
       <c r="AZ175" s="3"/>
       <c r="BA175" s="3"/>
@@ -14173,8 +14172,8 @@
       <c r="S176" s="3"/>
       <c r="T176" s="3"/>
       <c r="U176" s="3"/>
-      <c r="V176" s="3"/>
-      <c r="W176" s="2"/>
+      <c r="V176" s="2"/>
+      <c r="W176" s="3"/>
       <c r="X176" s="3"/>
       <c r="Y176" s="2"/>
       <c r="Z176" s="3"/>
@@ -14185,7 +14184,7 @@
       <c r="AE176" s="3"/>
       <c r="AF176" s="4"/>
       <c r="AG176" s="3"/>
-      <c r="AH176" s="2"/>
+      <c r="AH176" s="3"/>
       <c r="AI176" s="3"/>
       <c r="AJ176" s="3"/>
       <c r="AK176" s="3"/>
@@ -14197,7 +14196,7 @@
       <c r="AQ176" s="3"/>
       <c r="AR176" s="3"/>
       <c r="AS176" s="3"/>
-      <c r="AT176" s="2"/>
+      <c r="AT176" s="3"/>
       <c r="AU176" s="3"/>
       <c r="AV176" s="3"/>
       <c r="AW176" s="3"/>
@@ -14247,10 +14246,10 @@
       <c r="S177" s="3"/>
       <c r="T177" s="3"/>
       <c r="U177" s="3"/>
-      <c r="V177" s="2"/>
+      <c r="V177" s="3"/>
       <c r="W177" s="3"/>
       <c r="X177" s="3"/>
-      <c r="Y177" s="2"/>
+      <c r="Y177" s="3"/>
       <c r="Z177" s="3"/>
       <c r="AA177" s="4"/>
       <c r="AB177" s="5"/>
@@ -14259,7 +14258,7 @@
       <c r="AE177" s="3"/>
       <c r="AF177" s="4"/>
       <c r="AG177" s="3"/>
-      <c r="AH177" s="3"/>
+      <c r="AH177" s="2"/>
       <c r="AI177" s="3"/>
       <c r="AJ177" s="3"/>
       <c r="AK177" s="3"/>
@@ -14311,7 +14310,7 @@
       <c r="I178" s="2"/>
       <c r="J178" s="2"/>
       <c r="K178" s="3"/>
-      <c r="L178" s="2"/>
+      <c r="L178" s="3"/>
       <c r="M178" s="2"/>
       <c r="N178" s="2"/>
       <c r="O178" s="3"/>
@@ -14333,7 +14332,7 @@
       <c r="AE178" s="3"/>
       <c r="AF178" s="4"/>
       <c r="AG178" s="3"/>
-      <c r="AH178" s="2"/>
+      <c r="AH178" s="3"/>
       <c r="AI178" s="3"/>
       <c r="AJ178" s="3"/>
       <c r="AK178" s="3"/>
@@ -14349,7 +14348,7 @@
       <c r="AU178" s="3"/>
       <c r="AV178" s="3"/>
       <c r="AW178" s="3"/>
-      <c r="AX178" s="3"/>
+      <c r="AX178" s="2"/>
       <c r="AY178" s="3"/>
       <c r="AZ178" s="3"/>
       <c r="BA178" s="3"/>
@@ -14407,7 +14406,7 @@
       <c r="AE179" s="3"/>
       <c r="AF179" s="4"/>
       <c r="AG179" s="3"/>
-      <c r="AH179" s="3"/>
+      <c r="AH179" s="2"/>
       <c r="AI179" s="3"/>
       <c r="AJ179" s="3"/>
       <c r="AK179" s="3"/>
@@ -14470,9 +14469,9 @@
       <c r="T180" s="3"/>
       <c r="U180" s="3"/>
       <c r="V180" s="3"/>
-      <c r="W180" s="3"/>
+      <c r="W180" s="2"/>
       <c r="X180" s="3"/>
-      <c r="Y180" s="3"/>
+      <c r="Y180" s="2"/>
       <c r="Z180" s="3"/>
       <c r="AA180" s="4"/>
       <c r="AB180" s="5"/>
@@ -14481,7 +14480,7 @@
       <c r="AE180" s="3"/>
       <c r="AF180" s="4"/>
       <c r="AG180" s="3"/>
-      <c r="AH180" s="2"/>
+      <c r="AH180" s="3"/>
       <c r="AI180" s="3"/>
       <c r="AJ180" s="3"/>
       <c r="AK180" s="3"/>
@@ -14497,7 +14496,7 @@
       <c r="AU180" s="3"/>
       <c r="AV180" s="3"/>
       <c r="AW180" s="3"/>
-      <c r="AX180" s="2"/>
+      <c r="AX180" s="3"/>
       <c r="AY180" s="3"/>
       <c r="AZ180" s="3"/>
       <c r="BA180" s="3"/>
@@ -14550,12 +14549,12 @@
       <c r="Z181" s="3"/>
       <c r="AA181" s="4"/>
       <c r="AB181" s="5"/>
-      <c r="AC181" s="3"/>
+      <c r="AC181" s="2"/>
       <c r="AD181" s="3"/>
       <c r="AE181" s="3"/>
       <c r="AF181" s="4"/>
       <c r="AG181" s="3"/>
-      <c r="AH181" s="3"/>
+      <c r="AH181" s="2"/>
       <c r="AI181" s="3"/>
       <c r="AJ181" s="3"/>
       <c r="AK181" s="3"/>
@@ -14607,7 +14606,7 @@
       <c r="I182" s="2"/>
       <c r="J182" s="2"/>
       <c r="K182" s="3"/>
-      <c r="L182" s="3"/>
+      <c r="L182" s="2"/>
       <c r="M182" s="2"/>
       <c r="N182" s="2"/>
       <c r="O182" s="3"/>
@@ -14616,7 +14615,7 @@
       <c r="R182" s="3"/>
       <c r="S182" s="3"/>
       <c r="T182" s="3"/>
-      <c r="U182" s="3"/>
+      <c r="U182" s="12"/>
       <c r="V182" s="3"/>
       <c r="W182" s="2"/>
       <c r="X182" s="3"/>
@@ -14624,7 +14623,7 @@
       <c r="Z182" s="3"/>
       <c r="AA182" s="4"/>
       <c r="AB182" s="5"/>
-      <c r="AC182" s="2"/>
+      <c r="AC182" s="3"/>
       <c r="AD182" s="3"/>
       <c r="AE182" s="3"/>
       <c r="AF182" s="4"/>
@@ -14690,7 +14689,7 @@
       <c r="R183" s="3"/>
       <c r="S183" s="3"/>
       <c r="T183" s="3"/>
-      <c r="U183" s="12"/>
+      <c r="U183" s="3"/>
       <c r="V183" s="3"/>
       <c r="W183" s="2"/>
       <c r="X183" s="3"/>
@@ -14698,7 +14697,7 @@
       <c r="Z183" s="3"/>
       <c r="AA183" s="4"/>
       <c r="AB183" s="5"/>
-      <c r="AC183" s="3"/>
+      <c r="AC183" s="2"/>
       <c r="AD183" s="3"/>
       <c r="AE183" s="3"/>
       <c r="AF183" s="4"/>
@@ -14756,8 +14755,8 @@
       <c r="J184" s="2"/>
       <c r="K184" s="3"/>
       <c r="L184" s="2"/>
-      <c r="M184" s="2"/>
-      <c r="N184" s="2"/>
+      <c r="M184" s="3"/>
+      <c r="N184" s="3"/>
       <c r="O184" s="3"/>
       <c r="P184" s="3"/>
       <c r="Q184" s="3"/>
@@ -14772,7 +14771,7 @@
       <c r="Z184" s="3"/>
       <c r="AA184" s="4"/>
       <c r="AB184" s="5"/>
-      <c r="AC184" s="2"/>
+      <c r="AC184" s="3"/>
       <c r="AD184" s="3"/>
       <c r="AE184" s="3"/>
       <c r="AF184" s="4"/>
@@ -14787,7 +14786,7 @@
       <c r="AO184" s="3"/>
       <c r="AP184" s="3"/>
       <c r="AQ184" s="3"/>
-      <c r="AR184" s="3"/>
+      <c r="AR184" s="2"/>
       <c r="AS184" s="3"/>
       <c r="AT184" s="3"/>
       <c r="AU184" s="3"/>
@@ -14835,7 +14834,7 @@
       <c r="O185" s="3"/>
       <c r="P185" s="3"/>
       <c r="Q185" s="3"/>
-      <c r="R185" s="3"/>
+      <c r="R185" s="2"/>
       <c r="S185" s="3"/>
       <c r="T185" s="3"/>
       <c r="U185" s="3"/>
@@ -14902,18 +14901,18 @@
       <c r="H186" s="3"/>
       <c r="I186" s="2"/>
       <c r="J186" s="2"/>
-      <c r="K186" s="3"/>
+      <c r="K186" s="2"/>
       <c r="L186" s="2"/>
-      <c r="M186" s="3"/>
-      <c r="N186" s="3"/>
-      <c r="O186" s="3"/>
+      <c r="M186" s="2"/>
+      <c r="N186" s="2"/>
+      <c r="O186" s="2"/>
       <c r="P186" s="3"/>
       <c r="Q186" s="3"/>
-      <c r="R186" s="2"/>
-      <c r="S186" s="3"/>
+      <c r="R186" s="3"/>
+      <c r="S186" s="2"/>
       <c r="T186" s="3"/>
       <c r="U186" s="3"/>
-      <c r="V186" s="3"/>
+      <c r="V186" s="2"/>
       <c r="W186" s="2"/>
       <c r="X186" s="3"/>
       <c r="Y186" s="2"/>
@@ -14935,7 +14934,7 @@
       <c r="AO186" s="3"/>
       <c r="AP186" s="3"/>
       <c r="AQ186" s="3"/>
-      <c r="AR186" s="2"/>
+      <c r="AR186" s="3"/>
       <c r="AS186" s="3"/>
       <c r="AT186" s="3"/>
       <c r="AU186" s="3"/>
@@ -14987,14 +14986,14 @@
       <c r="S187" s="2"/>
       <c r="T187" s="3"/>
       <c r="U187" s="3"/>
-      <c r="V187" s="2"/>
+      <c r="V187" s="3"/>
       <c r="W187" s="2"/>
       <c r="X187" s="3"/>
       <c r="Y187" s="2"/>
       <c r="Z187" s="3"/>
       <c r="AA187" s="4"/>
       <c r="AB187" s="5"/>
-      <c r="AC187" s="3"/>
+      <c r="AC187" s="2"/>
       <c r="AD187" s="3"/>
       <c r="AE187" s="3"/>
       <c r="AF187" s="4"/>
@@ -15039,7 +15038,7 @@
       <c r="BS187" s="3"/>
       <c r="BT187" s="3"/>
     </row>
-    <row r="188" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="2"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
@@ -15058,17 +15057,17 @@
       <c r="P188" s="3"/>
       <c r="Q188" s="3"/>
       <c r="R188" s="3"/>
-      <c r="S188" s="2"/>
+      <c r="S188" s="3"/>
       <c r="T188" s="3"/>
       <c r="U188" s="3"/>
-      <c r="V188" s="3"/>
-      <c r="W188" s="2"/>
+      <c r="V188" s="2"/>
+      <c r="W188" s="3"/>
       <c r="X188" s="3"/>
-      <c r="Y188" s="2"/>
+      <c r="Y188" s="3"/>
       <c r="Z188" s="3"/>
       <c r="AA188" s="4"/>
       <c r="AB188" s="5"/>
-      <c r="AC188" s="2"/>
+      <c r="AC188" s="3"/>
       <c r="AD188" s="3"/>
       <c r="AE188" s="3"/>
       <c r="AF188" s="4"/>
@@ -15081,10 +15080,10 @@
       <c r="AM188" s="3"/>
       <c r="AN188" s="3"/>
       <c r="AO188" s="3"/>
-      <c r="AP188" s="3"/>
+      <c r="AP188" s="2"/>
       <c r="AQ188" s="3"/>
       <c r="AR188" s="3"/>
-      <c r="AS188" s="3"/>
+      <c r="AS188" s="2"/>
       <c r="AT188" s="3"/>
       <c r="AU188" s="3"/>
       <c r="AV188" s="3"/>
@@ -15155,7 +15154,7 @@
       <c r="AM189" s="3"/>
       <c r="AN189" s="3"/>
       <c r="AO189" s="3"/>
-      <c r="AP189" s="2"/>
+      <c r="AP189" s="3"/>
       <c r="AQ189" s="3"/>
       <c r="AR189" s="3"/>
       <c r="AS189" s="2"/>
@@ -15209,8 +15208,8 @@
       <c r="S190" s="3"/>
       <c r="T190" s="3"/>
       <c r="U190" s="3"/>
-      <c r="V190" s="2"/>
-      <c r="W190" s="3"/>
+      <c r="V190" s="3"/>
+      <c r="W190" s="2"/>
       <c r="X190" s="3"/>
       <c r="Y190" s="3"/>
       <c r="Z190" s="3"/>
@@ -15221,7 +15220,7 @@
       <c r="AE190" s="3"/>
       <c r="AF190" s="4"/>
       <c r="AG190" s="3"/>
-      <c r="AH190" s="2"/>
+      <c r="AH190" s="3"/>
       <c r="AI190" s="3"/>
       <c r="AJ190" s="3"/>
       <c r="AK190" s="3"/>
@@ -15232,8 +15231,8 @@
       <c r="AP190" s="3"/>
       <c r="AQ190" s="3"/>
       <c r="AR190" s="3"/>
-      <c r="AS190" s="2"/>
-      <c r="AT190" s="3"/>
+      <c r="AS190" s="3"/>
+      <c r="AT190" s="2"/>
       <c r="AU190" s="3"/>
       <c r="AV190" s="3"/>
       <c r="AW190" s="3"/>
@@ -15276,7 +15275,7 @@
       <c r="L191" s="2"/>
       <c r="M191" s="2"/>
       <c r="N191" s="2"/>
-      <c r="O191" s="2"/>
+      <c r="O191" s="3"/>
       <c r="P191" s="3"/>
       <c r="Q191" s="3"/>
       <c r="R191" s="3"/>
@@ -15295,7 +15294,7 @@
       <c r="AE191" s="3"/>
       <c r="AF191" s="4"/>
       <c r="AG191" s="3"/>
-      <c r="AH191" s="3"/>
+      <c r="AH191" s="2"/>
       <c r="AI191" s="3"/>
       <c r="AJ191" s="3"/>
       <c r="AK191" s="3"/>
@@ -15346,12 +15345,12 @@
       <c r="H192" s="3"/>
       <c r="I192" s="2"/>
       <c r="J192" s="2"/>
-      <c r="K192" s="2"/>
+      <c r="K192" s="3"/>
       <c r="L192" s="2"/>
       <c r="M192" s="2"/>
       <c r="N192" s="2"/>
       <c r="O192" s="3"/>
-      <c r="P192" s="3"/>
+      <c r="P192" s="2"/>
       <c r="Q192" s="3"/>
       <c r="R192" s="3"/>
       <c r="S192" s="3"/>
@@ -15360,15 +15359,15 @@
       <c r="V192" s="3"/>
       <c r="W192" s="2"/>
       <c r="X192" s="3"/>
-      <c r="Y192" s="3"/>
+      <c r="Y192" s="2"/>
       <c r="Z192" s="3"/>
       <c r="AA192" s="4"/>
       <c r="AB192" s="5"/>
-      <c r="AC192" s="3"/>
+      <c r="AC192" s="2"/>
       <c r="AD192" s="3"/>
       <c r="AE192" s="3"/>
       <c r="AF192" s="4"/>
-      <c r="AG192" s="3"/>
+      <c r="AG192" s="2"/>
       <c r="AH192" s="2"/>
       <c r="AI192" s="3"/>
       <c r="AJ192" s="3"/>
@@ -15381,7 +15380,7 @@
       <c r="AQ192" s="3"/>
       <c r="AR192" s="3"/>
       <c r="AS192" s="3"/>
-      <c r="AT192" s="2"/>
+      <c r="AT192" s="3"/>
       <c r="AU192" s="3"/>
       <c r="AV192" s="3"/>
       <c r="AW192" s="3"/>
@@ -15421,11 +15420,11 @@
       <c r="I193" s="2"/>
       <c r="J193" s="2"/>
       <c r="K193" s="3"/>
-      <c r="L193" s="2"/>
+      <c r="L193" s="3"/>
       <c r="M193" s="2"/>
       <c r="N193" s="2"/>
       <c r="O193" s="3"/>
-      <c r="P193" s="2"/>
+      <c r="P193" s="3"/>
       <c r="Q193" s="3"/>
       <c r="R193" s="3"/>
       <c r="S193" s="3"/>
@@ -15438,7 +15437,7 @@
       <c r="Z193" s="3"/>
       <c r="AA193" s="4"/>
       <c r="AB193" s="5"/>
-      <c r="AC193" s="2"/>
+      <c r="AC193" s="3"/>
       <c r="AD193" s="3"/>
       <c r="AE193" s="3"/>
       <c r="AF193" s="4"/>
@@ -15572,8 +15571,8 @@
       <c r="L195" s="3"/>
       <c r="M195" s="2"/>
       <c r="N195" s="2"/>
-      <c r="O195" s="3"/>
-      <c r="P195" s="3"/>
+      <c r="O195" s="2"/>
+      <c r="P195" s="2"/>
       <c r="Q195" s="3"/>
       <c r="R195" s="3"/>
       <c r="S195" s="3"/>
@@ -15631,7 +15630,7 @@
       <c r="BS195" s="3"/>
       <c r="BT195" s="3"/>
     </row>
-    <row r="196" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="2"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
@@ -15654,9 +15653,9 @@
       <c r="T196" s="3"/>
       <c r="U196" s="3"/>
       <c r="V196" s="3"/>
-      <c r="W196" s="2"/>
+      <c r="W196" s="3"/>
       <c r="X196" s="3"/>
-      <c r="Y196" s="2"/>
+      <c r="Y196" s="3"/>
       <c r="Z196" s="3"/>
       <c r="AA196" s="4"/>
       <c r="AB196" s="5"/>
@@ -15705,7 +15704,7 @@
       <c r="BS196" s="3"/>
       <c r="BT196" s="3"/>
     </row>
-    <row r="197" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="2"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
@@ -15721,16 +15720,16 @@
       <c r="M197" s="2"/>
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
-      <c r="P197" s="2"/>
+      <c r="P197" s="3"/>
       <c r="Q197" s="3"/>
       <c r="R197" s="3"/>
       <c r="S197" s="3"/>
       <c r="T197" s="3"/>
       <c r="U197" s="3"/>
       <c r="V197" s="3"/>
-      <c r="W197" s="3"/>
+      <c r="W197" s="2"/>
       <c r="X197" s="3"/>
-      <c r="Y197" s="3"/>
+      <c r="Y197" s="2"/>
       <c r="Z197" s="3"/>
       <c r="AA197" s="4"/>
       <c r="AB197" s="5"/>
@@ -15791,7 +15790,7 @@
       <c r="I198" s="2"/>
       <c r="J198" s="2"/>
       <c r="K198" s="3"/>
-      <c r="L198" s="3"/>
+      <c r="L198" s="2"/>
       <c r="M198" s="2"/>
       <c r="N198" s="2"/>
       <c r="O198" s="2"/>
@@ -15865,7 +15864,7 @@
       <c r="I199" s="2"/>
       <c r="J199" s="2"/>
       <c r="K199" s="3"/>
-      <c r="L199" s="2"/>
+      <c r="L199" s="3"/>
       <c r="M199" s="2"/>
       <c r="N199" s="2"/>
       <c r="O199" s="2"/>
@@ -15886,7 +15885,7 @@
       <c r="AD199" s="3"/>
       <c r="AE199" s="3"/>
       <c r="AF199" s="4"/>
-      <c r="AG199" s="2"/>
+      <c r="AG199" s="3"/>
       <c r="AH199" s="2"/>
       <c r="AI199" s="3"/>
       <c r="AJ199" s="3"/>
@@ -15942,7 +15941,7 @@
       <c r="L200" s="3"/>
       <c r="M200" s="2"/>
       <c r="N200" s="2"/>
-      <c r="O200" s="2"/>
+      <c r="O200" s="3"/>
       <c r="P200" s="3"/>
       <c r="Q200" s="3"/>
       <c r="R200" s="3"/>
@@ -16024,13 +16023,13 @@
       <c r="T201" s="3"/>
       <c r="U201" s="3"/>
       <c r="V201" s="3"/>
-      <c r="W201" s="2"/>
+      <c r="W201" s="3"/>
       <c r="X201" s="3"/>
       <c r="Y201" s="2"/>
       <c r="Z201" s="3"/>
       <c r="AA201" s="4"/>
       <c r="AB201" s="5"/>
-      <c r="AC201" s="3"/>
+      <c r="AC201" s="2"/>
       <c r="AD201" s="3"/>
       <c r="AE201" s="3"/>
       <c r="AF201" s="4"/>
@@ -16098,14 +16097,14 @@
       <c r="T202" s="3"/>
       <c r="U202" s="3"/>
       <c r="V202" s="3"/>
-      <c r="W202" s="3"/>
+      <c r="W202" s="2"/>
       <c r="X202" s="3"/>
       <c r="Y202" s="2"/>
       <c r="Z202" s="3"/>
       <c r="AA202" s="4"/>
       <c r="AB202" s="5"/>
       <c r="AC202" s="2"/>
-      <c r="AD202" s="3"/>
+      <c r="AD202" s="2"/>
       <c r="AE202" s="3"/>
       <c r="AF202" s="4"/>
       <c r="AG202" s="3"/>
@@ -16116,12 +16115,12 @@
       <c r="AL202" s="3"/>
       <c r="AM202" s="3"/>
       <c r="AN202" s="3"/>
-      <c r="AO202" s="3"/>
+      <c r="AO202" s="2"/>
       <c r="AP202" s="3"/>
       <c r="AQ202" s="3"/>
       <c r="AR202" s="3"/>
       <c r="AS202" s="3"/>
-      <c r="AT202" s="3"/>
+      <c r="AT202" s="2"/>
       <c r="AU202" s="3"/>
       <c r="AV202" s="3"/>
       <c r="AW202" s="3"/>
@@ -16190,7 +16189,7 @@
       <c r="AL203" s="3"/>
       <c r="AM203" s="3"/>
       <c r="AN203" s="3"/>
-      <c r="AO203" s="2"/>
+      <c r="AO203" s="3"/>
       <c r="AP203" s="3"/>
       <c r="AQ203" s="3"/>
       <c r="AR203" s="3"/>
@@ -16229,7 +16228,7 @@
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
       <c r="E204" s="3"/>
-      <c r="F204" s="2"/>
+      <c r="F204" s="3"/>
       <c r="G204" s="3"/>
       <c r="H204" s="3"/>
       <c r="I204" s="2"/>
@@ -16252,12 +16251,12 @@
       <c r="Z204" s="3"/>
       <c r="AA204" s="4"/>
       <c r="AB204" s="5"/>
-      <c r="AC204" s="2"/>
-      <c r="AD204" s="2"/>
+      <c r="AC204" s="3"/>
+      <c r="AD204" s="3"/>
       <c r="AE204" s="3"/>
       <c r="AF204" s="4"/>
       <c r="AG204" s="3"/>
-      <c r="AH204" s="2"/>
+      <c r="AH204" s="3"/>
       <c r="AI204" s="3"/>
       <c r="AJ204" s="3"/>
       <c r="AK204" s="3"/>
@@ -16269,7 +16268,7 @@
       <c r="AQ204" s="3"/>
       <c r="AR204" s="3"/>
       <c r="AS204" s="3"/>
-      <c r="AT204" s="2"/>
+      <c r="AT204" s="3"/>
       <c r="AU204" s="3"/>
       <c r="AV204" s="3"/>
       <c r="AW204" s="3"/>
@@ -16303,7 +16302,7 @@
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
       <c r="E205" s="3"/>
-      <c r="F205" s="3"/>
+      <c r="F205" s="2"/>
       <c r="G205" s="3"/>
       <c r="H205" s="3"/>
       <c r="I205" s="2"/>
@@ -16320,7 +16319,7 @@
       <c r="T205" s="3"/>
       <c r="U205" s="3"/>
       <c r="V205" s="3"/>
-      <c r="W205" s="2"/>
+      <c r="W205" s="3"/>
       <c r="X205" s="3"/>
       <c r="Y205" s="2"/>
       <c r="Z205" s="3"/>
@@ -16331,7 +16330,7 @@
       <c r="AE205" s="3"/>
       <c r="AF205" s="4"/>
       <c r="AG205" s="3"/>
-      <c r="AH205" s="3"/>
+      <c r="AH205" s="2"/>
       <c r="AI205" s="3"/>
       <c r="AJ205" s="3"/>
       <c r="AK205" s="3"/>
@@ -16383,7 +16382,7 @@
       <c r="I206" s="2"/>
       <c r="J206" s="2"/>
       <c r="K206" s="3"/>
-      <c r="L206" s="3"/>
+      <c r="L206" s="2"/>
       <c r="M206" s="2"/>
       <c r="N206" s="2"/>
       <c r="O206" s="3"/>
@@ -16393,8 +16392,8 @@
       <c r="S206" s="3"/>
       <c r="T206" s="3"/>
       <c r="U206" s="3"/>
-      <c r="V206" s="3"/>
-      <c r="W206" s="3"/>
+      <c r="V206" s="2"/>
+      <c r="W206" s="2"/>
       <c r="X206" s="3"/>
       <c r="Y206" s="2"/>
       <c r="Z206" s="3"/>
@@ -16417,7 +16416,7 @@
       <c r="AQ206" s="3"/>
       <c r="AR206" s="3"/>
       <c r="AS206" s="3"/>
-      <c r="AT206" s="3"/>
+      <c r="AT206" s="2"/>
       <c r="AU206" s="3"/>
       <c r="AV206" s="3"/>
       <c r="AW206" s="3"/>
@@ -16457,7 +16456,7 @@
       <c r="I207" s="2"/>
       <c r="J207" s="2"/>
       <c r="K207" s="3"/>
-      <c r="L207" s="2"/>
+      <c r="L207" s="3"/>
       <c r="M207" s="2"/>
       <c r="N207" s="2"/>
       <c r="O207" s="3"/>
@@ -16467,8 +16466,8 @@
       <c r="S207" s="3"/>
       <c r="T207" s="3"/>
       <c r="U207" s="3"/>
-      <c r="V207" s="2"/>
-      <c r="W207" s="2"/>
+      <c r="V207" s="3"/>
+      <c r="W207" s="3"/>
       <c r="X207" s="3"/>
       <c r="Y207" s="2"/>
       <c r="Z207" s="3"/>
@@ -16497,7 +16496,7 @@
       <c r="AW207" s="3"/>
       <c r="AX207" s="3"/>
       <c r="AY207" s="3"/>
-      <c r="AZ207" s="3"/>
+      <c r="AZ207" s="16"/>
       <c r="BA207" s="3"/>
       <c r="BB207" s="3"/>
       <c r="BC207" s="3"/>
@@ -16565,13 +16564,13 @@
       <c r="AQ208" s="3"/>
       <c r="AR208" s="3"/>
       <c r="AS208" s="3"/>
-      <c r="AT208" s="2"/>
+      <c r="AT208" s="3"/>
       <c r="AU208" s="3"/>
       <c r="AV208" s="3"/>
       <c r="AW208" s="3"/>
       <c r="AX208" s="3"/>
       <c r="AY208" s="3"/>
-      <c r="AZ208" s="16"/>
+      <c r="AZ208" s="3"/>
       <c r="BA208" s="3"/>
       <c r="BB208" s="3"/>
       <c r="BC208" s="3"/>
@@ -16616,13 +16615,13 @@
       <c r="T209" s="3"/>
       <c r="U209" s="3"/>
       <c r="V209" s="3"/>
-      <c r="W209" s="3"/>
+      <c r="W209" s="2"/>
       <c r="X209" s="3"/>
       <c r="Y209" s="2"/>
       <c r="Z209" s="3"/>
       <c r="AA209" s="4"/>
       <c r="AB209" s="5"/>
-      <c r="AC209" s="3"/>
+      <c r="AC209" s="2"/>
       <c r="AD209" s="3"/>
       <c r="AE209" s="3"/>
       <c r="AF209" s="4"/>
@@ -16641,7 +16640,7 @@
       <c r="AS209" s="3"/>
       <c r="AT209" s="3"/>
       <c r="AU209" s="3"/>
-      <c r="AV209" s="3"/>
+      <c r="AV209" s="2"/>
       <c r="AW209" s="3"/>
       <c r="AX209" s="3"/>
       <c r="AY209" s="3"/>
@@ -16690,7 +16689,7 @@
       <c r="T210" s="3"/>
       <c r="U210" s="3"/>
       <c r="V210" s="3"/>
-      <c r="W210" s="2"/>
+      <c r="W210" s="3"/>
       <c r="X210" s="3"/>
       <c r="Y210" s="2"/>
       <c r="Z210" s="3"/>
@@ -16715,7 +16714,7 @@
       <c r="AS210" s="3"/>
       <c r="AT210" s="3"/>
       <c r="AU210" s="3"/>
-      <c r="AV210" s="2"/>
+      <c r="AV210" s="3"/>
       <c r="AW210" s="3"/>
       <c r="AX210" s="3"/>
       <c r="AY210" s="3"/>
@@ -16763,8 +16762,8 @@
       <c r="S211" s="3"/>
       <c r="T211" s="3"/>
       <c r="U211" s="3"/>
-      <c r="V211" s="3"/>
-      <c r="W211" s="3"/>
+      <c r="V211" s="2"/>
+      <c r="W211" s="2"/>
       <c r="X211" s="3"/>
       <c r="Y211" s="2"/>
       <c r="Z211" s="3"/>
@@ -16793,7 +16792,7 @@
       <c r="AW211" s="3"/>
       <c r="AX211" s="3"/>
       <c r="AY211" s="3"/>
-      <c r="AZ211" s="3"/>
+      <c r="AZ211" s="2"/>
       <c r="BA211" s="3"/>
       <c r="BB211" s="3"/>
       <c r="BC211" s="3"/>
@@ -16837,8 +16836,8 @@
       <c r="S212" s="3"/>
       <c r="T212" s="3"/>
       <c r="U212" s="3"/>
-      <c r="V212" s="2"/>
-      <c r="W212" s="2"/>
+      <c r="V212" s="3"/>
+      <c r="W212" s="3"/>
       <c r="X212" s="3"/>
       <c r="Y212" s="2"/>
       <c r="Z212" s="3"/>
@@ -16901,7 +16900,7 @@
       <c r="I213" s="2"/>
       <c r="J213" s="2"/>
       <c r="K213" s="3"/>
-      <c r="L213" s="3"/>
+      <c r="L213" s="2"/>
       <c r="M213" s="2"/>
       <c r="N213" s="2"/>
       <c r="O213" s="3"/>
@@ -16911,8 +16910,8 @@
       <c r="S213" s="3"/>
       <c r="T213" s="3"/>
       <c r="U213" s="3"/>
-      <c r="V213" s="3"/>
-      <c r="W213" s="3"/>
+      <c r="V213" s="2"/>
+      <c r="W213" s="2"/>
       <c r="X213" s="3"/>
       <c r="Y213" s="2"/>
       <c r="Z213" s="3"/>
@@ -17037,7 +17036,7 @@
       <c r="BS214" s="3"/>
       <c r="BT214" s="3"/>
     </row>
-    <row r="215" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="215" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="2"/>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
@@ -17049,7 +17048,7 @@
       <c r="I215" s="2"/>
       <c r="J215" s="2"/>
       <c r="K215" s="3"/>
-      <c r="L215" s="2"/>
+      <c r="L215" s="3"/>
       <c r="M215" s="2"/>
       <c r="N215" s="2"/>
       <c r="O215" s="3"/>
@@ -17062,7 +17061,7 @@
       <c r="V215" s="2"/>
       <c r="W215" s="2"/>
       <c r="X215" s="3"/>
-      <c r="Y215" s="2"/>
+      <c r="Y215" s="3"/>
       <c r="Z215" s="3"/>
       <c r="AA215" s="4"/>
       <c r="AB215" s="5"/>
@@ -17207,10 +17206,10 @@
       <c r="S217" s="3"/>
       <c r="T217" s="3"/>
       <c r="U217" s="3"/>
-      <c r="V217" s="2"/>
+      <c r="V217" s="3"/>
       <c r="W217" s="2"/>
       <c r="X217" s="3"/>
-      <c r="Y217" s="3"/>
+      <c r="Y217" s="2"/>
       <c r="Z217" s="3"/>
       <c r="AA217" s="4"/>
       <c r="AB217" s="5"/>
@@ -17237,7 +17236,7 @@
       <c r="AW217" s="3"/>
       <c r="AX217" s="3"/>
       <c r="AY217" s="3"/>
-      <c r="AZ217" s="2"/>
+      <c r="AZ217" s="3"/>
       <c r="BA217" s="3"/>
       <c r="BB217" s="3"/>
       <c r="BC217" s="3"/>
@@ -17728,7 +17727,7 @@
       <c r="V224" s="3"/>
       <c r="W224" s="2"/>
       <c r="X224" s="3"/>
-      <c r="Y224" s="2"/>
+      <c r="Y224" s="3"/>
       <c r="Z224" s="3"/>
       <c r="AA224" s="4"/>
       <c r="AB224" s="5"/>
@@ -17789,7 +17788,7 @@
       <c r="I225" s="2"/>
       <c r="J225" s="2"/>
       <c r="K225" s="3"/>
-      <c r="L225" s="3"/>
+      <c r="L225" s="2"/>
       <c r="M225" s="2"/>
       <c r="N225" s="2"/>
       <c r="O225" s="3"/>
@@ -17802,11 +17801,11 @@
       <c r="V225" s="3"/>
       <c r="W225" s="2"/>
       <c r="X225" s="3"/>
-      <c r="Y225" s="3"/>
+      <c r="Y225" s="2"/>
       <c r="Z225" s="3"/>
       <c r="AA225" s="4"/>
       <c r="AB225" s="5"/>
-      <c r="AC225" s="2"/>
+      <c r="AC225" s="3"/>
       <c r="AD225" s="3"/>
       <c r="AE225" s="3"/>
       <c r="AF225" s="4"/>
@@ -17870,7 +17869,7 @@
       <c r="P226" s="3"/>
       <c r="Q226" s="3"/>
       <c r="R226" s="3"/>
-      <c r="S226" s="3"/>
+      <c r="S226" s="2"/>
       <c r="T226" s="3"/>
       <c r="U226" s="3"/>
       <c r="V226" s="3"/>
@@ -17944,7 +17943,7 @@
       <c r="P227" s="3"/>
       <c r="Q227" s="3"/>
       <c r="R227" s="3"/>
-      <c r="S227" s="2"/>
+      <c r="S227" s="3"/>
       <c r="T227" s="3"/>
       <c r="U227" s="3"/>
       <c r="V227" s="3"/>
@@ -18028,8 +18027,8 @@
       <c r="Z228" s="3"/>
       <c r="AA228" s="4"/>
       <c r="AB228" s="5"/>
-      <c r="AC228" s="3"/>
-      <c r="AD228" s="3"/>
+      <c r="AC228" s="2"/>
+      <c r="AD228" s="2"/>
       <c r="AE228" s="3"/>
       <c r="AF228" s="4"/>
       <c r="AG228" s="3"/>
@@ -18078,14 +18077,14 @@
       <c r="B229" s="3"/>
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
-      <c r="E229" s="3"/>
+      <c r="E229" s="2"/>
       <c r="F229" s="2"/>
       <c r="G229" s="3"/>
       <c r="H229" s="3"/>
       <c r="I229" s="2"/>
       <c r="J229" s="2"/>
       <c r="K229" s="3"/>
-      <c r="L229" s="2"/>
+      <c r="L229" s="3"/>
       <c r="M229" s="2"/>
       <c r="N229" s="2"/>
       <c r="O229" s="3"/>
@@ -18098,17 +18097,17 @@
       <c r="V229" s="3"/>
       <c r="W229" s="2"/>
       <c r="X229" s="3"/>
-      <c r="Y229" s="2"/>
+      <c r="Y229" s="3"/>
       <c r="Z229" s="3"/>
       <c r="AA229" s="4"/>
       <c r="AB229" s="5"/>
-      <c r="AC229" s="2"/>
-      <c r="AD229" s="2"/>
+      <c r="AC229" s="3"/>
+      <c r="AD229" s="3"/>
       <c r="AE229" s="3"/>
       <c r="AF229" s="4"/>
       <c r="AG229" s="3"/>
       <c r="AH229" s="2"/>
-      <c r="AI229" s="3"/>
+      <c r="AI229" s="2"/>
       <c r="AJ229" s="3"/>
       <c r="AK229" s="3"/>
       <c r="AL229" s="3"/>
@@ -18152,7 +18151,7 @@
       <c r="B230" s="3"/>
       <c r="C230" s="3"/>
       <c r="D230" s="3"/>
-      <c r="E230" s="2"/>
+      <c r="E230" s="3"/>
       <c r="F230" s="2"/>
       <c r="G230" s="3"/>
       <c r="H230" s="3"/>
@@ -18170,9 +18169,9 @@
       <c r="T230" s="3"/>
       <c r="U230" s="3"/>
       <c r="V230" s="3"/>
-      <c r="W230" s="2"/>
+      <c r="W230" s="3"/>
       <c r="X230" s="3"/>
-      <c r="Y230" s="3"/>
+      <c r="Y230" s="2"/>
       <c r="Z230" s="3"/>
       <c r="AA230" s="4"/>
       <c r="AB230" s="5"/>
@@ -18182,7 +18181,7 @@
       <c r="AF230" s="4"/>
       <c r="AG230" s="3"/>
       <c r="AH230" s="2"/>
-      <c r="AI230" s="2"/>
+      <c r="AI230" s="3"/>
       <c r="AJ230" s="3"/>
       <c r="AK230" s="3"/>
       <c r="AL230" s="3"/>
@@ -18244,7 +18243,7 @@
       <c r="T231" s="3"/>
       <c r="U231" s="3"/>
       <c r="V231" s="3"/>
-      <c r="W231" s="3"/>
+      <c r="W231" s="2"/>
       <c r="X231" s="3"/>
       <c r="Y231" s="2"/>
       <c r="Z231" s="3"/>
@@ -18269,7 +18268,7 @@
       <c r="AS231" s="3"/>
       <c r="AT231" s="3"/>
       <c r="AU231" s="3"/>
-      <c r="AV231" s="3"/>
+      <c r="AV231" s="2"/>
       <c r="AW231" s="3"/>
       <c r="AX231" s="3"/>
       <c r="AY231" s="3"/>
@@ -18318,9 +18317,9 @@
       <c r="T232" s="3"/>
       <c r="U232" s="3"/>
       <c r="V232" s="3"/>
-      <c r="W232" s="2"/>
+      <c r="W232" s="3"/>
       <c r="X232" s="3"/>
-      <c r="Y232" s="2"/>
+      <c r="Y232" s="3"/>
       <c r="Z232" s="3"/>
       <c r="AA232" s="4"/>
       <c r="AB232" s="5"/>
@@ -18374,10 +18373,10 @@
       <c r="B233" s="3"/>
       <c r="C233" s="3"/>
       <c r="D233" s="3"/>
-      <c r="E233" s="3"/>
+      <c r="E233" s="2"/>
       <c r="F233" s="2"/>
       <c r="G233" s="3"/>
-      <c r="H233" s="3"/>
+      <c r="H233" s="2"/>
       <c r="I233" s="2"/>
       <c r="J233" s="2"/>
       <c r="K233" s="3"/>
@@ -18392,19 +18391,19 @@
       <c r="T233" s="3"/>
       <c r="U233" s="3"/>
       <c r="V233" s="3"/>
-      <c r="W233" s="3"/>
+      <c r="W233" s="2"/>
       <c r="X233" s="3"/>
-      <c r="Y233" s="3"/>
+      <c r="Y233" s="2"/>
       <c r="Z233" s="3"/>
       <c r="AA233" s="4"/>
       <c r="AB233" s="5"/>
-      <c r="AC233" s="3"/>
-      <c r="AD233" s="3"/>
+      <c r="AC233" s="2"/>
+      <c r="AD233" s="2"/>
       <c r="AE233" s="3"/>
       <c r="AF233" s="4"/>
       <c r="AG233" s="3"/>
       <c r="AH233" s="2"/>
-      <c r="AI233" s="3"/>
+      <c r="AI233" s="2"/>
       <c r="AJ233" s="3"/>
       <c r="AK233" s="3"/>
       <c r="AL233" s="3"/>
@@ -18444,14 +18443,14 @@
       <c r="BT233" s="3"/>
     </row>
     <row r="234" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A234" s="2"/>
+      <c r="A234" s="17"/>
       <c r="B234" s="3"/>
       <c r="C234" s="3"/>
       <c r="D234" s="3"/>
       <c r="E234" s="2"/>
-      <c r="F234" s="2"/>
-      <c r="G234" s="3"/>
-      <c r="H234" s="2"/>
+      <c r="F234" s="3"/>
+      <c r="G234" s="17"/>
+      <c r="H234" s="3"/>
       <c r="I234" s="2"/>
       <c r="J234" s="2"/>
       <c r="K234" s="3"/>
@@ -18465,15 +18464,15 @@
       <c r="S234" s="3"/>
       <c r="T234" s="3"/>
       <c r="U234" s="3"/>
-      <c r="V234" s="3"/>
-      <c r="W234" s="2"/>
+      <c r="V234" s="2"/>
+      <c r="W234" s="3"/>
       <c r="X234" s="3"/>
       <c r="Y234" s="2"/>
       <c r="Z234" s="3"/>
       <c r="AA234" s="4"/>
       <c r="AB234" s="5"/>
-      <c r="AC234" s="2"/>
-      <c r="AD234" s="2"/>
+      <c r="AC234" s="3"/>
+      <c r="AD234" s="3"/>
       <c r="AE234" s="3"/>
       <c r="AF234" s="4"/>
       <c r="AG234" s="3"/>
@@ -18488,7 +18487,7 @@
       <c r="AP234" s="3"/>
       <c r="AQ234" s="3"/>
       <c r="AR234" s="3"/>
-      <c r="AS234" s="3"/>
+      <c r="AS234" s="2"/>
       <c r="AT234" s="3"/>
       <c r="AU234" s="3"/>
       <c r="AV234" s="2"/>
@@ -18592,13 +18591,13 @@
       <c r="BT235" s="3"/>
     </row>
     <row r="236" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A236" s="17"/>
+      <c r="A236" s="2"/>
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
       <c r="D236" s="3"/>
       <c r="E236" s="2"/>
-      <c r="F236" s="3"/>
-      <c r="G236" s="17"/>
+      <c r="F236" s="2"/>
+      <c r="G236" s="3"/>
       <c r="H236" s="3"/>
       <c r="I236" s="2"/>
       <c r="J236" s="2"/>
@@ -18636,7 +18635,7 @@
       <c r="AP236" s="3"/>
       <c r="AQ236" s="3"/>
       <c r="AR236" s="3"/>
-      <c r="AS236" s="2"/>
+      <c r="AS236" s="3"/>
       <c r="AT236" s="3"/>
       <c r="AU236" s="3"/>
       <c r="AV236" s="2"/>
@@ -18687,8 +18686,8 @@
       <c r="S237" s="3"/>
       <c r="T237" s="3"/>
       <c r="U237" s="3"/>
-      <c r="V237" s="2"/>
-      <c r="W237" s="3"/>
+      <c r="V237" s="3"/>
+      <c r="W237" s="2"/>
       <c r="X237" s="3"/>
       <c r="Y237" s="2"/>
       <c r="Z237" s="3"/>
@@ -18744,14 +18743,14 @@
       <c r="B238" s="3"/>
       <c r="C238" s="3"/>
       <c r="D238" s="3"/>
-      <c r="E238" s="2"/>
+      <c r="E238" s="3"/>
       <c r="F238" s="2"/>
       <c r="G238" s="3"/>
       <c r="H238" s="3"/>
       <c r="I238" s="2"/>
       <c r="J238" s="2"/>
       <c r="K238" s="3"/>
-      <c r="L238" s="3"/>
+      <c r="L238" s="2"/>
       <c r="M238" s="2"/>
       <c r="N238" s="2"/>
       <c r="O238" s="3"/>
@@ -18768,7 +18767,7 @@
       <c r="Z238" s="3"/>
       <c r="AA238" s="4"/>
       <c r="AB238" s="5"/>
-      <c r="AC238" s="3"/>
+      <c r="AC238" s="2"/>
       <c r="AD238" s="3"/>
       <c r="AE238" s="3"/>
       <c r="AF238" s="4"/>
@@ -18825,7 +18824,7 @@
       <c r="I239" s="2"/>
       <c r="J239" s="2"/>
       <c r="K239" s="3"/>
-      <c r="L239" s="2"/>
+      <c r="L239" s="3"/>
       <c r="M239" s="2"/>
       <c r="N239" s="2"/>
       <c r="O239" s="3"/>
@@ -18917,7 +18916,7 @@
       <c r="AA240" s="4"/>
       <c r="AB240" s="5"/>
       <c r="AC240" s="2"/>
-      <c r="AD240" s="3"/>
+      <c r="AD240" s="2"/>
       <c r="AE240" s="3"/>
       <c r="AF240" s="4"/>
       <c r="AG240" s="3"/>
@@ -19040,7 +19039,7 @@
       <c r="B242" s="3"/>
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
-      <c r="E242" s="3"/>
+      <c r="E242" s="2"/>
       <c r="F242" s="2"/>
       <c r="G242" s="3"/>
       <c r="H242" s="3"/>
@@ -19060,12 +19059,12 @@
       <c r="V242" s="3"/>
       <c r="W242" s="2"/>
       <c r="X242" s="3"/>
-      <c r="Y242" s="2"/>
+      <c r="Y242" s="3"/>
       <c r="Z242" s="3"/>
       <c r="AA242" s="4"/>
       <c r="AB242" s="5"/>
-      <c r="AC242" s="2"/>
-      <c r="AD242" s="2"/>
+      <c r="AC242" s="3"/>
+      <c r="AD242" s="3"/>
       <c r="AE242" s="3"/>
       <c r="AF242" s="4"/>
       <c r="AG242" s="3"/>
@@ -19208,7 +19207,7 @@
       <c r="V244" s="3"/>
       <c r="W244" s="2"/>
       <c r="X244" s="3"/>
-      <c r="Y244" s="3"/>
+      <c r="Y244" s="2"/>
       <c r="Z244" s="3"/>
       <c r="AA244" s="4"/>
       <c r="AB244" s="5"/>
@@ -19262,7 +19261,7 @@
       <c r="B245" s="3"/>
       <c r="C245" s="3"/>
       <c r="D245" s="3"/>
-      <c r="E245" s="2"/>
+      <c r="E245" s="3"/>
       <c r="F245" s="2"/>
       <c r="G245" s="3"/>
       <c r="H245" s="3"/>
@@ -19286,13 +19285,13 @@
       <c r="Z245" s="3"/>
       <c r="AA245" s="4"/>
       <c r="AB245" s="5"/>
-      <c r="AC245" s="3"/>
+      <c r="AC245" s="2"/>
       <c r="AD245" s="3"/>
       <c r="AE245" s="3"/>
       <c r="AF245" s="4"/>
       <c r="AG245" s="3"/>
       <c r="AH245" s="2"/>
-      <c r="AI245" s="2"/>
+      <c r="AI245" s="3"/>
       <c r="AJ245" s="3"/>
       <c r="AK245" s="3"/>
       <c r="AL245" s="3"/>
@@ -19303,12 +19302,12 @@
       <c r="AQ245" s="3"/>
       <c r="AR245" s="3"/>
       <c r="AS245" s="3"/>
-      <c r="AT245" s="3"/>
+      <c r="AT245" s="2"/>
       <c r="AU245" s="3"/>
-      <c r="AV245" s="2"/>
+      <c r="AV245" s="3"/>
       <c r="AW245" s="3"/>
       <c r="AX245" s="3"/>
-      <c r="AY245" s="3"/>
+      <c r="AY245" s="18"/>
       <c r="AZ245" s="3"/>
       <c r="BA245" s="3"/>
       <c r="BB245" s="3"/>
@@ -19360,7 +19359,7 @@
       <c r="Z246" s="3"/>
       <c r="AA246" s="4"/>
       <c r="AB246" s="5"/>
-      <c r="AC246" s="2"/>
+      <c r="AC246" s="3"/>
       <c r="AD246" s="3"/>
       <c r="AE246" s="3"/>
       <c r="AF246" s="4"/>
@@ -19377,12 +19376,12 @@
       <c r="AQ246" s="3"/>
       <c r="AR246" s="3"/>
       <c r="AS246" s="3"/>
-      <c r="AT246" s="2"/>
+      <c r="AT246" s="3"/>
       <c r="AU246" s="3"/>
       <c r="AV246" s="3"/>
       <c r="AW246" s="3"/>
       <c r="AX246" s="3"/>
-      <c r="AY246" s="18"/>
+      <c r="AY246" s="3"/>
       <c r="AZ246" s="3"/>
       <c r="BA246" s="3"/>
       <c r="BB246" s="3"/>
@@ -19749,11 +19748,11 @@
       <c r="AS251" s="3"/>
       <c r="AT251" s="3"/>
       <c r="AU251" s="3"/>
-      <c r="AV251" s="3"/>
+      <c r="AV251" s="2"/>
       <c r="AW251" s="3"/>
       <c r="AX251" s="3"/>
-      <c r="AY251" s="3"/>
-      <c r="AZ251" s="3"/>
+      <c r="AY251" s="18"/>
+      <c r="AZ251" s="18"/>
       <c r="BA251" s="3"/>
       <c r="BB251" s="3"/>
       <c r="BC251" s="3"/>
@@ -19856,7 +19855,7 @@
       <c r="D253" s="3"/>
       <c r="E253" s="3"/>
       <c r="F253" s="2"/>
-      <c r="G253" s="3"/>
+      <c r="G253" s="2"/>
       <c r="H253" s="3"/>
       <c r="I253" s="2"/>
       <c r="J253" s="2"/>
@@ -19878,8 +19877,8 @@
       <c r="Z253" s="3"/>
       <c r="AA253" s="4"/>
       <c r="AB253" s="5"/>
-      <c r="AC253" s="3"/>
-      <c r="AD253" s="3"/>
+      <c r="AC253" s="2"/>
+      <c r="AD253" s="2"/>
       <c r="AE253" s="3"/>
       <c r="AF253" s="4"/>
       <c r="AG253" s="3"/>
@@ -19895,13 +19894,13 @@
       <c r="AQ253" s="3"/>
       <c r="AR253" s="3"/>
       <c r="AS253" s="3"/>
-      <c r="AT253" s="3"/>
+      <c r="AT253" s="2"/>
       <c r="AU253" s="3"/>
-      <c r="AV253" s="2"/>
+      <c r="AV253" s="3"/>
       <c r="AW253" s="3"/>
       <c r="AX253" s="3"/>
-      <c r="AY253" s="18"/>
-      <c r="AZ253" s="18"/>
+      <c r="AY253" s="3"/>
+      <c r="AZ253" s="2"/>
       <c r="BA253" s="3"/>
       <c r="BB253" s="3"/>
       <c r="BC253" s="3"/>
@@ -19930,7 +19929,7 @@
       <c r="D254" s="3"/>
       <c r="E254" s="3"/>
       <c r="F254" s="2"/>
-      <c r="G254" s="2"/>
+      <c r="G254" s="3"/>
       <c r="H254" s="3"/>
       <c r="I254" s="2"/>
       <c r="J254" s="2"/>
@@ -19953,7 +19952,7 @@
       <c r="AA254" s="4"/>
       <c r="AB254" s="5"/>
       <c r="AC254" s="2"/>
-      <c r="AD254" s="2"/>
+      <c r="AD254" s="3"/>
       <c r="AE254" s="3"/>
       <c r="AF254" s="4"/>
       <c r="AG254" s="3"/>
@@ -19969,13 +19968,13 @@
       <c r="AQ254" s="3"/>
       <c r="AR254" s="3"/>
       <c r="AS254" s="3"/>
-      <c r="AT254" s="2"/>
+      <c r="AT254" s="3"/>
       <c r="AU254" s="3"/>
       <c r="AV254" s="3"/>
       <c r="AW254" s="3"/>
       <c r="AX254" s="3"/>
       <c r="AY254" s="3"/>
-      <c r="AZ254" s="2"/>
+      <c r="AZ254" s="3"/>
       <c r="BA254" s="3"/>
       <c r="BB254" s="3"/>
       <c r="BC254" s="3"/>
@@ -20092,7 +20091,7 @@
       <c r="R256" s="3"/>
       <c r="S256" s="3"/>
       <c r="T256" s="3"/>
-      <c r="U256" s="3"/>
+      <c r="U256" s="2"/>
       <c r="V256" s="3"/>
       <c r="W256" s="2"/>
       <c r="X256" s="3"/>
@@ -20100,7 +20099,7 @@
       <c r="Z256" s="3"/>
       <c r="AA256" s="4"/>
       <c r="AB256" s="5"/>
-      <c r="AC256" s="2"/>
+      <c r="AC256" s="3"/>
       <c r="AD256" s="3"/>
       <c r="AE256" s="3"/>
       <c r="AF256" s="4"/>
@@ -20166,7 +20165,7 @@
       <c r="R257" s="3"/>
       <c r="S257" s="3"/>
       <c r="T257" s="3"/>
-      <c r="U257" s="2"/>
+      <c r="U257" s="3"/>
       <c r="V257" s="3"/>
       <c r="W257" s="2"/>
       <c r="X257" s="3"/>
@@ -20193,11 +20192,11 @@
       <c r="AS257" s="3"/>
       <c r="AT257" s="3"/>
       <c r="AU257" s="3"/>
-      <c r="AV257" s="3"/>
+      <c r="AV257" s="2"/>
       <c r="AW257" s="3"/>
       <c r="AX257" s="3"/>
       <c r="AY257" s="3"/>
-      <c r="AZ257" s="3"/>
+      <c r="AZ257" s="2"/>
       <c r="BA257" s="3"/>
       <c r="BB257" s="3"/>
       <c r="BC257" s="3"/>
@@ -20271,7 +20270,7 @@
       <c r="AW258" s="3"/>
       <c r="AX258" s="3"/>
       <c r="AY258" s="3"/>
-      <c r="AZ258" s="2"/>
+      <c r="AZ258" s="3"/>
       <c r="BA258" s="3"/>
       <c r="BB258" s="3"/>
       <c r="BC258" s="3"/>
@@ -20293,7 +20292,7 @@
       <c r="BS258" s="3"/>
       <c r="BT258" s="3"/>
     </row>
-    <row r="259" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="259" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="2"/>
       <c r="B259" s="3"/>
       <c r="C259" s="3"/>
@@ -20382,7 +20381,7 @@
       <c r="L260" s="3"/>
       <c r="M260" s="2"/>
       <c r="N260" s="2"/>
-      <c r="O260" s="3"/>
+      <c r="O260" s="2"/>
       <c r="P260" s="3"/>
       <c r="Q260" s="3"/>
       <c r="R260" s="3"/>
@@ -20400,7 +20399,7 @@
       <c r="AD260" s="3"/>
       <c r="AE260" s="3"/>
       <c r="AF260" s="4"/>
-      <c r="AG260" s="3"/>
+      <c r="AG260" s="2"/>
       <c r="AH260" s="2"/>
       <c r="AI260" s="3"/>
       <c r="AJ260" s="3"/>
@@ -20409,7 +20408,7 @@
       <c r="AM260" s="3"/>
       <c r="AN260" s="3"/>
       <c r="AO260" s="3"/>
-      <c r="AP260" s="3"/>
+      <c r="AP260" s="2"/>
       <c r="AQ260" s="3"/>
       <c r="AR260" s="3"/>
       <c r="AS260" s="3"/>
@@ -20456,7 +20455,7 @@
       <c r="L261" s="3"/>
       <c r="M261" s="2"/>
       <c r="N261" s="2"/>
-      <c r="O261" s="2"/>
+      <c r="O261" s="3"/>
       <c r="P261" s="3"/>
       <c r="Q261" s="3"/>
       <c r="R261" s="3"/>
@@ -20464,17 +20463,17 @@
       <c r="T261" s="3"/>
       <c r="U261" s="3"/>
       <c r="V261" s="3"/>
-      <c r="W261" s="2"/>
+      <c r="W261" s="3"/>
       <c r="X261" s="3"/>
       <c r="Y261" s="2"/>
       <c r="Z261" s="3"/>
       <c r="AA261" s="4"/>
       <c r="AB261" s="5"/>
-      <c r="AC261" s="3"/>
+      <c r="AC261" s="2"/>
       <c r="AD261" s="3"/>
       <c r="AE261" s="3"/>
       <c r="AF261" s="4"/>
-      <c r="AG261" s="2"/>
+      <c r="AG261" s="3"/>
       <c r="AH261" s="2"/>
       <c r="AI261" s="3"/>
       <c r="AJ261" s="3"/>
@@ -20483,13 +20482,13 @@
       <c r="AM261" s="3"/>
       <c r="AN261" s="3"/>
       <c r="AO261" s="3"/>
-      <c r="AP261" s="2"/>
+      <c r="AP261" s="3"/>
       <c r="AQ261" s="3"/>
       <c r="AR261" s="3"/>
       <c r="AS261" s="3"/>
       <c r="AT261" s="3"/>
       <c r="AU261" s="3"/>
-      <c r="AV261" s="2"/>
+      <c r="AV261" s="3"/>
       <c r="AW261" s="3"/>
       <c r="AX261" s="3"/>
       <c r="AY261" s="3"/>
@@ -20522,7 +20521,7 @@
       <c r="D262" s="3"/>
       <c r="E262" s="3"/>
       <c r="F262" s="2"/>
-      <c r="G262" s="3"/>
+      <c r="G262" s="2"/>
       <c r="H262" s="3"/>
       <c r="I262" s="2"/>
       <c r="J262" s="2"/>
@@ -20538,18 +20537,18 @@
       <c r="T262" s="3"/>
       <c r="U262" s="3"/>
       <c r="V262" s="3"/>
-      <c r="W262" s="3"/>
+      <c r="W262" s="2"/>
       <c r="X262" s="3"/>
       <c r="Y262" s="2"/>
       <c r="Z262" s="3"/>
       <c r="AA262" s="4"/>
       <c r="AB262" s="5"/>
       <c r="AC262" s="2"/>
-      <c r="AD262" s="3"/>
+      <c r="AD262" s="2"/>
       <c r="AE262" s="3"/>
       <c r="AF262" s="4"/>
       <c r="AG262" s="3"/>
-      <c r="AH262" s="2"/>
+      <c r="AH262" s="3"/>
       <c r="AI262" s="3"/>
       <c r="AJ262" s="3"/>
       <c r="AK262" s="3"/>
@@ -20596,7 +20595,7 @@
       <c r="D263" s="3"/>
       <c r="E263" s="3"/>
       <c r="F263" s="2"/>
-      <c r="G263" s="2"/>
+      <c r="G263" s="3"/>
       <c r="H263" s="3"/>
       <c r="I263" s="2"/>
       <c r="J263" s="2"/>
@@ -20612,18 +20611,18 @@
       <c r="T263" s="3"/>
       <c r="U263" s="3"/>
       <c r="V263" s="3"/>
-      <c r="W263" s="2"/>
+      <c r="W263" s="3"/>
       <c r="X263" s="3"/>
       <c r="Y263" s="2"/>
       <c r="Z263" s="3"/>
       <c r="AA263" s="4"/>
       <c r="AB263" s="5"/>
-      <c r="AC263" s="2"/>
-      <c r="AD263" s="2"/>
+      <c r="AC263" s="3"/>
+      <c r="AD263" s="3"/>
       <c r="AE263" s="3"/>
       <c r="AF263" s="4"/>
       <c r="AG263" s="3"/>
-      <c r="AH263" s="3"/>
+      <c r="AH263" s="2"/>
       <c r="AI263" s="3"/>
       <c r="AJ263" s="3"/>
       <c r="AK263" s="3"/>
@@ -20637,7 +20636,7 @@
       <c r="AS263" s="3"/>
       <c r="AT263" s="3"/>
       <c r="AU263" s="3"/>
-      <c r="AV263" s="3"/>
+      <c r="AV263" s="2"/>
       <c r="AW263" s="3"/>
       <c r="AX263" s="3"/>
       <c r="AY263" s="3"/>
@@ -20686,7 +20685,7 @@
       <c r="T264" s="3"/>
       <c r="U264" s="3"/>
       <c r="V264" s="3"/>
-      <c r="W264" s="3"/>
+      <c r="W264" s="2"/>
       <c r="X264" s="3"/>
       <c r="Y264" s="2"/>
       <c r="Z264" s="3"/>
@@ -20697,7 +20696,7 @@
       <c r="AE264" s="3"/>
       <c r="AF264" s="4"/>
       <c r="AG264" s="3"/>
-      <c r="AH264" s="2"/>
+      <c r="AH264" s="3"/>
       <c r="AI264" s="3"/>
       <c r="AJ264" s="3"/>
       <c r="AK264" s="3"/>
@@ -20711,7 +20710,7 @@
       <c r="AS264" s="3"/>
       <c r="AT264" s="3"/>
       <c r="AU264" s="3"/>
-      <c r="AV264" s="2"/>
+      <c r="AV264" s="3"/>
       <c r="AW264" s="3"/>
       <c r="AX264" s="3"/>
       <c r="AY264" s="3"/>
@@ -20742,7 +20741,7 @@
       <c r="B265" s="3"/>
       <c r="C265" s="3"/>
       <c r="D265" s="3"/>
-      <c r="E265" s="3"/>
+      <c r="E265" s="2"/>
       <c r="F265" s="2"/>
       <c r="G265" s="3"/>
       <c r="H265" s="3"/>
@@ -20758,8 +20757,8 @@
       <c r="R265" s="3"/>
       <c r="S265" s="3"/>
       <c r="T265" s="3"/>
-      <c r="U265" s="3"/>
-      <c r="V265" s="3"/>
+      <c r="U265" s="2"/>
+      <c r="V265" s="2"/>
       <c r="W265" s="2"/>
       <c r="X265" s="3"/>
       <c r="Y265" s="2"/>
@@ -20771,11 +20770,11 @@
       <c r="AE265" s="3"/>
       <c r="AF265" s="4"/>
       <c r="AG265" s="3"/>
-      <c r="AH265" s="3"/>
-      <c r="AI265" s="3"/>
+      <c r="AH265" s="2"/>
+      <c r="AI265" s="2"/>
       <c r="AJ265" s="3"/>
-      <c r="AK265" s="3"/>
-      <c r="AL265" s="3"/>
+      <c r="AK265" s="2"/>
+      <c r="AL265" s="18"/>
       <c r="AM265" s="3"/>
       <c r="AN265" s="3"/>
       <c r="AO265" s="3"/>
@@ -20785,11 +20784,11 @@
       <c r="AS265" s="3"/>
       <c r="AT265" s="3"/>
       <c r="AU265" s="3"/>
-      <c r="AV265" s="3"/>
+      <c r="AV265" s="2"/>
       <c r="AW265" s="3"/>
       <c r="AX265" s="3"/>
-      <c r="AY265" s="3"/>
-      <c r="AZ265" s="3"/>
+      <c r="AY265" s="19"/>
+      <c r="AZ265" s="18"/>
       <c r="BA265" s="3"/>
       <c r="BB265" s="3"/>
       <c r="BC265" s="3"/>
@@ -20816,8 +20815,8 @@
       <c r="B266" s="3"/>
       <c r="C266" s="3"/>
       <c r="D266" s="3"/>
-      <c r="E266" s="2"/>
-      <c r="F266" s="2"/>
+      <c r="E266" s="3"/>
+      <c r="F266" s="3"/>
       <c r="G266" s="3"/>
       <c r="H266" s="3"/>
       <c r="I266" s="2"/>
@@ -20832,9 +20831,9 @@
       <c r="R266" s="3"/>
       <c r="S266" s="3"/>
       <c r="T266" s="3"/>
-      <c r="U266" s="2"/>
+      <c r="U266" s="3"/>
       <c r="V266" s="2"/>
-      <c r="W266" s="2"/>
+      <c r="W266" s="3"/>
       <c r="X266" s="3"/>
       <c r="Y266" s="2"/>
       <c r="Z266" s="3"/>
@@ -20846,10 +20845,10 @@
       <c r="AF266" s="4"/>
       <c r="AG266" s="3"/>
       <c r="AH266" s="2"/>
-      <c r="AI266" s="2"/>
+      <c r="AI266" s="3"/>
       <c r="AJ266" s="3"/>
-      <c r="AK266" s="2"/>
-      <c r="AL266" s="18"/>
+      <c r="AK266" s="3"/>
+      <c r="AL266" s="3"/>
       <c r="AM266" s="3"/>
       <c r="AN266" s="3"/>
       <c r="AO266" s="3"/>
@@ -20858,12 +20857,12 @@
       <c r="AR266" s="3"/>
       <c r="AS266" s="3"/>
       <c r="AT266" s="3"/>
-      <c r="AU266" s="3"/>
-      <c r="AV266" s="2"/>
+      <c r="AU266" s="2"/>
+      <c r="AV266" s="3"/>
       <c r="AW266" s="3"/>
       <c r="AX266" s="3"/>
-      <c r="AY266" s="19"/>
-      <c r="AZ266" s="18"/>
+      <c r="AY266" s="3"/>
+      <c r="AZ266" s="3"/>
       <c r="BA266" s="3"/>
       <c r="BB266" s="3"/>
       <c r="BC266" s="3"/>
@@ -20891,7 +20890,7 @@
       <c r="C267" s="3"/>
       <c r="D267" s="3"/>
       <c r="E267" s="3"/>
-      <c r="F267" s="3"/>
+      <c r="F267" s="2"/>
       <c r="G267" s="3"/>
       <c r="H267" s="3"/>
       <c r="I267" s="2"/>
@@ -20906,9 +20905,9 @@
       <c r="R267" s="3"/>
       <c r="S267" s="3"/>
       <c r="T267" s="3"/>
-      <c r="U267" s="3"/>
+      <c r="U267" s="2"/>
       <c r="V267" s="2"/>
-      <c r="W267" s="3"/>
+      <c r="W267" s="2"/>
       <c r="X267" s="3"/>
       <c r="Y267" s="2"/>
       <c r="Z267" s="3"/>
@@ -20980,9 +20979,9 @@
       <c r="R268" s="3"/>
       <c r="S268" s="3"/>
       <c r="T268" s="3"/>
-      <c r="U268" s="2"/>
+      <c r="U268" s="3"/>
       <c r="V268" s="2"/>
-      <c r="W268" s="2"/>
+      <c r="W268" s="3"/>
       <c r="X268" s="3"/>
       <c r="Y268" s="2"/>
       <c r="Z268" s="3"/>
@@ -21006,7 +21005,7 @@
       <c r="AR268" s="3"/>
       <c r="AS268" s="3"/>
       <c r="AT268" s="3"/>
-      <c r="AU268" s="2"/>
+      <c r="AU268" s="3"/>
       <c r="AV268" s="3"/>
       <c r="AW268" s="3"/>
       <c r="AX268" s="3"/>
@@ -21202,7 +21201,7 @@
       <c r="R271" s="3"/>
       <c r="S271" s="3"/>
       <c r="T271" s="3"/>
-      <c r="U271" s="3"/>
+      <c r="U271" s="2"/>
       <c r="V271" s="2"/>
       <c r="W271" s="3"/>
       <c r="X271" s="3"/>
@@ -21276,7 +21275,7 @@
       <c r="R272" s="3"/>
       <c r="S272" s="3"/>
       <c r="T272" s="3"/>
-      <c r="U272" s="2"/>
+      <c r="U272" s="3"/>
       <c r="V272" s="2"/>
       <c r="W272" s="3"/>
       <c r="X272" s="3"/>
@@ -21352,7 +21351,7 @@
       <c r="T273" s="3"/>
       <c r="U273" s="3"/>
       <c r="V273" s="2"/>
-      <c r="W273" s="3"/>
+      <c r="W273" s="2"/>
       <c r="X273" s="3"/>
       <c r="Y273" s="2"/>
       <c r="Z273" s="3"/>
@@ -21426,7 +21425,7 @@
       <c r="T274" s="3"/>
       <c r="U274" s="3"/>
       <c r="V274" s="2"/>
-      <c r="W274" s="2"/>
+      <c r="W274" s="3"/>
       <c r="X274" s="3"/>
       <c r="Y274" s="2"/>
       <c r="Z274" s="3"/>
@@ -21502,7 +21501,7 @@
       <c r="V275" s="2"/>
       <c r="W275" s="3"/>
       <c r="X275" s="3"/>
-      <c r="Y275" s="2"/>
+      <c r="Y275" s="3"/>
       <c r="Z275" s="3"/>
       <c r="AA275" s="4"/>
       <c r="AB275" s="5"/>
@@ -21551,7 +21550,7 @@
       <c r="BS275" s="3"/>
       <c r="BT275" s="3"/>
     </row>
-    <row r="276" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="276" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="2"/>
       <c r="B276" s="3"/>
       <c r="C276" s="3"/>
@@ -21574,13 +21573,13 @@
       <c r="T276" s="3"/>
       <c r="U276" s="3"/>
       <c r="V276" s="2"/>
-      <c r="W276" s="3"/>
+      <c r="W276" s="2"/>
       <c r="X276" s="3"/>
       <c r="Y276" s="3"/>
       <c r="Z276" s="3"/>
       <c r="AA276" s="4"/>
       <c r="AB276" s="5"/>
-      <c r="AC276" s="3"/>
+      <c r="AC276" s="2"/>
       <c r="AD276" s="3"/>
       <c r="AE276" s="3"/>
       <c r="AF276" s="4"/>
@@ -21647,14 +21646,14 @@
       <c r="S277" s="3"/>
       <c r="T277" s="3"/>
       <c r="U277" s="3"/>
-      <c r="V277" s="2"/>
-      <c r="W277" s="2"/>
+      <c r="V277" s="3"/>
+      <c r="W277" s="3"/>
       <c r="X277" s="3"/>
       <c r="Y277" s="3"/>
       <c r="Z277" s="3"/>
       <c r="AA277" s="4"/>
       <c r="AB277" s="5"/>
-      <c r="AC277" s="2"/>
+      <c r="AC277" s="3"/>
       <c r="AD277" s="3"/>
       <c r="AE277" s="3"/>
       <c r="AF277" s="4"/>
@@ -21673,7 +21672,7 @@
       <c r="AS277" s="3"/>
       <c r="AT277" s="3"/>
       <c r="AU277" s="3"/>
-      <c r="AV277" s="3"/>
+      <c r="AV277" s="2"/>
       <c r="AW277" s="3"/>
       <c r="AX277" s="3"/>
       <c r="AY277" s="3"/>
@@ -21943,7 +21942,7 @@
       <c r="S281" s="3"/>
       <c r="T281" s="3"/>
       <c r="U281" s="3"/>
-      <c r="V281" s="3"/>
+      <c r="V281" s="2"/>
       <c r="W281" s="3"/>
       <c r="X281" s="3"/>
       <c r="Y281" s="3"/>
@@ -21995,13 +21994,13 @@
       <c r="BS281" s="3"/>
       <c r="BT281" s="3"/>
     </row>
-    <row r="282" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="282" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="2"/>
-      <c r="B282" s="3"/>
+      <c r="B282" s="18"/>
       <c r="C282" s="3"/>
       <c r="D282" s="3"/>
-      <c r="E282" s="3"/>
-      <c r="F282" s="2"/>
+      <c r="E282" s="2"/>
+      <c r="F282" s="18"/>
       <c r="G282" s="3"/>
       <c r="H282" s="3"/>
       <c r="I282" s="2"/>
@@ -22018,9 +22017,9 @@
       <c r="T282" s="3"/>
       <c r="U282" s="3"/>
       <c r="V282" s="2"/>
-      <c r="W282" s="3"/>
+      <c r="W282" s="2"/>
       <c r="X282" s="3"/>
-      <c r="Y282" s="3"/>
+      <c r="Y282" s="2"/>
       <c r="Z282" s="3"/>
       <c r="AA282" s="4"/>
       <c r="AB282" s="5"/>
@@ -22030,11 +22029,11 @@
       <c r="AF282" s="4"/>
       <c r="AG282" s="3"/>
       <c r="AH282" s="2"/>
-      <c r="AI282" s="3"/>
+      <c r="AI282" s="2"/>
       <c r="AJ282" s="3"/>
       <c r="AK282" s="3"/>
-      <c r="AL282" s="3"/>
-      <c r="AM282" s="3"/>
+      <c r="AL282" s="18"/>
+      <c r="AM282" s="18"/>
       <c r="AN282" s="3"/>
       <c r="AO282" s="3"/>
       <c r="AP282" s="3"/>
@@ -22043,11 +22042,11 @@
       <c r="AS282" s="3"/>
       <c r="AT282" s="3"/>
       <c r="AU282" s="3"/>
-      <c r="AV282" s="2"/>
+      <c r="AV282" s="3"/>
       <c r="AW282" s="3"/>
       <c r="AX282" s="3"/>
-      <c r="AY282" s="3"/>
-      <c r="AZ282" s="3"/>
+      <c r="AY282" s="19"/>
+      <c r="AZ282" s="18"/>
       <c r="BA282" s="3"/>
       <c r="BB282" s="3"/>
       <c r="BC282" s="3"/>
@@ -22069,13 +22068,13 @@
       <c r="BS282" s="3"/>
       <c r="BT282" s="3"/>
     </row>
-    <row r="283" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="283" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="2"/>
-      <c r="B283" s="18"/>
+      <c r="B283" s="3"/>
       <c r="C283" s="3"/>
       <c r="D283" s="3"/>
       <c r="E283" s="2"/>
-      <c r="F283" s="18"/>
+      <c r="F283" s="2"/>
       <c r="G283" s="3"/>
       <c r="H283" s="3"/>
       <c r="I283" s="2"/>
@@ -22104,11 +22103,11 @@
       <c r="AF283" s="4"/>
       <c r="AG283" s="3"/>
       <c r="AH283" s="2"/>
-      <c r="AI283" s="2"/>
+      <c r="AI283" s="3"/>
       <c r="AJ283" s="3"/>
       <c r="AK283" s="3"/>
-      <c r="AL283" s="18"/>
-      <c r="AM283" s="18"/>
+      <c r="AL283" s="3"/>
+      <c r="AM283" s="3"/>
       <c r="AN283" s="3"/>
       <c r="AO283" s="3"/>
       <c r="AP283" s="3"/>
@@ -22120,8 +22119,8 @@
       <c r="AV283" s="3"/>
       <c r="AW283" s="3"/>
       <c r="AX283" s="3"/>
-      <c r="AY283" s="19"/>
-      <c r="AZ283" s="18"/>
+      <c r="AY283" s="3"/>
+      <c r="AZ283" s="3"/>
       <c r="BA283" s="3"/>
       <c r="BB283" s="3"/>
       <c r="BC283" s="3"/>
@@ -22148,7 +22147,7 @@
       <c r="B284" s="3"/>
       <c r="C284" s="3"/>
       <c r="D284" s="3"/>
-      <c r="E284" s="2"/>
+      <c r="E284" s="3"/>
       <c r="F284" s="2"/>
       <c r="G284" s="3"/>
       <c r="H284" s="3"/>
@@ -22222,7 +22221,7 @@
       <c r="B285" s="3"/>
       <c r="C285" s="3"/>
       <c r="D285" s="3"/>
-      <c r="E285" s="3"/>
+      <c r="E285" s="2"/>
       <c r="F285" s="2"/>
       <c r="G285" s="3"/>
       <c r="H285" s="3"/>
@@ -22238,7 +22237,7 @@
       <c r="R285" s="3"/>
       <c r="S285" s="3"/>
       <c r="T285" s="3"/>
-      <c r="U285" s="3"/>
+      <c r="U285" s="2"/>
       <c r="V285" s="2"/>
       <c r="W285" s="2"/>
       <c r="X285" s="3"/>
@@ -22252,7 +22251,7 @@
       <c r="AF285" s="4"/>
       <c r="AG285" s="3"/>
       <c r="AH285" s="2"/>
-      <c r="AI285" s="3"/>
+      <c r="AI285" s="2"/>
       <c r="AJ285" s="3"/>
       <c r="AK285" s="3"/>
       <c r="AL285" s="3"/>
@@ -22265,7 +22264,7 @@
       <c r="AS285" s="3"/>
       <c r="AT285" s="3"/>
       <c r="AU285" s="3"/>
-      <c r="AV285" s="3"/>
+      <c r="AV285" s="2"/>
       <c r="AW285" s="3"/>
       <c r="AX285" s="3"/>
       <c r="AY285" s="3"/>
@@ -22312,7 +22311,7 @@
       <c r="R286" s="3"/>
       <c r="S286" s="3"/>
       <c r="T286" s="3"/>
-      <c r="U286" s="2"/>
+      <c r="U286" s="3"/>
       <c r="V286" s="2"/>
       <c r="W286" s="2"/>
       <c r="X286" s="3"/>
@@ -22400,7 +22399,7 @@
       <c r="AF287" s="4"/>
       <c r="AG287" s="3"/>
       <c r="AH287" s="2"/>
-      <c r="AI287" s="2"/>
+      <c r="AI287" s="3"/>
       <c r="AJ287" s="3"/>
       <c r="AK287" s="3"/>
       <c r="AL287" s="3"/>
@@ -22534,7 +22533,7 @@
       <c r="R289" s="3"/>
       <c r="S289" s="3"/>
       <c r="T289" s="3"/>
-      <c r="U289" s="3"/>
+      <c r="U289" s="2"/>
       <c r="V289" s="2"/>
       <c r="W289" s="2"/>
       <c r="X289" s="3"/>
@@ -22548,7 +22547,7 @@
       <c r="AF289" s="4"/>
       <c r="AG289" s="3"/>
       <c r="AH289" s="2"/>
-      <c r="AI289" s="3"/>
+      <c r="AI289" s="2"/>
       <c r="AJ289" s="3"/>
       <c r="AK289" s="3"/>
       <c r="AL289" s="3"/>
@@ -22682,15 +22681,15 @@
       <c r="R291" s="3"/>
       <c r="S291" s="3"/>
       <c r="T291" s="3"/>
-      <c r="U291" s="2"/>
-      <c r="V291" s="2"/>
+      <c r="U291" s="3"/>
+      <c r="V291" s="3"/>
       <c r="W291" s="2"/>
       <c r="X291" s="3"/>
       <c r="Y291" s="2"/>
       <c r="Z291" s="3"/>
       <c r="AA291" s="4"/>
       <c r="AB291" s="5"/>
-      <c r="AC291" s="3"/>
+      <c r="AC291" s="2"/>
       <c r="AD291" s="3"/>
       <c r="AE291" s="3"/>
       <c r="AF291" s="4"/>
@@ -22740,7 +22739,7 @@
       <c r="B292" s="3"/>
       <c r="C292" s="3"/>
       <c r="D292" s="3"/>
-      <c r="E292" s="2"/>
+      <c r="E292" s="3"/>
       <c r="F292" s="2"/>
       <c r="G292" s="3"/>
       <c r="H292" s="3"/>
@@ -22770,7 +22769,7 @@
       <c r="AF292" s="4"/>
       <c r="AG292" s="3"/>
       <c r="AH292" s="2"/>
-      <c r="AI292" s="2"/>
+      <c r="AI292" s="3"/>
       <c r="AJ292" s="3"/>
       <c r="AK292" s="3"/>
       <c r="AL292" s="3"/>
@@ -22783,7 +22782,7 @@
       <c r="AS292" s="3"/>
       <c r="AT292" s="3"/>
       <c r="AU292" s="3"/>
-      <c r="AV292" s="2"/>
+      <c r="AV292" s="3"/>
       <c r="AW292" s="3"/>
       <c r="AX292" s="3"/>
       <c r="AY292" s="3"/>
@@ -22832,13 +22831,13 @@
       <c r="T293" s="3"/>
       <c r="U293" s="3"/>
       <c r="V293" s="3"/>
-      <c r="W293" s="2"/>
+      <c r="W293" s="3"/>
       <c r="X293" s="3"/>
       <c r="Y293" s="2"/>
       <c r="Z293" s="3"/>
       <c r="AA293" s="4"/>
       <c r="AB293" s="5"/>
-      <c r="AC293" s="2"/>
+      <c r="AC293" s="3"/>
       <c r="AD293" s="3"/>
       <c r="AE293" s="3"/>
       <c r="AF293" s="4"/>
@@ -22900,13 +22899,13 @@
       <c r="N294" s="2"/>
       <c r="O294" s="3"/>
       <c r="P294" s="3"/>
-      <c r="Q294" s="3"/>
+      <c r="Q294" s="2"/>
       <c r="R294" s="3"/>
       <c r="S294" s="3"/>
       <c r="T294" s="3"/>
       <c r="U294" s="3"/>
       <c r="V294" s="3"/>
-      <c r="W294" s="3"/>
+      <c r="W294" s="2"/>
       <c r="X294" s="3"/>
       <c r="Y294" s="2"/>
       <c r="Z294" s="3"/>
@@ -22917,7 +22916,7 @@
       <c r="AE294" s="3"/>
       <c r="AF294" s="4"/>
       <c r="AG294" s="3"/>
-      <c r="AH294" s="2"/>
+      <c r="AH294" s="3"/>
       <c r="AI294" s="3"/>
       <c r="AJ294" s="3"/>
       <c r="AK294" s="3"/>
@@ -23122,7 +23121,7 @@
       <c r="N297" s="2"/>
       <c r="O297" s="3"/>
       <c r="P297" s="3"/>
-      <c r="Q297" s="2"/>
+      <c r="Q297" s="3"/>
       <c r="R297" s="3"/>
       <c r="S297" s="3"/>
       <c r="T297" s="3"/>
@@ -23295,7 +23294,7 @@
       <c r="AM299" s="3"/>
       <c r="AN299" s="3"/>
       <c r="AO299" s="3"/>
-      <c r="AP299" s="3"/>
+      <c r="AP299" s="2"/>
       <c r="AQ299" s="3"/>
       <c r="AR299" s="3"/>
       <c r="AS299" s="3"/>
@@ -23350,7 +23349,7 @@
       <c r="T300" s="3"/>
       <c r="U300" s="3"/>
       <c r="V300" s="3"/>
-      <c r="W300" s="2"/>
+      <c r="W300" s="3"/>
       <c r="X300" s="3"/>
       <c r="Y300" s="2"/>
       <c r="Z300" s="3"/>
@@ -23361,7 +23360,7 @@
       <c r="AE300" s="3"/>
       <c r="AF300" s="4"/>
       <c r="AG300" s="3"/>
-      <c r="AH300" s="3"/>
+      <c r="AH300" s="2"/>
       <c r="AI300" s="3"/>
       <c r="AJ300" s="3"/>
       <c r="AK300" s="3"/>
@@ -23369,11 +23368,11 @@
       <c r="AM300" s="3"/>
       <c r="AN300" s="3"/>
       <c r="AO300" s="3"/>
-      <c r="AP300" s="2"/>
+      <c r="AP300" s="3"/>
       <c r="AQ300" s="3"/>
       <c r="AR300" s="3"/>
       <c r="AS300" s="3"/>
-      <c r="AT300" s="3"/>
+      <c r="AT300" s="2"/>
       <c r="AU300" s="3"/>
       <c r="AV300" s="3"/>
       <c r="AW300" s="3"/>
@@ -23520,10 +23519,10 @@
       <c r="AP302" s="3"/>
       <c r="AQ302" s="3"/>
       <c r="AR302" s="3"/>
-      <c r="AS302" s="3"/>
-      <c r="AT302" s="2"/>
+      <c r="AS302" s="2"/>
+      <c r="AT302" s="3"/>
       <c r="AU302" s="3"/>
-      <c r="AV302" s="3"/>
+      <c r="AV302" s="2"/>
       <c r="AW302" s="3"/>
       <c r="AX302" s="3"/>
       <c r="AY302" s="3"/>
@@ -23574,7 +23573,7 @@
       <c r="V303" s="3"/>
       <c r="W303" s="3"/>
       <c r="X303" s="3"/>
-      <c r="Y303" s="2"/>
+      <c r="Y303" s="3"/>
       <c r="Z303" s="3"/>
       <c r="AA303" s="4"/>
       <c r="AB303" s="5"/>
@@ -23594,7 +23593,7 @@
       <c r="AP303" s="3"/>
       <c r="AQ303" s="3"/>
       <c r="AR303" s="3"/>
-      <c r="AS303" s="2"/>
+      <c r="AS303" s="3"/>
       <c r="AT303" s="3"/>
       <c r="AU303" s="3"/>
       <c r="AV303" s="2"/>
@@ -23629,8 +23628,8 @@
       <c r="C304" s="3"/>
       <c r="D304" s="3"/>
       <c r="E304" s="3"/>
-      <c r="F304" s="2"/>
-      <c r="G304" s="3"/>
+      <c r="F304" s="3"/>
+      <c r="G304" s="2"/>
       <c r="H304" s="3"/>
       <c r="I304" s="2"/>
       <c r="J304" s="2"/>
@@ -23646,9 +23645,9 @@
       <c r="T304" s="3"/>
       <c r="U304" s="3"/>
       <c r="V304" s="3"/>
-      <c r="W304" s="3"/>
+      <c r="W304" s="2"/>
       <c r="X304" s="3"/>
-      <c r="Y304" s="3"/>
+      <c r="Y304" s="2"/>
       <c r="Z304" s="3"/>
       <c r="AA304" s="4"/>
       <c r="AB304" s="5"/>
@@ -23657,7 +23656,7 @@
       <c r="AE304" s="3"/>
       <c r="AF304" s="4"/>
       <c r="AG304" s="3"/>
-      <c r="AH304" s="2"/>
+      <c r="AH304" s="3"/>
       <c r="AI304" s="3"/>
       <c r="AJ304" s="3"/>
       <c r="AK304" s="3"/>
@@ -23671,7 +23670,7 @@
       <c r="AS304" s="3"/>
       <c r="AT304" s="3"/>
       <c r="AU304" s="3"/>
-      <c r="AV304" s="2"/>
+      <c r="AV304" s="3"/>
       <c r="AW304" s="3"/>
       <c r="AX304" s="3"/>
       <c r="AY304" s="3"/>
@@ -23703,7 +23702,7 @@
       <c r="C305" s="3"/>
       <c r="D305" s="3"/>
       <c r="E305" s="3"/>
-      <c r="F305" s="3"/>
+      <c r="F305" s="2"/>
       <c r="G305" s="2"/>
       <c r="H305" s="3"/>
       <c r="I305" s="2"/>
@@ -23852,7 +23851,7 @@
       <c r="D307" s="3"/>
       <c r="E307" s="3"/>
       <c r="F307" s="2"/>
-      <c r="G307" s="2"/>
+      <c r="G307" s="3"/>
       <c r="H307" s="3"/>
       <c r="I307" s="2"/>
       <c r="J307" s="2"/>
@@ -23869,7 +23868,7 @@
       <c r="U307" s="3"/>
       <c r="V307" s="3"/>
       <c r="W307" s="2"/>
-      <c r="X307" s="3"/>
+      <c r="X307" s="2"/>
       <c r="Y307" s="2"/>
       <c r="Z307" s="3"/>
       <c r="AA307" s="4"/>
@@ -23954,7 +23953,7 @@
       <c r="AF308" s="4"/>
       <c r="AG308" s="3"/>
       <c r="AH308" s="3"/>
-      <c r="AI308" s="3"/>
+      <c r="AI308" s="2"/>
       <c r="AJ308" s="3"/>
       <c r="AK308" s="3"/>
       <c r="AL308" s="3"/>
@@ -24016,9 +24015,9 @@
       <c r="T309" s="3"/>
       <c r="U309" s="3"/>
       <c r="V309" s="3"/>
-      <c r="W309" s="2"/>
-      <c r="X309" s="2"/>
-      <c r="Y309" s="2"/>
+      <c r="W309" s="3"/>
+      <c r="X309" s="3"/>
+      <c r="Y309" s="3"/>
       <c r="Z309" s="3"/>
       <c r="AA309" s="4"/>
       <c r="AB309" s="5"/>
@@ -24027,21 +24026,21 @@
       <c r="AE309" s="3"/>
       <c r="AF309" s="4"/>
       <c r="AG309" s="3"/>
-      <c r="AH309" s="3"/>
-      <c r="AI309" s="2"/>
+      <c r="AH309" s="2"/>
+      <c r="AI309" s="3"/>
       <c r="AJ309" s="3"/>
       <c r="AK309" s="3"/>
       <c r="AL309" s="3"/>
       <c r="AM309" s="3"/>
       <c r="AN309" s="3"/>
-      <c r="AO309" s="3"/>
+      <c r="AO309" s="2"/>
       <c r="AP309" s="3"/>
-      <c r="AQ309" s="3"/>
-      <c r="AR309" s="3"/>
+      <c r="AQ309" s="2"/>
+      <c r="AR309" s="2"/>
       <c r="AS309" s="3"/>
       <c r="AT309" s="3"/>
       <c r="AU309" s="3"/>
-      <c r="AV309" s="3"/>
+      <c r="AV309" s="2"/>
       <c r="AW309" s="3"/>
       <c r="AX309" s="3"/>
       <c r="AY309" s="3"/>
@@ -24079,10 +24078,10 @@
       <c r="I310" s="2"/>
       <c r="J310" s="2"/>
       <c r="K310" s="3"/>
-      <c r="L310" s="3"/>
+      <c r="L310" s="2"/>
       <c r="M310" s="2"/>
       <c r="N310" s="2"/>
-      <c r="O310" s="3"/>
+      <c r="O310" s="2"/>
       <c r="P310" s="3"/>
       <c r="Q310" s="3"/>
       <c r="R310" s="3"/>
@@ -24153,10 +24152,10 @@
       <c r="I311" s="2"/>
       <c r="J311" s="2"/>
       <c r="K311" s="3"/>
-      <c r="L311" s="2"/>
+      <c r="L311" s="3"/>
       <c r="M311" s="2"/>
       <c r="N311" s="2"/>
-      <c r="O311" s="2"/>
+      <c r="O311" s="3"/>
       <c r="P311" s="3"/>
       <c r="Q311" s="3"/>
       <c r="R311" s="3"/>
@@ -24170,7 +24169,7 @@
       <c r="Z311" s="3"/>
       <c r="AA311" s="4"/>
       <c r="AB311" s="5"/>
-      <c r="AC311" s="3"/>
+      <c r="AC311" s="2"/>
       <c r="AD311" s="3"/>
       <c r="AE311" s="3"/>
       <c r="AF311" s="4"/>
@@ -24226,11 +24225,11 @@
       <c r="H312" s="3"/>
       <c r="I312" s="2"/>
       <c r="J312" s="2"/>
-      <c r="K312" s="3"/>
-      <c r="L312" s="3"/>
+      <c r="K312" s="2"/>
+      <c r="L312" s="2"/>
       <c r="M312" s="2"/>
       <c r="N312" s="2"/>
-      <c r="O312" s="3"/>
+      <c r="O312" s="2"/>
       <c r="P312" s="3"/>
       <c r="Q312" s="3"/>
       <c r="R312" s="3"/>
@@ -24238,17 +24237,17 @@
       <c r="T312" s="3"/>
       <c r="U312" s="3"/>
       <c r="V312" s="3"/>
-      <c r="W312" s="3"/>
+      <c r="W312" s="2"/>
       <c r="X312" s="3"/>
-      <c r="Y312" s="3"/>
+      <c r="Y312" s="2"/>
       <c r="Z312" s="3"/>
       <c r="AA312" s="4"/>
       <c r="AB312" s="5"/>
-      <c r="AC312" s="2"/>
+      <c r="AC312" s="3"/>
       <c r="AD312" s="3"/>
       <c r="AE312" s="3"/>
       <c r="AF312" s="4"/>
-      <c r="AG312" s="3"/>
+      <c r="AG312" s="2"/>
       <c r="AH312" s="2"/>
       <c r="AI312" s="3"/>
       <c r="AJ312" s="3"/>
@@ -24259,11 +24258,11 @@
       <c r="AO312" s="2"/>
       <c r="AP312" s="3"/>
       <c r="AQ312" s="2"/>
-      <c r="AR312" s="2"/>
+      <c r="AR312" s="3"/>
       <c r="AS312" s="3"/>
       <c r="AT312" s="3"/>
       <c r="AU312" s="3"/>
-      <c r="AV312" s="2"/>
+      <c r="AV312" s="3"/>
       <c r="AW312" s="3"/>
       <c r="AX312" s="3"/>
       <c r="AY312" s="3"/>
@@ -24300,11 +24299,11 @@
       <c r="H313" s="3"/>
       <c r="I313" s="2"/>
       <c r="J313" s="2"/>
-      <c r="K313" s="2"/>
+      <c r="K313" s="3"/>
       <c r="L313" s="2"/>
-      <c r="M313" s="2"/>
-      <c r="N313" s="2"/>
-      <c r="O313" s="2"/>
+      <c r="M313" s="3"/>
+      <c r="N313" s="3"/>
+      <c r="O313" s="3"/>
       <c r="P313" s="3"/>
       <c r="Q313" s="3"/>
       <c r="R313" s="3"/>
@@ -24323,7 +24322,7 @@
       <c r="AE313" s="3"/>
       <c r="AF313" s="4"/>
       <c r="AG313" s="2"/>
-      <c r="AH313" s="2"/>
+      <c r="AH313" s="3"/>
       <c r="AI313" s="3"/>
       <c r="AJ313" s="3"/>
       <c r="AK313" s="3"/>
@@ -24332,7 +24331,7 @@
       <c r="AN313" s="3"/>
       <c r="AO313" s="2"/>
       <c r="AP313" s="3"/>
-      <c r="AQ313" s="2"/>
+      <c r="AQ313" s="3"/>
       <c r="AR313" s="3"/>
       <c r="AS313" s="3"/>
       <c r="AT313" s="3"/>
@@ -24375,9 +24374,9 @@
       <c r="I314" s="2"/>
       <c r="J314" s="2"/>
       <c r="K314" s="3"/>
-      <c r="L314" s="2"/>
-      <c r="M314" s="3"/>
-      <c r="N314" s="3"/>
+      <c r="L314" s="3"/>
+      <c r="M314" s="2"/>
+      <c r="N314" s="2"/>
       <c r="O314" s="3"/>
       <c r="P314" s="3"/>
       <c r="Q314" s="3"/>
@@ -24386,7 +24385,7 @@
       <c r="T314" s="3"/>
       <c r="U314" s="3"/>
       <c r="V314" s="3"/>
-      <c r="W314" s="2"/>
+      <c r="W314" s="3"/>
       <c r="X314" s="3"/>
       <c r="Y314" s="2"/>
       <c r="Z314" s="3"/>
@@ -24396,8 +24395,8 @@
       <c r="AD314" s="3"/>
       <c r="AE314" s="3"/>
       <c r="AF314" s="4"/>
-      <c r="AG314" s="2"/>
-      <c r="AH314" s="3"/>
+      <c r="AG314" s="3"/>
+      <c r="AH314" s="2"/>
       <c r="AI314" s="3"/>
       <c r="AJ314" s="3"/>
       <c r="AK314" s="3"/>
@@ -24460,7 +24459,7 @@
       <c r="T315" s="3"/>
       <c r="U315" s="3"/>
       <c r="V315" s="3"/>
-      <c r="W315" s="3"/>
+      <c r="W315" s="2"/>
       <c r="X315" s="3"/>
       <c r="Y315" s="2"/>
       <c r="Z315" s="3"/>
@@ -24526,7 +24525,7 @@
       <c r="L316" s="3"/>
       <c r="M316" s="2"/>
       <c r="N316" s="2"/>
-      <c r="O316" s="3"/>
+      <c r="O316" s="2"/>
       <c r="P316" s="3"/>
       <c r="Q316" s="3"/>
       <c r="R316" s="3"/>
@@ -24618,7 +24617,7 @@
       <c r="AD317" s="3"/>
       <c r="AE317" s="3"/>
       <c r="AF317" s="4"/>
-      <c r="AG317" s="3"/>
+      <c r="AG317" s="2"/>
       <c r="AH317" s="2"/>
       <c r="AI317" s="3"/>
       <c r="AJ317" s="3"/>
@@ -24748,7 +24747,7 @@
       <c r="L319" s="3"/>
       <c r="M319" s="2"/>
       <c r="N319" s="2"/>
-      <c r="O319" s="2"/>
+      <c r="O319" s="3"/>
       <c r="P319" s="3"/>
       <c r="Q319" s="3"/>
       <c r="R319" s="3"/>
@@ -24904,9 +24903,9 @@
       <c r="T321" s="3"/>
       <c r="U321" s="3"/>
       <c r="V321" s="3"/>
-      <c r="W321" s="2"/>
+      <c r="W321" s="3"/>
       <c r="X321" s="3"/>
-      <c r="Y321" s="2"/>
+      <c r="Y321" s="3"/>
       <c r="Z321" s="3"/>
       <c r="AA321" s="4"/>
       <c r="AB321" s="5"/>
@@ -24914,7 +24913,7 @@
       <c r="AD321" s="3"/>
       <c r="AE321" s="3"/>
       <c r="AF321" s="4"/>
-      <c r="AG321" s="2"/>
+      <c r="AG321" s="3"/>
       <c r="AH321" s="2"/>
       <c r="AI321" s="3"/>
       <c r="AJ321" s="3"/>
@@ -24924,7 +24923,7 @@
       <c r="AN321" s="3"/>
       <c r="AO321" s="2"/>
       <c r="AP321" s="3"/>
-      <c r="AQ321" s="3"/>
+      <c r="AQ321" s="2"/>
       <c r="AR321" s="3"/>
       <c r="AS321" s="3"/>
       <c r="AT321" s="3"/>
@@ -24970,7 +24969,7 @@
       <c r="L322" s="3"/>
       <c r="M322" s="2"/>
       <c r="N322" s="2"/>
-      <c r="O322" s="3"/>
+      <c r="O322" s="2"/>
       <c r="P322" s="3"/>
       <c r="Q322" s="3"/>
       <c r="R322" s="3"/>
@@ -24978,9 +24977,9 @@
       <c r="T322" s="3"/>
       <c r="U322" s="3"/>
       <c r="V322" s="3"/>
-      <c r="W322" s="3"/>
+      <c r="W322" s="2"/>
       <c r="X322" s="3"/>
-      <c r="Y322" s="3"/>
+      <c r="Y322" s="2"/>
       <c r="Z322" s="3"/>
       <c r="AA322" s="4"/>
       <c r="AB322" s="5"/>
@@ -24988,7 +24987,7 @@
       <c r="AD322" s="3"/>
       <c r="AE322" s="3"/>
       <c r="AF322" s="4"/>
-      <c r="AG322" s="3"/>
+      <c r="AG322" s="2"/>
       <c r="AH322" s="2"/>
       <c r="AI322" s="3"/>
       <c r="AJ322" s="3"/>
@@ -24998,7 +24997,7 @@
       <c r="AN322" s="3"/>
       <c r="AO322" s="2"/>
       <c r="AP322" s="3"/>
-      <c r="AQ322" s="2"/>
+      <c r="AQ322" s="3"/>
       <c r="AR322" s="3"/>
       <c r="AS322" s="3"/>
       <c r="AT322" s="3"/>
@@ -25072,7 +25071,7 @@
       <c r="AN323" s="3"/>
       <c r="AO323" s="2"/>
       <c r="AP323" s="3"/>
-      <c r="AQ323" s="3"/>
+      <c r="AQ323" s="2"/>
       <c r="AR323" s="3"/>
       <c r="AS323" s="3"/>
       <c r="AT323" s="3"/>
@@ -25146,7 +25145,7 @@
       <c r="AN324" s="3"/>
       <c r="AO324" s="2"/>
       <c r="AP324" s="3"/>
-      <c r="AQ324" s="2"/>
+      <c r="AQ324" s="3"/>
       <c r="AR324" s="3"/>
       <c r="AS324" s="3"/>
       <c r="AT324" s="3"/>
@@ -25189,10 +25188,10 @@
       <c r="I325" s="2"/>
       <c r="J325" s="2"/>
       <c r="K325" s="3"/>
-      <c r="L325" s="3"/>
+      <c r="L325" s="2"/>
       <c r="M325" s="2"/>
       <c r="N325" s="2"/>
-      <c r="O325" s="2"/>
+      <c r="O325" s="3"/>
       <c r="P325" s="3"/>
       <c r="Q325" s="3"/>
       <c r="R325" s="3"/>
@@ -25206,7 +25205,7 @@
       <c r="Z325" s="3"/>
       <c r="AA325" s="4"/>
       <c r="AB325" s="5"/>
-      <c r="AC325" s="3"/>
+      <c r="AC325" s="2"/>
       <c r="AD325" s="3"/>
       <c r="AE325" s="3"/>
       <c r="AF325" s="4"/>
@@ -25218,7 +25217,7 @@
       <c r="AL325" s="3"/>
       <c r="AM325" s="3"/>
       <c r="AN325" s="3"/>
-      <c r="AO325" s="2"/>
+      <c r="AO325" s="3"/>
       <c r="AP325" s="3"/>
       <c r="AQ325" s="3"/>
       <c r="AR325" s="3"/>
@@ -25421,18 +25420,18 @@
       <c r="S328" s="3"/>
       <c r="T328" s="3"/>
       <c r="U328" s="3"/>
-      <c r="V328" s="3"/>
+      <c r="V328" s="2"/>
       <c r="W328" s="2"/>
       <c r="X328" s="3"/>
-      <c r="Y328" s="2"/>
+      <c r="Y328" s="3"/>
       <c r="Z328" s="3"/>
       <c r="AA328" s="4"/>
       <c r="AB328" s="5"/>
-      <c r="AC328" s="2"/>
+      <c r="AC328" s="3"/>
       <c r="AD328" s="3"/>
       <c r="AE328" s="3"/>
       <c r="AF328" s="4"/>
-      <c r="AG328" s="2"/>
+      <c r="AG328" s="3"/>
       <c r="AH328" s="2"/>
       <c r="AI328" s="3"/>
       <c r="AJ328" s="3"/>
@@ -25440,9 +25439,9 @@
       <c r="AL328" s="3"/>
       <c r="AM328" s="3"/>
       <c r="AN328" s="3"/>
-      <c r="AO328" s="3"/>
+      <c r="AO328" s="2"/>
       <c r="AP328" s="3"/>
-      <c r="AQ328" s="3"/>
+      <c r="AQ328" s="2"/>
       <c r="AR328" s="3"/>
       <c r="AS328" s="3"/>
       <c r="AT328" s="3"/>
@@ -25495,14 +25494,14 @@
       <c r="S329" s="3"/>
       <c r="T329" s="3"/>
       <c r="U329" s="3"/>
-      <c r="V329" s="2"/>
-      <c r="W329" s="2"/>
+      <c r="V329" s="3"/>
+      <c r="W329" s="3"/>
       <c r="X329" s="3"/>
       <c r="Y329" s="3"/>
       <c r="Z329" s="3"/>
       <c r="AA329" s="4"/>
       <c r="AB329" s="5"/>
-      <c r="AC329" s="3"/>
+      <c r="AC329" s="2"/>
       <c r="AD329" s="3"/>
       <c r="AE329" s="3"/>
       <c r="AF329" s="4"/>
@@ -25549,7 +25548,7 @@
     </row>
     <row r="330" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="2"/>
-      <c r="B330" s="3"/>
+      <c r="B330" s="16"/>
       <c r="C330" s="3"/>
       <c r="D330" s="3"/>
       <c r="E330" s="3"/>
@@ -25562,7 +25561,7 @@
       <c r="L330" s="2"/>
       <c r="M330" s="2"/>
       <c r="N330" s="2"/>
-      <c r="O330" s="3"/>
+      <c r="O330" s="2"/>
       <c r="P330" s="3"/>
       <c r="Q330" s="3"/>
       <c r="R330" s="3"/>
@@ -25570,17 +25569,17 @@
       <c r="T330" s="3"/>
       <c r="U330" s="3"/>
       <c r="V330" s="3"/>
-      <c r="W330" s="3"/>
+      <c r="W330" s="2"/>
       <c r="X330" s="3"/>
-      <c r="Y330" s="3"/>
+      <c r="Y330" s="2"/>
       <c r="Z330" s="3"/>
       <c r="AA330" s="4"/>
       <c r="AB330" s="5"/>
-      <c r="AC330" s="2"/>
+      <c r="AC330" s="3"/>
       <c r="AD330" s="3"/>
       <c r="AE330" s="3"/>
       <c r="AF330" s="4"/>
-      <c r="AG330" s="3"/>
+      <c r="AG330" s="2"/>
       <c r="AH330" s="2"/>
       <c r="AI330" s="3"/>
       <c r="AJ330" s="3"/>
@@ -25590,7 +25589,7 @@
       <c r="AN330" s="3"/>
       <c r="AO330" s="2"/>
       <c r="AP330" s="3"/>
-      <c r="AQ330" s="2"/>
+      <c r="AQ330" s="3"/>
       <c r="AR330" s="3"/>
       <c r="AS330" s="3"/>
       <c r="AT330" s="3"/>
@@ -25623,7 +25622,7 @@
     </row>
     <row r="331" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="2"/>
-      <c r="B331" s="16"/>
+      <c r="B331" s="20"/>
       <c r="C331" s="3"/>
       <c r="D331" s="3"/>
       <c r="E331" s="3"/>
@@ -25697,7 +25696,7 @@
     </row>
     <row r="332" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="2"/>
-      <c r="B332" s="20"/>
+      <c r="B332" s="3"/>
       <c r="C332" s="3"/>
       <c r="D332" s="3"/>
       <c r="E332" s="3"/>
@@ -25728,7 +25727,7 @@
       <c r="AD332" s="3"/>
       <c r="AE332" s="3"/>
       <c r="AF332" s="4"/>
-      <c r="AG332" s="2"/>
+      <c r="AG332" s="3"/>
       <c r="AH332" s="2"/>
       <c r="AI332" s="3"/>
       <c r="AJ332" s="3"/>
@@ -25802,7 +25801,7 @@
       <c r="AD333" s="3"/>
       <c r="AE333" s="3"/>
       <c r="AF333" s="4"/>
-      <c r="AG333" s="3"/>
+      <c r="AG333" s="2"/>
       <c r="AH333" s="2"/>
       <c r="AI333" s="3"/>
       <c r="AJ333" s="3"/>
@@ -25876,7 +25875,7 @@
       <c r="AD334" s="3"/>
       <c r="AE334" s="3"/>
       <c r="AF334" s="4"/>
-      <c r="AG334" s="2"/>
+      <c r="AG334" s="3"/>
       <c r="AH334" s="2"/>
       <c r="AI334" s="3"/>
       <c r="AJ334" s="3"/>
@@ -25950,7 +25949,7 @@
       <c r="AD335" s="3"/>
       <c r="AE335" s="3"/>
       <c r="AF335" s="4"/>
-      <c r="AG335" s="3"/>
+      <c r="AG335" s="2"/>
       <c r="AH335" s="2"/>
       <c r="AI335" s="3"/>
       <c r="AJ335" s="3"/>
@@ -26006,7 +26005,7 @@
       <c r="L336" s="2"/>
       <c r="M336" s="2"/>
       <c r="N336" s="2"/>
-      <c r="O336" s="2"/>
+      <c r="O336" s="3"/>
       <c r="P336" s="3"/>
       <c r="Q336" s="3"/>
       <c r="R336" s="3"/>
@@ -26088,9 +26087,9 @@
       <c r="T337" s="3"/>
       <c r="U337" s="3"/>
       <c r="V337" s="3"/>
-      <c r="W337" s="2"/>
+      <c r="W337" s="3"/>
       <c r="X337" s="3"/>
-      <c r="Y337" s="2"/>
+      <c r="Y337" s="3"/>
       <c r="Z337" s="3"/>
       <c r="AA337" s="4"/>
       <c r="AB337" s="5"/>
@@ -26098,7 +26097,7 @@
       <c r="AD337" s="3"/>
       <c r="AE337" s="3"/>
       <c r="AF337" s="4"/>
-      <c r="AG337" s="2"/>
+      <c r="AG337" s="3"/>
       <c r="AH337" s="2"/>
       <c r="AI337" s="3"/>
       <c r="AJ337" s="3"/>
@@ -26256,7 +26255,7 @@
       <c r="AN339" s="3"/>
       <c r="AO339" s="2"/>
       <c r="AP339" s="3"/>
-      <c r="AQ339" s="3"/>
+      <c r="AQ339" s="2"/>
       <c r="AR339" s="3"/>
       <c r="AS339" s="3"/>
       <c r="AT339" s="3"/>
@@ -26299,7 +26298,7 @@
       <c r="I340" s="2"/>
       <c r="J340" s="2"/>
       <c r="K340" s="3"/>
-      <c r="L340" s="2"/>
+      <c r="L340" s="3"/>
       <c r="M340" s="2"/>
       <c r="N340" s="2"/>
       <c r="O340" s="3"/>
@@ -26310,9 +26309,9 @@
       <c r="T340" s="3"/>
       <c r="U340" s="3"/>
       <c r="V340" s="3"/>
-      <c r="W340" s="3"/>
+      <c r="W340" s="2"/>
       <c r="X340" s="3"/>
-      <c r="Y340" s="3"/>
+      <c r="Y340" s="2"/>
       <c r="Z340" s="3"/>
       <c r="AA340" s="4"/>
       <c r="AB340" s="5"/>
@@ -26330,7 +26329,7 @@
       <c r="AN340" s="3"/>
       <c r="AO340" s="2"/>
       <c r="AP340" s="3"/>
-      <c r="AQ340" s="2"/>
+      <c r="AQ340" s="3"/>
       <c r="AR340" s="3"/>
       <c r="AS340" s="3"/>
       <c r="AT340" s="3"/>
@@ -26339,7 +26338,7 @@
       <c r="AW340" s="3"/>
       <c r="AX340" s="3"/>
       <c r="AY340" s="3"/>
-      <c r="AZ340" s="3"/>
+      <c r="AZ340" s="2"/>
       <c r="BA340" s="3"/>
       <c r="BB340" s="3"/>
       <c r="BC340" s="3"/>
@@ -26382,11 +26381,11 @@
       <c r="R341" s="3"/>
       <c r="S341" s="3"/>
       <c r="T341" s="3"/>
-      <c r="U341" s="3"/>
-      <c r="V341" s="3"/>
+      <c r="U341" s="2"/>
+      <c r="V341" s="12"/>
       <c r="W341" s="2"/>
       <c r="X341" s="3"/>
-      <c r="Y341" s="2"/>
+      <c r="Y341" s="3"/>
       <c r="Z341" s="3"/>
       <c r="AA341" s="4"/>
       <c r="AB341" s="5"/>
@@ -26404,7 +26403,7 @@
       <c r="AN341" s="3"/>
       <c r="AO341" s="2"/>
       <c r="AP341" s="3"/>
-      <c r="AQ341" s="3"/>
+      <c r="AQ341" s="2"/>
       <c r="AR341" s="3"/>
       <c r="AS341" s="3"/>
       <c r="AT341" s="3"/>
@@ -26413,7 +26412,7 @@
       <c r="AW341" s="3"/>
       <c r="AX341" s="3"/>
       <c r="AY341" s="3"/>
-      <c r="AZ341" s="2"/>
+      <c r="AZ341" s="3"/>
       <c r="BA341" s="3"/>
       <c r="BB341" s="3"/>
       <c r="BC341" s="3"/>
@@ -26446,21 +26445,21 @@
       <c r="H342" s="3"/>
       <c r="I342" s="2"/>
       <c r="J342" s="2"/>
-      <c r="K342" s="3"/>
-      <c r="L342" s="3"/>
+      <c r="K342" s="2"/>
+      <c r="L342" s="2"/>
       <c r="M342" s="2"/>
       <c r="N342" s="2"/>
-      <c r="O342" s="3"/>
+      <c r="O342" s="2"/>
       <c r="P342" s="3"/>
       <c r="Q342" s="3"/>
       <c r="R342" s="3"/>
       <c r="S342" s="3"/>
       <c r="T342" s="3"/>
-      <c r="U342" s="2"/>
-      <c r="V342" s="12"/>
+      <c r="U342" s="3"/>
+      <c r="V342" s="3"/>
       <c r="W342" s="2"/>
       <c r="X342" s="3"/>
-      <c r="Y342" s="3"/>
+      <c r="Y342" s="2"/>
       <c r="Z342" s="3"/>
       <c r="AA342" s="4"/>
       <c r="AB342" s="5"/>
@@ -26468,7 +26467,7 @@
       <c r="AD342" s="3"/>
       <c r="AE342" s="3"/>
       <c r="AF342" s="4"/>
-      <c r="AG342" s="3"/>
+      <c r="AG342" s="2"/>
       <c r="AH342" s="2"/>
       <c r="AI342" s="3"/>
       <c r="AJ342" s="3"/>
@@ -26810,17 +26809,17 @@
       <c r="B347" s="3"/>
       <c r="C347" s="3"/>
       <c r="D347" s="3"/>
-      <c r="E347" s="3"/>
+      <c r="E347" s="2"/>
       <c r="F347" s="2"/>
       <c r="G347" s="3"/>
       <c r="H347" s="3"/>
       <c r="I347" s="2"/>
       <c r="J347" s="2"/>
-      <c r="K347" s="2"/>
-      <c r="L347" s="2"/>
+      <c r="K347" s="3"/>
+      <c r="L347" s="3"/>
       <c r="M347" s="2"/>
       <c r="N347" s="2"/>
-      <c r="O347" s="2"/>
+      <c r="O347" s="3"/>
       <c r="P347" s="3"/>
       <c r="Q347" s="3"/>
       <c r="R347" s="3"/>
@@ -26838,22 +26837,22 @@
       <c r="AD347" s="3"/>
       <c r="AE347" s="3"/>
       <c r="AF347" s="4"/>
-      <c r="AG347" s="2"/>
-      <c r="AH347" s="2"/>
+      <c r="AG347" s="3"/>
+      <c r="AH347" s="3"/>
       <c r="AI347" s="3"/>
       <c r="AJ347" s="3"/>
       <c r="AK347" s="3"/>
       <c r="AL347" s="3"/>
       <c r="AM347" s="3"/>
       <c r="AN347" s="3"/>
-      <c r="AO347" s="2"/>
+      <c r="AO347" s="3"/>
       <c r="AP347" s="3"/>
-      <c r="AQ347" s="2"/>
+      <c r="AQ347" s="3"/>
       <c r="AR347" s="3"/>
       <c r="AS347" s="3"/>
       <c r="AT347" s="3"/>
       <c r="AU347" s="3"/>
-      <c r="AV347" s="3"/>
+      <c r="AV347" s="2"/>
       <c r="AW347" s="3"/>
       <c r="AX347" s="3"/>
       <c r="AY347" s="3"/>
@@ -26884,7 +26883,7 @@
       <c r="B348" s="3"/>
       <c r="C348" s="3"/>
       <c r="D348" s="3"/>
-      <c r="E348" s="2"/>
+      <c r="E348" s="3"/>
       <c r="F348" s="2"/>
       <c r="G348" s="3"/>
       <c r="H348" s="3"/>
@@ -26904,7 +26903,7 @@
       <c r="V348" s="3"/>
       <c r="W348" s="2"/>
       <c r="X348" s="3"/>
-      <c r="Y348" s="2"/>
+      <c r="Y348" s="3"/>
       <c r="Z348" s="3"/>
       <c r="AA348" s="4"/>
       <c r="AB348" s="5"/>
@@ -26958,7 +26957,7 @@
       <c r="B349" s="3"/>
       <c r="C349" s="3"/>
       <c r="D349" s="3"/>
-      <c r="E349" s="3"/>
+      <c r="E349" s="2"/>
       <c r="F349" s="2"/>
       <c r="G349" s="3"/>
       <c r="H349" s="3"/>
@@ -26978,7 +26977,7 @@
       <c r="V349" s="3"/>
       <c r="W349" s="2"/>
       <c r="X349" s="3"/>
-      <c r="Y349" s="3"/>
+      <c r="Y349" s="2"/>
       <c r="Z349" s="3"/>
       <c r="AA349" s="4"/>
       <c r="AB349" s="5"/>
@@ -26987,7 +26986,7 @@
       <c r="AE349" s="3"/>
       <c r="AF349" s="4"/>
       <c r="AG349" s="3"/>
-      <c r="AH349" s="3"/>
+      <c r="AH349" s="2"/>
       <c r="AI349" s="3"/>
       <c r="AJ349" s="3"/>
       <c r="AK349" s="3"/>
@@ -26998,7 +26997,7 @@
       <c r="AP349" s="3"/>
       <c r="AQ349" s="3"/>
       <c r="AR349" s="3"/>
-      <c r="AS349" s="3"/>
+      <c r="AS349" s="2"/>
       <c r="AT349" s="3"/>
       <c r="AU349" s="3"/>
       <c r="AV349" s="2"/>
@@ -27032,7 +27031,7 @@
       <c r="B350" s="3"/>
       <c r="C350" s="3"/>
       <c r="D350" s="3"/>
-      <c r="E350" s="2"/>
+      <c r="E350" s="3"/>
       <c r="F350" s="2"/>
       <c r="G350" s="3"/>
       <c r="H350" s="3"/>
@@ -27061,7 +27060,7 @@
       <c r="AE350" s="3"/>
       <c r="AF350" s="4"/>
       <c r="AG350" s="3"/>
-      <c r="AH350" s="2"/>
+      <c r="AH350" s="3"/>
       <c r="AI350" s="3"/>
       <c r="AJ350" s="3"/>
       <c r="AK350" s="3"/>
@@ -27072,7 +27071,7 @@
       <c r="AP350" s="3"/>
       <c r="AQ350" s="3"/>
       <c r="AR350" s="3"/>
-      <c r="AS350" s="2"/>
+      <c r="AS350" s="3"/>
       <c r="AT350" s="3"/>
       <c r="AU350" s="3"/>
       <c r="AV350" s="2"/>
@@ -27422,7 +27421,7 @@
       <c r="V355" s="3"/>
       <c r="W355" s="2"/>
       <c r="X355" s="3"/>
-      <c r="Y355" s="2"/>
+      <c r="Y355" s="3"/>
       <c r="Z355" s="3"/>
       <c r="AA355" s="4"/>
       <c r="AB355" s="5"/>
@@ -27517,7 +27516,7 @@
       <c r="AQ356" s="3"/>
       <c r="AR356" s="3"/>
       <c r="AS356" s="3"/>
-      <c r="AT356" s="3"/>
+      <c r="AT356" s="12"/>
       <c r="AU356" s="3"/>
       <c r="AV356" s="2"/>
       <c r="AW356" s="3"/>
@@ -27739,7 +27738,7 @@
       <c r="AQ359" s="3"/>
       <c r="AR359" s="3"/>
       <c r="AS359" s="3"/>
-      <c r="AT359" s="12"/>
+      <c r="AT359" s="3"/>
       <c r="AU359" s="3"/>
       <c r="AV359" s="2"/>
       <c r="AW359" s="3"/>
@@ -27866,7 +27865,7 @@
       <c r="V361" s="3"/>
       <c r="W361" s="2"/>
       <c r="X361" s="3"/>
-      <c r="Y361" s="3"/>
+      <c r="Y361" s="2"/>
       <c r="Z361" s="3"/>
       <c r="AA361" s="4"/>
       <c r="AB361" s="5"/>
@@ -28216,7 +28215,7 @@
       <c r="B366" s="3"/>
       <c r="C366" s="3"/>
       <c r="D366" s="3"/>
-      <c r="E366" s="3"/>
+      <c r="E366" s="2"/>
       <c r="F366" s="2"/>
       <c r="G366" s="3"/>
       <c r="H366" s="3"/>
@@ -28233,7 +28232,7 @@
       <c r="S366" s="3"/>
       <c r="T366" s="3"/>
       <c r="U366" s="3"/>
-      <c r="V366" s="3"/>
+      <c r="V366" s="2"/>
       <c r="W366" s="2"/>
       <c r="X366" s="3"/>
       <c r="Y366" s="2"/>
@@ -28291,8 +28290,8 @@
       <c r="C367" s="3"/>
       <c r="D367" s="3"/>
       <c r="E367" s="2"/>
-      <c r="F367" s="2"/>
-      <c r="G367" s="3"/>
+      <c r="F367" s="3"/>
+      <c r="G367" s="2"/>
       <c r="H367" s="3"/>
       <c r="I367" s="2"/>
       <c r="J367" s="2"/>
@@ -28307,7 +28306,7 @@
       <c r="S367" s="3"/>
       <c r="T367" s="3"/>
       <c r="U367" s="3"/>
-      <c r="V367" s="2"/>
+      <c r="V367" s="3"/>
       <c r="W367" s="2"/>
       <c r="X367" s="3"/>
       <c r="Y367" s="2"/>
@@ -28360,13 +28359,13 @@
       <c r="BT367" s="3"/>
     </row>
     <row r="368" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A368" s="2"/>
+      <c r="A368" s="13"/>
       <c r="B368" s="3"/>
       <c r="C368" s="3"/>
       <c r="D368" s="3"/>
-      <c r="E368" s="2"/>
-      <c r="F368" s="3"/>
-      <c r="G368" s="2"/>
+      <c r="E368" s="3"/>
+      <c r="F368" s="13"/>
+      <c r="G368" s="3"/>
       <c r="H368" s="3"/>
       <c r="I368" s="2"/>
       <c r="J368" s="2"/>
@@ -28434,12 +28433,12 @@
       <c r="BT368" s="3"/>
     </row>
     <row r="369" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A369" s="13"/>
+      <c r="A369" s="2"/>
       <c r="B369" s="3"/>
       <c r="C369" s="3"/>
       <c r="D369" s="3"/>
-      <c r="E369" s="3"/>
-      <c r="F369" s="13"/>
+      <c r="E369" s="2"/>
+      <c r="F369" s="2"/>
       <c r="G369" s="3"/>
       <c r="H369" s="3"/>
       <c r="I369" s="2"/>
@@ -28512,7 +28511,7 @@
       <c r="B370" s="3"/>
       <c r="C370" s="3"/>
       <c r="D370" s="3"/>
-      <c r="E370" s="2"/>
+      <c r="E370" s="3"/>
       <c r="F370" s="2"/>
       <c r="G370" s="3"/>
       <c r="H370" s="3"/>
@@ -28754,7 +28753,7 @@
       <c r="V373" s="3"/>
       <c r="W373" s="2"/>
       <c r="X373" s="3"/>
-      <c r="Y373" s="2"/>
+      <c r="Y373" s="3"/>
       <c r="Z373" s="3"/>
       <c r="AA373" s="4"/>
       <c r="AB373" s="5"/>
@@ -28808,7 +28807,7 @@
       <c r="B374" s="3"/>
       <c r="C374" s="3"/>
       <c r="D374" s="3"/>
-      <c r="E374" s="3"/>
+      <c r="E374" s="2"/>
       <c r="F374" s="2"/>
       <c r="G374" s="3"/>
       <c r="H374" s="3"/>
@@ -28828,7 +28827,7 @@
       <c r="V374" s="3"/>
       <c r="W374" s="2"/>
       <c r="X374" s="3"/>
-      <c r="Y374" s="3"/>
+      <c r="Y374" s="2"/>
       <c r="Z374" s="3"/>
       <c r="AA374" s="4"/>
       <c r="AB374" s="5"/>
@@ -28848,7 +28847,7 @@
       <c r="AP374" s="3"/>
       <c r="AQ374" s="3"/>
       <c r="AR374" s="3"/>
-      <c r="AS374" s="3"/>
+      <c r="AS374" s="2"/>
       <c r="AT374" s="3"/>
       <c r="AU374" s="3"/>
       <c r="AV374" s="2"/>
@@ -28956,7 +28955,7 @@
       <c r="B376" s="3"/>
       <c r="C376" s="3"/>
       <c r="D376" s="3"/>
-      <c r="E376" s="2"/>
+      <c r="E376" s="3"/>
       <c r="F376" s="2"/>
       <c r="G376" s="3"/>
       <c r="H376" s="3"/>
@@ -28973,7 +28972,7 @@
       <c r="S376" s="3"/>
       <c r="T376" s="3"/>
       <c r="U376" s="3"/>
-      <c r="V376" s="3"/>
+      <c r="V376" s="21"/>
       <c r="W376" s="2"/>
       <c r="X376" s="3"/>
       <c r="Y376" s="2"/>
@@ -28996,10 +28995,10 @@
       <c r="AP376" s="3"/>
       <c r="AQ376" s="3"/>
       <c r="AR376" s="3"/>
-      <c r="AS376" s="2"/>
+      <c r="AS376" s="3"/>
       <c r="AT376" s="3"/>
       <c r="AU376" s="3"/>
-      <c r="AV376" s="2"/>
+      <c r="AV376" s="3"/>
       <c r="AW376" s="3"/>
       <c r="AX376" s="3"/>
       <c r="AY376" s="3"/>
@@ -29121,7 +29120,7 @@
       <c r="S378" s="3"/>
       <c r="T378" s="3"/>
       <c r="U378" s="3"/>
-      <c r="V378" s="21"/>
+      <c r="V378" s="3"/>
       <c r="W378" s="2"/>
       <c r="X378" s="3"/>
       <c r="Y378" s="2"/>
@@ -29147,7 +29146,7 @@
       <c r="AS378" s="3"/>
       <c r="AT378" s="3"/>
       <c r="AU378" s="3"/>
-      <c r="AV378" s="3"/>
+      <c r="AV378" s="2"/>
       <c r="AW378" s="3"/>
       <c r="AX378" s="3"/>
       <c r="AY378" s="3"/>
@@ -29178,7 +29177,7 @@
       <c r="B379" s="3"/>
       <c r="C379" s="3"/>
       <c r="D379" s="3"/>
-      <c r="E379" s="3"/>
+      <c r="E379" s="2"/>
       <c r="F379" s="2"/>
       <c r="G379" s="3"/>
       <c r="H379" s="3"/>
@@ -29373,7 +29372,7 @@
       <c r="AW381" s="3"/>
       <c r="AX381" s="3"/>
       <c r="AY381" s="3"/>
-      <c r="AZ381" s="3"/>
+      <c r="AZ381" s="2"/>
       <c r="BA381" s="3"/>
       <c r="BB381" s="3"/>
       <c r="BC381" s="3"/>
@@ -29447,7 +29446,7 @@
       <c r="AW382" s="3"/>
       <c r="AX382" s="3"/>
       <c r="AY382" s="3"/>
-      <c r="AZ382" s="2"/>
+      <c r="AZ382" s="3"/>
       <c r="BA382" s="3"/>
       <c r="BB382" s="3"/>
       <c r="BC382" s="3"/>
@@ -29474,7 +29473,7 @@
       <c r="B383" s="3"/>
       <c r="C383" s="3"/>
       <c r="D383" s="3"/>
-      <c r="E383" s="2"/>
+      <c r="E383" s="3"/>
       <c r="F383" s="2"/>
       <c r="G383" s="3"/>
       <c r="H383" s="3"/>
@@ -29696,9 +29695,9 @@
       <c r="B386" s="3"/>
       <c r="C386" s="3"/>
       <c r="D386" s="3"/>
-      <c r="E386" s="3"/>
-      <c r="F386" s="2"/>
-      <c r="G386" s="3"/>
+      <c r="E386" s="2"/>
+      <c r="F386" s="3"/>
+      <c r="G386" s="2"/>
       <c r="H386" s="3"/>
       <c r="I386" s="2"/>
       <c r="J386" s="2"/>
@@ -29771,8 +29770,8 @@
       <c r="C387" s="3"/>
       <c r="D387" s="3"/>
       <c r="E387" s="2"/>
-      <c r="F387" s="3"/>
-      <c r="G387" s="2"/>
+      <c r="F387" s="2"/>
+      <c r="G387" s="3"/>
       <c r="H387" s="3"/>
       <c r="I387" s="2"/>
       <c r="J387" s="2"/>
@@ -29845,8 +29844,8 @@
       <c r="C388" s="3"/>
       <c r="D388" s="3"/>
       <c r="E388" s="2"/>
-      <c r="F388" s="2"/>
-      <c r="G388" s="3"/>
+      <c r="F388" s="3"/>
+      <c r="G388" s="2"/>
       <c r="H388" s="3"/>
       <c r="I388" s="2"/>
       <c r="J388" s="2"/>
@@ -29992,9 +29991,9 @@
       <c r="B390" s="3"/>
       <c r="C390" s="3"/>
       <c r="D390" s="3"/>
-      <c r="E390" s="2"/>
-      <c r="F390" s="3"/>
-      <c r="G390" s="2"/>
+      <c r="E390" s="3"/>
+      <c r="F390" s="2"/>
+      <c r="G390" s="3"/>
       <c r="H390" s="3"/>
       <c r="I390" s="2"/>
       <c r="J390" s="2"/>
@@ -30006,7 +30005,7 @@
       <c r="P390" s="3"/>
       <c r="Q390" s="3"/>
       <c r="R390" s="3"/>
-      <c r="S390" s="3"/>
+      <c r="S390" s="2"/>
       <c r="T390" s="3"/>
       <c r="U390" s="3"/>
       <c r="V390" s="3"/>
@@ -30021,7 +30020,7 @@
       <c r="AE390" s="3"/>
       <c r="AF390" s="4"/>
       <c r="AG390" s="3"/>
-      <c r="AH390" s="3"/>
+      <c r="AH390" s="2"/>
       <c r="AI390" s="3"/>
       <c r="AJ390" s="3"/>
       <c r="AK390" s="3"/>
@@ -30035,7 +30034,7 @@
       <c r="AS390" s="3"/>
       <c r="AT390" s="3"/>
       <c r="AU390" s="3"/>
-      <c r="AV390" s="2"/>
+      <c r="AV390" s="3"/>
       <c r="AW390" s="3"/>
       <c r="AX390" s="3"/>
       <c r="AY390" s="3"/>
@@ -30140,7 +30139,7 @@
       <c r="B392" s="3"/>
       <c r="C392" s="3"/>
       <c r="D392" s="3"/>
-      <c r="E392" s="3"/>
+      <c r="E392" s="2"/>
       <c r="F392" s="2"/>
       <c r="G392" s="3"/>
       <c r="H392" s="3"/>
@@ -30154,7 +30153,7 @@
       <c r="P392" s="3"/>
       <c r="Q392" s="3"/>
       <c r="R392" s="3"/>
-      <c r="S392" s="2"/>
+      <c r="S392" s="3"/>
       <c r="T392" s="3"/>
       <c r="U392" s="3"/>
       <c r="V392" s="3"/>
@@ -30169,7 +30168,7 @@
       <c r="AE392" s="3"/>
       <c r="AF392" s="4"/>
       <c r="AG392" s="3"/>
-      <c r="AH392" s="2"/>
+      <c r="AH392" s="3"/>
       <c r="AI392" s="3"/>
       <c r="AJ392" s="3"/>
       <c r="AK392" s="3"/>
@@ -30183,7 +30182,7 @@
       <c r="AS392" s="3"/>
       <c r="AT392" s="3"/>
       <c r="AU392" s="3"/>
-      <c r="AV392" s="3"/>
+      <c r="AV392" s="2"/>
       <c r="AW392" s="3"/>
       <c r="AX392" s="3"/>
       <c r="AY392" s="3"/>
@@ -30288,7 +30287,7 @@
       <c r="B394" s="3"/>
       <c r="C394" s="3"/>
       <c r="D394" s="3"/>
-      <c r="E394" s="2"/>
+      <c r="E394" s="3"/>
       <c r="F394" s="2"/>
       <c r="G394" s="3"/>
       <c r="H394" s="3"/>
@@ -30362,7 +30361,7 @@
       <c r="B395" s="3"/>
       <c r="C395" s="3"/>
       <c r="D395" s="3"/>
-      <c r="E395" s="3"/>
+      <c r="E395" s="2"/>
       <c r="F395" s="2"/>
       <c r="G395" s="3"/>
       <c r="H395" s="3"/>
@@ -30452,8 +30451,8 @@
       <c r="R396" s="3"/>
       <c r="S396" s="3"/>
       <c r="T396" s="3"/>
-      <c r="U396" s="3"/>
-      <c r="V396" s="3"/>
+      <c r="U396" s="2"/>
+      <c r="V396" s="12"/>
       <c r="W396" s="2"/>
       <c r="X396" s="3"/>
       <c r="Y396" s="2"/>
@@ -30584,7 +30583,7 @@
       <c r="B398" s="3"/>
       <c r="C398" s="3"/>
       <c r="D398" s="3"/>
-      <c r="E398" s="2"/>
+      <c r="E398" s="3"/>
       <c r="F398" s="2"/>
       <c r="G398" s="3"/>
       <c r="H398" s="3"/>
@@ -30600,8 +30599,8 @@
       <c r="R398" s="3"/>
       <c r="S398" s="3"/>
       <c r="T398" s="3"/>
-      <c r="U398" s="2"/>
-      <c r="V398" s="12"/>
+      <c r="U398" s="3"/>
+      <c r="V398" s="3"/>
       <c r="W398" s="2"/>
       <c r="X398" s="3"/>
       <c r="Y398" s="2"/>
@@ -30701,7 +30700,7 @@
       <c r="AS399" s="3"/>
       <c r="AT399" s="3"/>
       <c r="AU399" s="3"/>
-      <c r="AV399" s="2"/>
+      <c r="AV399" s="3"/>
       <c r="AW399" s="3"/>
       <c r="AX399" s="3"/>
       <c r="AY399" s="3"/>
@@ -30775,7 +30774,7 @@
       <c r="AS400" s="3"/>
       <c r="AT400" s="3"/>
       <c r="AU400" s="3"/>
-      <c r="AV400" s="3"/>
+      <c r="AV400" s="2"/>
       <c r="AW400" s="3"/>
       <c r="AX400" s="3"/>
       <c r="AY400" s="3"/>
@@ -30880,7 +30879,7 @@
       <c r="B402" s="3"/>
       <c r="C402" s="3"/>
       <c r="D402" s="3"/>
-      <c r="E402" s="3"/>
+      <c r="E402" s="2"/>
       <c r="F402" s="2"/>
       <c r="G402" s="3"/>
       <c r="H402" s="3"/>
@@ -30973,8 +30972,8 @@
       <c r="U403" s="3"/>
       <c r="V403" s="3"/>
       <c r="W403" s="2"/>
-      <c r="X403" s="3"/>
-      <c r="Y403" s="2"/>
+      <c r="X403" s="2"/>
+      <c r="Y403" s="3"/>
       <c r="Z403" s="3"/>
       <c r="AA403" s="4"/>
       <c r="AB403" s="5"/>
@@ -31047,7 +31046,7 @@
       <c r="U404" s="3"/>
       <c r="V404" s="3"/>
       <c r="W404" s="2"/>
-      <c r="X404" s="2"/>
+      <c r="X404" s="3"/>
       <c r="Y404" s="3"/>
       <c r="Z404" s="3"/>
       <c r="AA404" s="4"/>
@@ -31122,7 +31121,7 @@
       <c r="V405" s="3"/>
       <c r="W405" s="2"/>
       <c r="X405" s="3"/>
-      <c r="Y405" s="3"/>
+      <c r="Y405" s="2"/>
       <c r="Z405" s="3"/>
       <c r="AA405" s="4"/>
       <c r="AB405" s="5"/>
@@ -31174,12 +31173,12 @@
     <row r="406" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="2"/>
       <c r="B406" s="3"/>
-      <c r="C406" s="3"/>
+      <c r="C406" s="2"/>
       <c r="D406" s="3"/>
-      <c r="E406" s="2"/>
-      <c r="F406" s="2"/>
-      <c r="G406" s="3"/>
-      <c r="H406" s="3"/>
+      <c r="E406" s="3"/>
+      <c r="F406" s="3"/>
+      <c r="G406" s="2"/>
+      <c r="H406" s="2"/>
       <c r="I406" s="2"/>
       <c r="J406" s="2"/>
       <c r="K406" s="3"/>
@@ -31191,7 +31190,7 @@
       <c r="Q406" s="3"/>
       <c r="R406" s="3"/>
       <c r="S406" s="3"/>
-      <c r="T406" s="3"/>
+      <c r="T406" s="2"/>
       <c r="U406" s="3"/>
       <c r="V406" s="3"/>
       <c r="W406" s="2"/>
@@ -31205,7 +31204,7 @@
       <c r="AE406" s="3"/>
       <c r="AF406" s="4"/>
       <c r="AG406" s="3"/>
-      <c r="AH406" s="3"/>
+      <c r="AH406" s="2"/>
       <c r="AI406" s="3"/>
       <c r="AJ406" s="3"/>
       <c r="AK406" s="3"/>
@@ -31223,7 +31222,7 @@
       <c r="AW406" s="3"/>
       <c r="AX406" s="3"/>
       <c r="AY406" s="3"/>
-      <c r="AZ406" s="3"/>
+      <c r="AZ406" s="2"/>
       <c r="BA406" s="3"/>
       <c r="BB406" s="3"/>
       <c r="BC406" s="3"/>
@@ -31248,12 +31247,12 @@
     <row r="407" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="2"/>
       <c r="B407" s="3"/>
-      <c r="C407" s="2"/>
+      <c r="C407" s="3"/>
       <c r="D407" s="3"/>
       <c r="E407" s="3"/>
-      <c r="F407" s="3"/>
-      <c r="G407" s="2"/>
-      <c r="H407" s="2"/>
+      <c r="F407" s="2"/>
+      <c r="G407" s="3"/>
+      <c r="H407" s="3"/>
       <c r="I407" s="2"/>
       <c r="J407" s="2"/>
       <c r="K407" s="3"/>
@@ -31265,16 +31264,16 @@
       <c r="Q407" s="3"/>
       <c r="R407" s="3"/>
       <c r="S407" s="3"/>
-      <c r="T407" s="2"/>
+      <c r="T407" s="3"/>
       <c r="U407" s="3"/>
-      <c r="V407" s="3"/>
+      <c r="V407" s="2"/>
       <c r="W407" s="2"/>
       <c r="X407" s="3"/>
       <c r="Y407" s="2"/>
       <c r="Z407" s="3"/>
       <c r="AA407" s="4"/>
       <c r="AB407" s="5"/>
-      <c r="AC407" s="3"/>
+      <c r="AC407" s="2"/>
       <c r="AD407" s="3"/>
       <c r="AE407" s="3"/>
       <c r="AF407" s="4"/>
@@ -31293,11 +31292,11 @@
       <c r="AS407" s="3"/>
       <c r="AT407" s="3"/>
       <c r="AU407" s="3"/>
-      <c r="AV407" s="2"/>
+      <c r="AV407" s="3"/>
       <c r="AW407" s="3"/>
       <c r="AX407" s="3"/>
       <c r="AY407" s="3"/>
-      <c r="AZ407" s="2"/>
+      <c r="AZ407" s="3"/>
       <c r="BA407" s="3"/>
       <c r="BB407" s="3"/>
       <c r="BC407" s="3"/>
@@ -31553,7 +31552,7 @@
       <c r="I411" s="2"/>
       <c r="J411" s="2"/>
       <c r="K411" s="3"/>
-      <c r="L411" s="3"/>
+      <c r="L411" s="2"/>
       <c r="M411" s="2"/>
       <c r="N411" s="2"/>
       <c r="O411" s="3"/>
@@ -31627,7 +31626,7 @@
       <c r="I412" s="2"/>
       <c r="J412" s="2"/>
       <c r="K412" s="3"/>
-      <c r="L412" s="2"/>
+      <c r="L412" s="3"/>
       <c r="M412" s="2"/>
       <c r="N412" s="2"/>
       <c r="O412" s="3"/>
@@ -31849,7 +31848,7 @@
       <c r="I415" s="2"/>
       <c r="J415" s="2"/>
       <c r="K415" s="3"/>
-      <c r="L415" s="3"/>
+      <c r="L415" s="2"/>
       <c r="M415" s="2"/>
       <c r="N415" s="2"/>
       <c r="O415" s="3"/>
@@ -31916,14 +31915,14 @@
       <c r="B416" s="3"/>
       <c r="C416" s="3"/>
       <c r="D416" s="3"/>
-      <c r="E416" s="3"/>
+      <c r="E416" s="2"/>
       <c r="F416" s="2"/>
       <c r="G416" s="3"/>
       <c r="H416" s="3"/>
       <c r="I416" s="2"/>
       <c r="J416" s="2"/>
       <c r="K416" s="3"/>
-      <c r="L416" s="2"/>
+      <c r="L416" s="3"/>
       <c r="M416" s="2"/>
       <c r="N416" s="2"/>
       <c r="O416" s="3"/>
@@ -32434,7 +32433,7 @@
       <c r="B423" s="3"/>
       <c r="C423" s="3"/>
       <c r="D423" s="3"/>
-      <c r="E423" s="2"/>
+      <c r="E423" s="3"/>
       <c r="F423" s="2"/>
       <c r="G423" s="3"/>
       <c r="H423" s="3"/>
@@ -32451,14 +32450,14 @@
       <c r="S423" s="3"/>
       <c r="T423" s="3"/>
       <c r="U423" s="3"/>
-      <c r="V423" s="2"/>
+      <c r="V423" s="3"/>
       <c r="W423" s="2"/>
       <c r="X423" s="3"/>
       <c r="Y423" s="2"/>
       <c r="Z423" s="3"/>
       <c r="AA423" s="4"/>
       <c r="AB423" s="5"/>
-      <c r="AC423" s="2"/>
+      <c r="AC423" s="3"/>
       <c r="AD423" s="3"/>
       <c r="AE423" s="3"/>
       <c r="AF423" s="4"/>
@@ -32475,7 +32474,7 @@
       <c r="AQ423" s="3"/>
       <c r="AR423" s="3"/>
       <c r="AS423" s="3"/>
-      <c r="AT423" s="3"/>
+      <c r="AT423" s="2"/>
       <c r="AU423" s="3"/>
       <c r="AV423" s="3"/>
       <c r="AW423" s="3"/>
@@ -32582,7 +32581,7 @@
       <c r="B425" s="3"/>
       <c r="C425" s="3"/>
       <c r="D425" s="3"/>
-      <c r="E425" s="3"/>
+      <c r="E425" s="2"/>
       <c r="F425" s="2"/>
       <c r="G425" s="3"/>
       <c r="H425" s="3"/>
@@ -32599,14 +32598,14 @@
       <c r="S425" s="3"/>
       <c r="T425" s="3"/>
       <c r="U425" s="3"/>
-      <c r="V425" s="3"/>
+      <c r="V425" s="2"/>
       <c r="W425" s="2"/>
       <c r="X425" s="3"/>
       <c r="Y425" s="2"/>
       <c r="Z425" s="3"/>
       <c r="AA425" s="4"/>
       <c r="AB425" s="5"/>
-      <c r="AC425" s="3"/>
+      <c r="AC425" s="2"/>
       <c r="AD425" s="3"/>
       <c r="AE425" s="3"/>
       <c r="AF425" s="4"/>
@@ -32623,7 +32622,7 @@
       <c r="AQ425" s="3"/>
       <c r="AR425" s="3"/>
       <c r="AS425" s="3"/>
-      <c r="AT425" s="2"/>
+      <c r="AT425" s="3"/>
       <c r="AU425" s="3"/>
       <c r="AV425" s="3"/>
       <c r="AW425" s="3"/>
@@ -32651,80 +32650,7 @@
       <c r="BS425" s="3"/>
       <c r="BT425" s="3"/>
     </row>
-    <row r="426" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A426" s="2"/>
-      <c r="B426" s="3"/>
-      <c r="C426" s="3"/>
-      <c r="D426" s="3"/>
-      <c r="E426" s="2"/>
-      <c r="F426" s="2"/>
-      <c r="G426" s="3"/>
-      <c r="H426" s="3"/>
-      <c r="I426" s="2"/>
-      <c r="J426" s="2"/>
-      <c r="K426" s="3"/>
-      <c r="L426" s="3"/>
-      <c r="M426" s="2"/>
-      <c r="N426" s="2"/>
-      <c r="O426" s="3"/>
-      <c r="P426" s="3"/>
-      <c r="Q426" s="3"/>
-      <c r="R426" s="3"/>
-      <c r="S426" s="3"/>
-      <c r="T426" s="3"/>
-      <c r="U426" s="3"/>
-      <c r="V426" s="2"/>
-      <c r="W426" s="2"/>
-      <c r="X426" s="3"/>
-      <c r="Y426" s="2"/>
-      <c r="Z426" s="3"/>
-      <c r="AA426" s="4"/>
-      <c r="AB426" s="5"/>
-      <c r="AC426" s="2"/>
-      <c r="AD426" s="3"/>
-      <c r="AE426" s="3"/>
-      <c r="AF426" s="4"/>
-      <c r="AG426" s="3"/>
-      <c r="AH426" s="2"/>
-      <c r="AI426" s="3"/>
-      <c r="AJ426" s="3"/>
-      <c r="AK426" s="3"/>
-      <c r="AL426" s="3"/>
-      <c r="AM426" s="3"/>
-      <c r="AN426" s="3"/>
-      <c r="AO426" s="3"/>
-      <c r="AP426" s="3"/>
-      <c r="AQ426" s="3"/>
-      <c r="AR426" s="3"/>
-      <c r="AS426" s="3"/>
-      <c r="AT426" s="3"/>
-      <c r="AU426" s="3"/>
-      <c r="AV426" s="3"/>
-      <c r="AW426" s="3"/>
-      <c r="AX426" s="3"/>
-      <c r="AY426" s="3"/>
-      <c r="AZ426" s="3"/>
-      <c r="BA426" s="3"/>
-      <c r="BB426" s="3"/>
-      <c r="BC426" s="3"/>
-      <c r="BD426" s="3"/>
-      <c r="BE426" s="3"/>
-      <c r="BF426" s="3"/>
-      <c r="BG426" s="3"/>
-      <c r="BH426" s="3"/>
-      <c r="BI426" s="3"/>
-      <c r="BJ426" s="3"/>
-      <c r="BK426" s="3"/>
-      <c r="BL426" s="3"/>
-      <c r="BM426" s="3"/>
-      <c r="BN426" s="3"/>
-      <c r="BO426" s="3"/>
-      <c r="BP426" s="3"/>
-      <c r="BQ426" s="3"/>
-      <c r="BR426" s="3"/>
-      <c r="BS426" s="3"/>
-      <c r="BT426" s="3"/>
-    </row>
+    <row r="1048203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -33099,7 +33025,7 @@
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <autoFilter ref="A3:AZ426"/>
+  <autoFilter ref="A3:AZ425"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
